--- a/docs/105_十五音音節表.xlsx
+++ b/docs/105_十五音音節表.xlsx
@@ -8,18 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AlanJui\work\rime-tlpa\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39A21C91-6D21-4441-A44A-C0D98E2F85F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A156D487-C636-445D-BAFB-AD72F3EF71A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="2" xr2:uid="{5BF56E62-E34C-4B16-A26D-70A9456E8A67}"/>
+    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="15720" activeTab="3" xr2:uid="{5BF56E62-E34C-4B16-A26D-70A9456E8A67}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
     <sheet name="十五音聲母" sheetId="4" r:id="rId2"/>
     <sheet name="十五音韻母" sheetId="5" r:id="rId3"/>
     <sheet name="十五音韻母【台羅拼音】" sheetId="7" r:id="rId4"/>
-    <sheet name="十五音音節表" sheetId="6" r:id="rId5"/>
-    <sheet name="十五音音節表【BoPoMo序】" sheetId="2" r:id="rId6"/>
-    <sheet name="音節表【台羅拼音序】" sheetId="3" r:id="rId7"/>
+    <sheet name="工作表2" sheetId="8" r:id="rId5"/>
+    <sheet name="十五音音節表" sheetId="6" r:id="rId6"/>
+    <sheet name="十五音音節表【BoPoMo序】" sheetId="2" r:id="rId7"/>
+    <sheet name="音節表【台羅拼音序】" sheetId="3" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +39,7 @@
       </xcalcf:calcFeatures>
     </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="2"/>
+      <xlwcv:version warnBelowVersion="2" setVersion="2"/>
     </ext>
   </extLst>
 </workbook>
@@ -67,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4902" uniqueCount="1402">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5169" uniqueCount="1557">
   <si>
     <t>十五音</t>
   </si>
@@ -5047,6 +5048,486 @@
     <t>ɛŋ</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
+  <si>
+    <t>促聲判斷</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">    - xform/un([48])/ut$1/    # 君</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    - xform/ian([48])/iat$1/    # 堅</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    - xform/im([48])/ip$1/    # 金</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    - xform/ui([48])/$1/    # 規</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    - xform/([48])/ee$1/    # 規</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    - xform/ee([48])/eeh$1/    # 嘉</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    - xform/an([48])/at$1/    # 干</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    - xform/ong([48])/ok$1/    # 公</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    - xform/uai([48])/uaih$1/    # 乖</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    - xform/ing([48])/ik$1/    # 經</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    - xform/uan([48])/uat$1/    # 觀</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    - xform/oo([48])/ooh$1/    # 沽</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    - xform/iau([48])/iauh$1/    # 嬌</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    - xform/e([48])/$1/    # 稽</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    - xform/([48])/iong$1/    # </t>
+  </si>
+  <si>
+    <t xml:space="preserve">    - xform/iong([48])/iok$1/    # 恭</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    - xform/o([48])/oh$1/    # 高</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    - xform/ai([48])/$1/    # 皆</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    - xform/([48])/in$1/    # </t>
+  </si>
+  <si>
+    <t xml:space="preserve">    - xform/in([48])/it$1/    # 巾</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    - xform/iang([48])/iak$1/    # 姜</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    - xform/am([48])/ap$1/    # 甘</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    - xform/ua([48])/uah$1/    # 瓜</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    - xform/ang([48])/ak$1/    # 江</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    - xform/iam([48])/iap$1/    # 兼</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    - xform/au([48])/auh$1/    # 交</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    - xform/ia([48])/iah$1/    # 迦</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    - xform/ue([48])/ueh$1/    # 檜</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    - xform/ann([48])/annh$1/    # 監</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    - xform/u([48])/uh$1/    # 艍</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    - xform/a([48])/ah$1/    # 膠</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    - xform/i([48])/ih$1/    # 居</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    - xform/iu([48])/$1/    # 丩</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    - xform/([48])/enn$1/    # </t>
+  </si>
+  <si>
+    <t xml:space="preserve">    - xform/enn([48])/ennh$1/    # 更</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    - xform/uinn([48])/$1/    # 褌</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    - xform/([48])/io$1/    # </t>
+  </si>
+  <si>
+    <t xml:space="preserve">    - xform/io([48])/ioh$1/    # 茄</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    - xform/inn([48])/$1/    # 梔</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    - xform/([48])/ionn$1/    # 梔</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    - xform/ionn([48])/$1/    # 薑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    - xform/([48])/iann$1/    # </t>
+  </si>
+  <si>
+    <t xml:space="preserve">    - xform/iann([48])/iannh$1/    # 驚</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    - xform/uann([48])/$1/    # 官</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    - xform/([48])/ng$1/    # </t>
+  </si>
+  <si>
+    <t xml:space="preserve">    - xform/ng([48])/ngh$1/    # 鋼</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    - xform/([48])/eh$1/    # 伽</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    - xform/ainn([48])/$1/    # 閒</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    - xform/([48])/onn$1/    # </t>
+  </si>
+  <si>
+    <t xml:space="preserve">    - xform/onn([48])/$1/    # 姑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    - xform/([48])/m$1/    # </t>
+  </si>
+  <si>
+    <t xml:space="preserve">    - xform/m([48])/mh$1/    # 姆</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    - xform/uang([48])/$1/    # 光</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    - xform/([48])/uainn$1/    # 光</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    - xform/uainn([48])/uainnh$1/    # 閂</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    - xform/([48])/$1/    # 糜</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    - xform/([48])/iaunn$1/    # 糜</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    - xform/iaunn([48])/$1/    # 嘄</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    - xform/([48])/om$1/    # 嘄</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    - xform/om([48])/op$1/    # 箴</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    - xform/([48])/$1/    # 爻</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    - xform/([48])/$1/    # </t>
+  </si>
+  <si>
+    <t xml:space="preserve">    - xform/([48])/onnh$1/    # 扛</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    - xform/iunn([48])/iunnh$1/    # 牛</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    - xform/er([48])/ir$1/    # </t>
+  </si>
+  <si>
+    <t xml:space="preserve">    - xform/ir([48])/$1/    # </t>
+  </si>
+  <si>
+    <t>字母長</t>
+  </si>
+  <si>
+    <t>字母長</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>xform</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>轉換式</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>xform轉換式</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    - xform/un([48?])/ut$1/    # 君</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    - xform/ut([48?])/ian$1/    # 君</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    - xform/ian([48?])/iat$1/    # 堅</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    - xform/iat([48?])/im$1/    # 堅</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    - xform/im([48?])/ip$1/    # 金</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    - xform/ip([48?])/ui$1/    # 金</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    - xform/ui([48?])/$1/    # 規</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    - xform/ee([48?])/eeh$1/    # 嘉</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    - xform/eeh([48?])/an$1/    # 嘉</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    - xform/an([48?])/at$1/    # 干</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    - xform/at([48?])/ong$1/    # 干</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    - xform/ong([48?])/ok$1/    # 公</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    - xform/ok([48?])/uai$1/    # 公</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    - xform/uai([48?])/uaih$1/    # 乖</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    - xform/uaih([48?])/ing$1/    # 乖</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    - xform/ing([48?])/ik$1/    # 經</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    - xform/ik([48?])/uan$1/    # 經</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    - xform/uan([48?])/uat$1/    # 觀</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    - xform/uat([48?])/oo$1/    # 觀</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    - xform/oo([48?])/ooh$1/    # 沽</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    - xform/ooh([48?])/iau$1/    # 沽</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    - xform/iau([48?])/iauh$1/    # 嬌</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    - xform/iauh([48?])/e$1/    # 嬌</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    - xform/e([48?])/$1/    # 稽</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    - xform/iong([48?])/iok$1/    # 恭</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    - xform/iok([48?])/o$1/    # 恭</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    - xform/o([48?])/oh$1/    # 高</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    - xform/oh([48?])/ai$1/    # 高</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    - xform/ai([48?])/$1/    # 皆</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    - xform/in([48?])/it$1/    # 巾</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    - xform/it([48?])/iang$1/    # 巾</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    - xform/iang([48?])/iak$1/    # 姜</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    - xform/iak([48?])/am$1/    # 姜</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    - xform/am([48?])/ap$1/    # 甘</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    - xform/ap([48?])/ua$1/    # 甘</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    - xform/ua([48?])/uah$1/    # 瓜</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    - xform/uah([48?])/ang$1/    # 瓜</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    - xform/ang([48?])/ak$1/    # 江</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    - xform/ak([48?])/iam$1/    # 江</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    - xform/iam([48?])/iap$1/    # 兼</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    - xform/iap([48?])/au$1/    # 兼</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    - xform/au([48?])/auh$1/    # 交</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    - xform/auh([48?])/ia$1/    # 交</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    - xform/ia([48?])/iah$1/    # 迦</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    - xform/iah([48?])/ue$1/    # 迦</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    - xform/ue([48?])/ueh$1/    # 檜</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    - xform/ueh([48?])/ann$1/    # 檜</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    - xform/ann([48?])/annh$1/    # 監</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    - xform/annh([48?])/u$1/    # 監</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    - xform/u([48?])/uh$1/    # 艍</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    - xform/uh([48?])/a$1/    # 艍</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    - xform/a([48?])/ah$1/    # 膠</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    - xform/ah([48?])/i$1/    # 膠</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    - xform/i([48?])/ih$1/    # 居</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    - xform/ih([48?])/iu$1/    # 居</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    - xform/iu([48?])/$1/    # 丩</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    - xform/enn([48?])/ennh$1/    # 更</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    - xform/ennh([48?])/uinn$1/    # 更</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    - xform/uinn([48?])/$1/    # 褌</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    - xform/io([48?])/ioh$1/    # 茄</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    - xform/ioh([48?])/inn$1/    # 茄</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    - xform/inn([48?])/$1/    # 梔</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    - xform/ionn([48?])/$1/    # 薑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    - xform/iann([48?])/iannh$1/    # 驚</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    - xform/iannh([48?])/uann$1/    # 驚</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    - xform/uann([48?])/$1/    # 官</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    - xform/ng([48?])/ngh$1/    # 鋼</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    - xform/ngh([48?])/$1/    # 鋼</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    - xform/eh([48?])/ainn$1/    # 伽</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    - xform/ainn([48?])/$1/    # 閒</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    - xform/onn([48?])/$1/    # 姑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    - xform/m([48?])/mh$1/    # 姆</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    - xform/mh([48?])/uang$1/    # 姆</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    - xform/uang([48?])/$1/    # 光</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    - xform/uainn([48?])/uainnh$1/    # 閂</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    - xform/uainnh([48?])/$1/    # 閂</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    - xform/iaunn([48?])/$1/    # 嘄</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    - xform/om([48?])/op$1/    # 箴</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    - xform/op([48?])/$1/    # 箴</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    - xform/onnh([48?])/iunn$1/    # 扛</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    - xform/iunn([48?])/iunnh$1/    # 牛</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    - xform/iunnh([48?])/er$1/    # 牛</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    - xform/er([48?])/ir$1/    # </t>
+  </si>
+  <si>
+    <t xml:space="preserve">    - xform/ir([48?])/$1/    # </t>
+  </si>
 </sst>
 </file>
 
@@ -5055,7 +5536,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="General;;"/>
   </numFmts>
-  <fonts count="41">
+  <fonts count="43">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -5323,6 +5804,20 @@
       <name val="Noto Sans TC Medium"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="細明體"/>
+      <family val="3"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="新細明體"/>
+      <family val="1"/>
+      <charset val="136"/>
+    </font>
   </fonts>
   <fills count="9">
     <fill>
@@ -5508,7 +6003,7 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="108">
+  <cellXfs count="106">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -5791,9 +6286,6 @@
     <xf numFmtId="0" fontId="23" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="2"/>
     </xf>
@@ -5803,16 +6295,7 @@
     <xf numFmtId="0" fontId="25" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="40" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -5821,24 +6304,37 @@
     <xf numFmtId="176" fontId="3" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="33" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
     <cellStyle name="一般 2" xfId="1" xr:uid="{E57FFF29-A59B-46E2-A496-66E529F383CC}"/>
   </cellStyles>
-  <dxfs count="80">
+  <dxfs count="71">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="2"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF7030A0"/>
@@ -6029,29 +6525,9 @@
       </fill>
     </dxf>
     <dxf>
-      <font>
-        <color rgb="FF7030A0"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF00B050"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFFFFCC"/>
+          <bgColor theme="2"/>
         </patternFill>
       </fill>
     </dxf>
@@ -6379,13 +6855,6 @@
       </border>
     </dxf>
     <dxf>
-      <border>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
       <border outline="0">
         <bottom style="thin">
           <color rgb="FFBFBFBF"/>
@@ -6399,6 +6868,13 @@
           <bgColor rgb="FFFFFFFF"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <border>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
     </dxf>
     <dxf>
       <font>
@@ -6441,74 +6917,6 @@
           <color indexed="64"/>
         </horizontal>
       </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF7030A0"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF00B050"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF7030A0"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF00B050"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2"/>
-        </patternFill>
-      </fill>
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
@@ -7076,73 +7484,73 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D4D53CAA-1AC5-435B-8EFA-F8A8BD117A7E}" name="聲母表" displayName="聲母表" ref="A1:M23" totalsRowShown="0" headerRowDxfId="62" headerRowBorderDxfId="61" tableBorderDxfId="60" totalsRowBorderDxfId="59">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D4D53CAA-1AC5-435B-8EFA-F8A8BD117A7E}" name="聲母表" displayName="聲母表" ref="A1:M23" totalsRowShown="0" headerRowDxfId="53" headerRowBorderDxfId="52" tableBorderDxfId="51" totalsRowBorderDxfId="50">
   <autoFilter ref="A1:M23" xr:uid="{D4D53CAA-1AC5-435B-8EFA-F8A8BD117A7E}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:M23">
     <sortCondition ref="B2:B23"/>
   </sortState>
   <tableColumns count="13">
-    <tableColumn id="1" xr3:uid="{C83BAA32-BD80-4A6A-B041-EFB4E5BF0EAD}" name="序號" dataDxfId="58"/>
-    <tableColumn id="13" xr3:uid="{F49FED34-8A68-43B1-A51D-B6550AE47953}" name="音序" dataDxfId="57"/>
-    <tableColumn id="2" xr3:uid="{A6E193EA-549C-4029-8823-9DFE17442FF1}" name="漢字例" dataDxfId="56"/>
+    <tableColumn id="1" xr3:uid="{C83BAA32-BD80-4A6A-B041-EFB4E5BF0EAD}" name="序號" dataDxfId="49"/>
+    <tableColumn id="13" xr3:uid="{F49FED34-8A68-43B1-A51D-B6550AE47953}" name="音序" dataDxfId="48"/>
+    <tableColumn id="2" xr3:uid="{A6E193EA-549C-4029-8823-9DFE17442FF1}" name="漢字例" dataDxfId="47"/>
     <tableColumn id="3" xr3:uid="{6A134241-ADBE-4BD1-A5C6-D00613EF82BB}" name="十五音"/>
     <tableColumn id="14" xr3:uid="{E372684C-80C8-4FBB-8980-C9CF51A93857}" name="新十五音"/>
-    <tableColumn id="5" xr3:uid="{D62696E3-AB0E-4D6E-B91E-A6119DD3697B}" name="國際音標" dataDxfId="55"/>
+    <tableColumn id="5" xr3:uid="{D62696E3-AB0E-4D6E-B91E-A6119DD3697B}" name="國際音標" dataDxfId="46"/>
     <tableColumn id="4" xr3:uid="{9014A3FB-03BF-4D2A-833F-6D18B2FC48DE}" name="台羅拼音"/>
-    <tableColumn id="7" xr3:uid="{DE46D56A-2F6F-460E-97EB-6221DBF36190}" name="台語音標" dataDxfId="54"/>
-    <tableColumn id="8" xr3:uid="{6416C7B5-02F3-4A4B-A59B-F5CCC29DA4BC}" name="白話字" dataDxfId="53"/>
-    <tableColumn id="9" xr3:uid="{499810EC-AD1D-46F1-B997-07B17DA95245}" name="閩拼方案" dataDxfId="52"/>
-    <tableColumn id="10" xr3:uid="{5D3D9CE2-D240-4ADB-A8EC-5DF1AD126A55}" name="注音二式" dataDxfId="51"/>
-    <tableColumn id="11" xr3:uid="{E1D819DB-0A80-42E2-A97A-E02BCFDCB063}" name="方音符號" dataDxfId="50"/>
-    <tableColumn id="12" xr3:uid="{F009D45F-2383-4AB9-BA72-A06F1F14EE9E}" name="台語注音" dataDxfId="49"/>
+    <tableColumn id="7" xr3:uid="{DE46D56A-2F6F-460E-97EB-6221DBF36190}" name="台語音標" dataDxfId="45"/>
+    <tableColumn id="8" xr3:uid="{6416C7B5-02F3-4A4B-A59B-F5CCC29DA4BC}" name="白話字" dataDxfId="44"/>
+    <tableColumn id="9" xr3:uid="{499810EC-AD1D-46F1-B997-07B17DA95245}" name="閩拼方案" dataDxfId="43"/>
+    <tableColumn id="10" xr3:uid="{5D3D9CE2-D240-4ADB-A8EC-5DF1AD126A55}" name="注音二式" dataDxfId="42"/>
+    <tableColumn id="11" xr3:uid="{E1D819DB-0A80-42E2-A97A-E02BCFDCB063}" name="方音符號" dataDxfId="41"/>
+    <tableColumn id="12" xr3:uid="{F009D45F-2383-4AB9-BA72-A06F1F14EE9E}" name="台語注音" dataDxfId="40"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{23E007DD-5182-4B78-80DA-A6AB6CA14806}" name="韻母表" displayName="韻母表" ref="A1:M101" totalsRowShown="0" headerRowDxfId="79" dataDxfId="77" headerRowBorderDxfId="78" tableBorderDxfId="76">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{23E007DD-5182-4B78-80DA-A6AB6CA14806}" name="韻母表" displayName="韻母表" ref="A1:M101" totalsRowShown="0" headerRowDxfId="70" dataDxfId="68" headerRowBorderDxfId="69" tableBorderDxfId="67">
   <autoFilter ref="A1:M101" xr:uid="{23E007DD-5182-4B78-80DA-A6AB6CA14806}"/>
   <tableColumns count="13">
-    <tableColumn id="1" xr3:uid="{89688CC6-39FE-4435-8344-AAA347FCBED4}" name="序號" dataDxfId="75"/>
-    <tableColumn id="5" xr3:uid="{8A21DB38-57E0-482B-95FC-B597347A8BDE}" name="韻序" dataDxfId="74">
+    <tableColumn id="1" xr3:uid="{89688CC6-39FE-4435-8344-AAA347FCBED4}" name="序號" dataDxfId="66"/>
+    <tableColumn id="5" xr3:uid="{8A21DB38-57E0-482B-95FC-B597347A8BDE}" name="韻序" dataDxfId="65">
       <calculatedColumnFormula xml:space="preserve"> IF(MOD(韻母表[[#This Row],[序號]],2)=0, 韻母表[[#This Row],[序號]]/2, ROUNDUP(韻母表[[#This Row],[序號]]/2,0))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{C94EAE18-8E51-4E6B-AD98-90C9372F5188}" name="漢字例" dataDxfId="73"/>
-    <tableColumn id="3" xr3:uid="{2C1D54ED-CBE3-4710-8C55-0AC6BB332524}" name="十五音" dataDxfId="72"/>
-    <tableColumn id="6" xr3:uid="{9CAF41C9-1F52-4C5E-8A5F-0F0DECF6DB84}" name="國際音標" dataDxfId="71"/>
-    <tableColumn id="7" xr3:uid="{6F37C033-2A03-4BC2-AB1F-B6A6D6E849EF}" name="國際音標2" dataDxfId="70"/>
-    <tableColumn id="4" xr3:uid="{F38AD89D-9FC9-4519-A8D2-EEB6952EEAC1}" name="台羅拼音" dataDxfId="69"/>
-    <tableColumn id="8" xr3:uid="{E2316195-DFB7-4D73-80AE-5AF5CB638098}" name="台語音標" dataDxfId="68"/>
-    <tableColumn id="9" xr3:uid="{0A03E710-B799-4430-BEA2-5ABB2CD0E1A1}" name="白話字" dataDxfId="67"/>
-    <tableColumn id="10" xr3:uid="{CA8E7716-EF33-499C-AAB0-A73DA24D6D6C}" name="閩拼方案" dataDxfId="66"/>
-    <tableColumn id="11" xr3:uid="{44C917DF-FD45-429A-B606-AA4AA4A2D8B8}" name="注音二式" dataDxfId="65"/>
-    <tableColumn id="12" xr3:uid="{A817EC74-78DE-4E34-8B25-4BAD35257767}" name="方音符號" dataDxfId="64"/>
-    <tableColumn id="13" xr3:uid="{156C12E1-9EC9-4906-AFF2-E587C73D5F0D}" name="台語注音" dataDxfId="63"/>
+    <tableColumn id="2" xr3:uid="{C94EAE18-8E51-4E6B-AD98-90C9372F5188}" name="漢字例" dataDxfId="64"/>
+    <tableColumn id="3" xr3:uid="{2C1D54ED-CBE3-4710-8C55-0AC6BB332524}" name="十五音" dataDxfId="63"/>
+    <tableColumn id="6" xr3:uid="{9CAF41C9-1F52-4C5E-8A5F-0F0DECF6DB84}" name="國際音標" dataDxfId="62"/>
+    <tableColumn id="7" xr3:uid="{6F37C033-2A03-4BC2-AB1F-B6A6D6E849EF}" name="國際音標2" dataDxfId="61"/>
+    <tableColumn id="4" xr3:uid="{F38AD89D-9FC9-4519-A8D2-EEB6952EEAC1}" name="台羅拼音" dataDxfId="60"/>
+    <tableColumn id="8" xr3:uid="{E2316195-DFB7-4D73-80AE-5AF5CB638098}" name="台語音標" dataDxfId="59"/>
+    <tableColumn id="9" xr3:uid="{0A03E710-B799-4430-BEA2-5ABB2CD0E1A1}" name="白話字" dataDxfId="58"/>
+    <tableColumn id="10" xr3:uid="{CA8E7716-EF33-499C-AAB0-A73DA24D6D6C}" name="閩拼方案" dataDxfId="57"/>
+    <tableColumn id="11" xr3:uid="{44C917DF-FD45-429A-B606-AA4AA4A2D8B8}" name="注音二式" dataDxfId="56"/>
+    <tableColumn id="12" xr3:uid="{A817EC74-78DE-4E34-8B25-4BAD35257767}" name="方音符號" dataDxfId="55"/>
+    <tableColumn id="13" xr3:uid="{156C12E1-9EC9-4906-AFF2-E587C73D5F0D}" name="台語注音" dataDxfId="54"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{445995B0-5C2F-4E9A-9739-9EF19DAF1BE1}" name="韻母表_4" displayName="韻母表_4" ref="A1:M104" totalsRowShown="0" headerRowDxfId="40" dataDxfId="39" headerRowBorderDxfId="37" tableBorderDxfId="38">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{445995B0-5C2F-4E9A-9739-9EF19DAF1BE1}" name="韻母表_4" displayName="韻母表_4" ref="A1:M104" totalsRowShown="0" headerRowDxfId="39" dataDxfId="37" headerRowBorderDxfId="38" tableBorderDxfId="36">
   <autoFilter ref="A1:M104" xr:uid="{23E007DD-5182-4B78-80DA-A6AB6CA14806}"/>
   <tableColumns count="13">
-    <tableColumn id="1" xr3:uid="{F8E86299-D90F-4592-ABDC-A0D652A239EA}" name="序號" dataDxfId="36"/>
-    <tableColumn id="5" xr3:uid="{24C83CBE-F51A-4055-8C74-B669A9FEC2BB}" name="韻序" dataDxfId="35">
+    <tableColumn id="1" xr3:uid="{F8E86299-D90F-4592-ABDC-A0D652A239EA}" name="序號" dataDxfId="35"/>
+    <tableColumn id="5" xr3:uid="{24C83CBE-F51A-4055-8C74-B669A9FEC2BB}" name="韻序" dataDxfId="34">
       <calculatedColumnFormula xml:space="preserve"> IF(MOD(韻母表_4[[#This Row],[序號]],2)=0, 韻母表_4[[#This Row],[序號]]/2, ROUNDUP(韻母表_4[[#This Row],[序號]]/2,0))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{0C6809DB-3017-45B3-875B-B288340415E9}" name="漢字例" dataDxfId="34"/>
-    <tableColumn id="3" xr3:uid="{EC7EADF7-9219-4A1D-BADE-5B70D687F5BE}" name="十五音" dataDxfId="33"/>
-    <tableColumn id="6" xr3:uid="{D42B0375-1395-4AA5-9592-400D314FF4A6}" name="國際音標" dataDxfId="32"/>
-    <tableColumn id="7" xr3:uid="{4FF66326-E3D3-4547-AACD-6FB02A224286}" name="國際音標2" dataDxfId="31"/>
-    <tableColumn id="4" xr3:uid="{14118607-EB7E-45B6-BA80-82DA602FEA15}" name="台羅拼音" dataDxfId="30"/>
-    <tableColumn id="8" xr3:uid="{B9308C5F-5158-4627-97E6-3777D062785C}" name="台語音標" dataDxfId="29"/>
-    <tableColumn id="9" xr3:uid="{4D40D46C-12FE-42D7-893F-D328F6CC3B39}" name="白話字" dataDxfId="28"/>
-    <tableColumn id="10" xr3:uid="{E55C9A5F-E95C-4F9C-95C2-8A79906E6908}" name="閩拼方案" dataDxfId="27"/>
-    <tableColumn id="11" xr3:uid="{2FF03B77-E51C-4F7F-AC68-ACCC6F92D98A}" name="注音二式" dataDxfId="26"/>
-    <tableColumn id="12" xr3:uid="{E71F16DA-D83F-43D8-B782-448D0B3850FD}" name="方音符號" dataDxfId="25"/>
-    <tableColumn id="13" xr3:uid="{AF2B7E9E-8412-4DD8-AF9D-37FEF1CA2005}" name="台語注音" dataDxfId="24"/>
+    <tableColumn id="2" xr3:uid="{0C6809DB-3017-45B3-875B-B288340415E9}" name="漢字例" dataDxfId="33"/>
+    <tableColumn id="3" xr3:uid="{EC7EADF7-9219-4A1D-BADE-5B70D687F5BE}" name="十五音" dataDxfId="32"/>
+    <tableColumn id="6" xr3:uid="{D42B0375-1395-4AA5-9592-400D314FF4A6}" name="國際音標" dataDxfId="31"/>
+    <tableColumn id="7" xr3:uid="{4FF66326-E3D3-4547-AACD-6FB02A224286}" name="國際音標2" dataDxfId="30"/>
+    <tableColumn id="4" xr3:uid="{14118607-EB7E-45B6-BA80-82DA602FEA15}" name="台羅拼音" dataDxfId="29"/>
+    <tableColumn id="8" xr3:uid="{B9308C5F-5158-4627-97E6-3777D062785C}" name="台語音標" dataDxfId="28"/>
+    <tableColumn id="9" xr3:uid="{4D40D46C-12FE-42D7-893F-D328F6CC3B39}" name="白話字" dataDxfId="27"/>
+    <tableColumn id="10" xr3:uid="{E55C9A5F-E95C-4F9C-95C2-8A79906E6908}" name="閩拼方案" dataDxfId="26"/>
+    <tableColumn id="11" xr3:uid="{2FF03B77-E51C-4F7F-AC68-ACCC6F92D98A}" name="注音二式" dataDxfId="25"/>
+    <tableColumn id="12" xr3:uid="{E71F16DA-D83F-43D8-B782-448D0B3850FD}" name="方音符號" dataDxfId="24"/>
+    <tableColumn id="13" xr3:uid="{AF2B7E9E-8412-4DD8-AF9D-37FEF1CA2005}" name="台語注音" dataDxfId="23"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -7468,7 +7876,7 @@
   <wetp:taskpane dockstate="right" visibility="0" width="0" row="0">
     <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </wetp:taskpane>
-  <wetp:taskpane dockstate="right" visibility="0" width="350" row="2">
+  <wetp:taskpane dockstate="right" visibility="0" width="350" row="3">
     <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
   </wetp:taskpane>
 </wetp:taskpanes>
@@ -7512,12 +7920,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="44.25">
-      <c r="A1" s="94" t="s">
+      <c r="A1" s="104" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="94"/>
-      <c r="C1" s="94"/>
-      <c r="D1" s="94"/>
+      <c r="B1" s="104"/>
+      <c r="C1" s="104"/>
+      <c r="D1" s="104"/>
       <c r="E1" s="4" t="s">
         <v>18</v>
       </c>
@@ -7586,12 +7994,12 @@
       </c>
     </row>
     <row r="2" spans="1:26" ht="29.25">
-      <c r="A2" s="94" t="s">
+      <c r="A2" s="104" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="94"/>
-      <c r="C2" s="94"/>
-      <c r="D2" s="94"/>
+      <c r="B2" s="104"/>
+      <c r="C2" s="104"/>
+      <c r="D2" s="104"/>
       <c r="E2" s="8" t="s">
         <v>1</v>
       </c>
@@ -7660,12 +8068,12 @@
       </c>
     </row>
     <row r="3" spans="1:26" ht="29.25">
-      <c r="A3" s="94" t="s">
+      <c r="A3" s="104" t="s">
         <v>40</v>
       </c>
-      <c r="B3" s="94"/>
-      <c r="C3" s="94"/>
-      <c r="D3" s="94"/>
+      <c r="B3" s="104"/>
+      <c r="C3" s="104"/>
+      <c r="D3" s="104"/>
       <c r="E3" s="12"/>
       <c r="F3" s="12" t="s">
         <v>41</v>
@@ -17869,7 +18277,7 @@
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="E4:Z103">
-    <cfRule type="expression" dxfId="48" priority="1">
+    <cfRule type="expression" dxfId="22" priority="1">
       <formula>E4=""</formula>
     </cfRule>
   </conditionalFormatting>
@@ -18824,7 +19232,7 @@
       <c r="K23" s="70" t="s">
         <v>53</v>
       </c>
-      <c r="L23" s="95" t="s">
+      <c r="L23" s="94" t="s">
         <v>1385</v>
       </c>
       <c r="M23" s="70" t="s">
@@ -22873,13 +23281,13 @@
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="A2:M101">
-    <cfRule type="expression" dxfId="46" priority="1">
+    <cfRule type="expression" dxfId="21" priority="1">
       <formula>MOD($B2,2)&lt;&gt;0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="45" priority="2">
+    <cfRule type="expression" dxfId="20" priority="2">
       <formula>MOD($A2,2)&lt;&gt;0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="44" priority="3">
+    <cfRule type="expression" dxfId="19" priority="3">
       <formula>MOD($A2,2)=0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -22892,15 +23300,22 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59C75227-57C4-4844-A39D-F2B25DB9903D}">
-  <dimension ref="A1:Q104"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <dimension ref="A1:AD104"/>
+  <sheetFormatPr defaultRowHeight="22.5"/>
   <cols>
     <col min="1" max="2" width="8.125" customWidth="1"/>
     <col min="3" max="3" width="10.625" customWidth="1"/>
     <col min="4" max="13" width="14.25" customWidth="1"/>
+    <col min="18" max="18" width="13.25" customWidth="1"/>
+    <col min="19" max="19" width="16.375" style="41" customWidth="1"/>
+    <col min="20" max="20" width="34.5" style="41" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="38.75" style="41" customWidth="1"/>
+    <col min="22" max="22" width="9" style="41"/>
+    <col min="23" max="23" width="42.125" style="41" customWidth="1"/>
+    <col min="24" max="30" width="9" style="41"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="25.5">
+    <row r="1" spans="1:23" ht="25.5">
       <c r="A1" s="80" t="s">
         <v>1054</v>
       </c>
@@ -22951,8 +23366,20 @@
       <c r="Q1" t="s">
         <v>1107</v>
       </c>
-    </row>
-    <row r="2" spans="1:17" ht="44.25">
+      <c r="R1" t="s">
+        <v>1402</v>
+      </c>
+      <c r="S1" s="105" t="s">
+        <v>1470</v>
+      </c>
+      <c r="T1" s="41" t="s">
+        <v>1471</v>
+      </c>
+      <c r="U1" s="41" t="s">
+        <v>1471</v>
+      </c>
+    </row>
+    <row r="2" spans="1:23" ht="44.25">
       <c r="A2" s="76">
         <v>1</v>
       </c>
@@ -22991,8 +23418,27 @@
       <c r="M2" s="79" t="s">
         <v>1066</v>
       </c>
-    </row>
-    <row r="3" spans="1:17" ht="44.25">
+      <c r="R2" t="b">
+        <f>IF(韻母表_4[[#This Row],[台羅拼音]]="", FALSE, ISNUMBER(FIND(RIGHT(韻母表_4[[#This Row],[台羅拼音]],1), "ptkh")))</f>
+        <v>0</v>
+      </c>
+      <c r="S2" s="41">
+        <f>IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R2=TRUE), "", LEN(韻母表_4[[#This Row],[台羅拼音]]))</f>
+        <v>2</v>
+      </c>
+      <c r="T2" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", $R2=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48?])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v xml:space="preserve">    - xform/un([48?])/ut$1/    # 君</v>
+      </c>
+      <c r="U2" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R2=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v xml:space="preserve">    - xform/un([48])/ut$1/    # 君</v>
+      </c>
+      <c r="W2" s="41" t="s">
+        <v>1403</v>
+      </c>
+    </row>
+    <row r="3" spans="1:23" ht="44.25">
       <c r="A3" s="54">
         <v>2</v>
       </c>
@@ -23031,8 +23477,27 @@
       <c r="M3" s="57" t="s">
         <v>1069</v>
       </c>
-    </row>
-    <row r="4" spans="1:17" ht="44.25">
+      <c r="R3" t="b">
+        <f>IF(韻母表_4[[#This Row],[台羅拼音]]="", FALSE, ISNUMBER(FIND(RIGHT(韻母表_4[[#This Row],[台羅拼音]],1), "ptkh")))</f>
+        <v>1</v>
+      </c>
+      <c r="S3" s="41" t="str">
+        <f>IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R3=TRUE), "", LEN(韻母表_4[[#This Row],[台羅拼音]]))</f>
+        <v/>
+      </c>
+      <c r="T3" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", $R3=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48?])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v/>
+      </c>
+      <c r="U3" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R3=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v/>
+      </c>
+      <c r="W3" s="41" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="4" spans="1:23" ht="44.25">
       <c r="A4" s="54">
         <v>3</v>
       </c>
@@ -23071,8 +23536,27 @@
       <c r="M4" s="57" t="s">
         <v>1070</v>
       </c>
-    </row>
-    <row r="5" spans="1:17" ht="44.25">
+      <c r="R4" t="b">
+        <f>IF(韻母表_4[[#This Row],[台羅拼音]]="", FALSE, ISNUMBER(FIND(RIGHT(韻母表_4[[#This Row],[台羅拼音]],1), "ptkh")))</f>
+        <v>0</v>
+      </c>
+      <c r="S4" s="41">
+        <f>IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R4=TRUE), "", LEN(韻母表_4[[#This Row],[台羅拼音]]))</f>
+        <v>3</v>
+      </c>
+      <c r="T4" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", $R4=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48?])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v xml:space="preserve">    - xform/ian([48?])/iat$1/    # 堅</v>
+      </c>
+      <c r="U4" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R4=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v xml:space="preserve">    - xform/ian([48])/iat$1/    # 堅</v>
+      </c>
+      <c r="W4" s="41" t="s">
+        <v>1404</v>
+      </c>
+    </row>
+    <row r="5" spans="1:23" ht="44.25">
       <c r="A5" s="54">
         <v>4</v>
       </c>
@@ -23111,8 +23595,27 @@
       <c r="M5" s="57" t="s">
         <v>1072</v>
       </c>
-    </row>
-    <row r="6" spans="1:17" ht="44.25">
+      <c r="R5" t="b">
+        <f>IF(韻母表_4[[#This Row],[台羅拼音]]="", FALSE, ISNUMBER(FIND(RIGHT(韻母表_4[[#This Row],[台羅拼音]],1), "ptkh")))</f>
+        <v>1</v>
+      </c>
+      <c r="S5" s="41" t="str">
+        <f>IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R5=TRUE), "", LEN(韻母表_4[[#This Row],[台羅拼音]]))</f>
+        <v/>
+      </c>
+      <c r="T5" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", $R5=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48?])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v/>
+      </c>
+      <c r="U5" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R5=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v/>
+      </c>
+      <c r="W5" s="41" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="6" spans="1:23" ht="44.25">
       <c r="A6" s="54">
         <v>5</v>
       </c>
@@ -23151,8 +23654,27 @@
       <c r="M6" s="57" t="s">
         <v>1074</v>
       </c>
-    </row>
-    <row r="7" spans="1:17" ht="44.25">
+      <c r="R6" t="b">
+        <f>IF(韻母表_4[[#This Row],[台羅拼音]]="", FALSE, ISNUMBER(FIND(RIGHT(韻母表_4[[#This Row],[台羅拼音]],1), "ptkh")))</f>
+        <v>0</v>
+      </c>
+      <c r="S6" s="41">
+        <f>IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R6=TRUE), "", LEN(韻母表_4[[#This Row],[台羅拼音]]))</f>
+        <v>2</v>
+      </c>
+      <c r="T6" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", $R6=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48?])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v xml:space="preserve">    - xform/im([48?])/ip$1/    # 金</v>
+      </c>
+      <c r="U6" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R6=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v xml:space="preserve">    - xform/im([48])/ip$1/    # 金</v>
+      </c>
+      <c r="W6" s="41" t="s">
+        <v>1405</v>
+      </c>
+    </row>
+    <row r="7" spans="1:23" ht="44.25">
       <c r="A7" s="54">
         <v>6</v>
       </c>
@@ -23191,8 +23713,27 @@
       <c r="M7" s="57" t="s">
         <v>1077</v>
       </c>
-    </row>
-    <row r="8" spans="1:17" ht="44.25">
+      <c r="R7" t="b">
+        <f>IF(韻母表_4[[#This Row],[台羅拼音]]="", FALSE, ISNUMBER(FIND(RIGHT(韻母表_4[[#This Row],[台羅拼音]],1), "ptkh")))</f>
+        <v>1</v>
+      </c>
+      <c r="S7" s="41" t="str">
+        <f>IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R7=TRUE), "", LEN(韻母表_4[[#This Row],[台羅拼音]]))</f>
+        <v/>
+      </c>
+      <c r="T7" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", $R7=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48?])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v/>
+      </c>
+      <c r="U7" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R7=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v/>
+      </c>
+      <c r="W7" s="41" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" ht="44.25">
       <c r="A8" s="54">
         <v>7</v>
       </c>
@@ -23231,8 +23772,27 @@
       <c r="M8" s="57" t="s">
         <v>1078</v>
       </c>
-    </row>
-    <row r="9" spans="1:17" ht="32.25">
+      <c r="R8" t="b">
+        <f>IF(韻母表_4[[#This Row],[台羅拼音]]="", FALSE, ISNUMBER(FIND(RIGHT(韻母表_4[[#This Row],[台羅拼音]],1), "ptkh")))</f>
+        <v>0</v>
+      </c>
+      <c r="S8" s="41">
+        <f>IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R8=TRUE), "", LEN(韻母表_4[[#This Row],[台羅拼音]]))</f>
+        <v>2</v>
+      </c>
+      <c r="T8" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", $R8=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48?])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v xml:space="preserve">    - xform/ui([48?])/$1/    # 規</v>
+      </c>
+      <c r="U8" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R8=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v xml:space="preserve">    - xform/ui([48])/$1/    # 規</v>
+      </c>
+      <c r="W8" s="41" t="s">
+        <v>1406</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" ht="32.25">
       <c r="A9" s="81">
         <v>8</v>
       </c>
@@ -23269,8 +23829,27 @@
       <c r="M9" s="84" t="s">
         <v>1079</v>
       </c>
-    </row>
-    <row r="10" spans="1:17" ht="44.25">
+      <c r="R9" t="b">
+        <f>IF(韻母表_4[[#This Row],[台羅拼音]]="", FALSE, ISNUMBER(FIND(RIGHT(韻母表_4[[#This Row],[台羅拼音]],1), "ptkh")))</f>
+        <v>0</v>
+      </c>
+      <c r="S9" s="41" t="str">
+        <f>IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R9=TRUE), "", LEN(韻母表_4[[#This Row],[台羅拼音]]))</f>
+        <v/>
+      </c>
+      <c r="T9" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", $R9=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48?])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v/>
+      </c>
+      <c r="U9" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R9=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v/>
+      </c>
+      <c r="W9" s="41" t="s">
+        <v>1407</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" ht="44.25">
       <c r="A10" s="54">
         <v>9</v>
       </c>
@@ -23311,8 +23890,27 @@
       <c r="M10" s="57" t="s">
         <v>1081</v>
       </c>
-    </row>
-    <row r="11" spans="1:17" ht="44.25">
+      <c r="R10" t="b">
+        <f>IF(韻母表_4[[#This Row],[台羅拼音]]="", FALSE, ISNUMBER(FIND(RIGHT(韻母表_4[[#This Row],[台羅拼音]],1), "ptkh")))</f>
+        <v>0</v>
+      </c>
+      <c r="S10" s="41">
+        <f>IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R10=TRUE), "", LEN(韻母表_4[[#This Row],[台羅拼音]]))</f>
+        <v>2</v>
+      </c>
+      <c r="T10" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", $R10=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48?])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v xml:space="preserve">    - xform/ee([48?])/eeh$1/    # 嘉</v>
+      </c>
+      <c r="U10" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R10=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v xml:space="preserve">    - xform/ee([48])/eeh$1/    # 嘉</v>
+      </c>
+      <c r="W10" s="41" t="s">
+        <v>1408</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" ht="44.25">
       <c r="A11" s="54">
         <v>10</v>
       </c>
@@ -23353,8 +23951,27 @@
       <c r="M11" s="57" t="s">
         <v>1084</v>
       </c>
-    </row>
-    <row r="12" spans="1:17" ht="44.25">
+      <c r="R11" t="b">
+        <f>IF(韻母表_4[[#This Row],[台羅拼音]]="", FALSE, ISNUMBER(FIND(RIGHT(韻母表_4[[#This Row],[台羅拼音]],1), "ptkh")))</f>
+        <v>1</v>
+      </c>
+      <c r="S11" s="41" t="str">
+        <f>IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R11=TRUE), "", LEN(韻母表_4[[#This Row],[台羅拼音]]))</f>
+        <v/>
+      </c>
+      <c r="T11" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", $R11=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48?])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v/>
+      </c>
+      <c r="U11" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R11=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v/>
+      </c>
+      <c r="W11" s="41" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="12" spans="1:23" ht="44.25">
       <c r="A12" s="54">
         <v>11</v>
       </c>
@@ -23393,8 +24010,27 @@
       <c r="M12" s="57" t="s">
         <v>1085</v>
       </c>
-    </row>
-    <row r="13" spans="1:17" ht="44.25">
+      <c r="R12" t="b">
+        <f>IF(韻母表_4[[#This Row],[台羅拼音]]="", FALSE, ISNUMBER(FIND(RIGHT(韻母表_4[[#This Row],[台羅拼音]],1), "ptkh")))</f>
+        <v>0</v>
+      </c>
+      <c r="S12" s="41">
+        <f>IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R12=TRUE), "", LEN(韻母表_4[[#This Row],[台羅拼音]]))</f>
+        <v>2</v>
+      </c>
+      <c r="T12" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", $R12=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48?])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v xml:space="preserve">    - xform/an([48?])/at$1/    # 干</v>
+      </c>
+      <c r="U12" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R12=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v xml:space="preserve">    - xform/an([48])/at$1/    # 干</v>
+      </c>
+      <c r="W12" s="41" t="s">
+        <v>1409</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" ht="44.25">
       <c r="A13" s="54">
         <v>12</v>
       </c>
@@ -23433,8 +24069,27 @@
       <c r="M13" s="57" t="s">
         <v>1088</v>
       </c>
-    </row>
-    <row r="14" spans="1:17" ht="44.25">
+      <c r="R13" t="b">
+        <f>IF(韻母表_4[[#This Row],[台羅拼音]]="", FALSE, ISNUMBER(FIND(RIGHT(韻母表_4[[#This Row],[台羅拼音]],1), "ptkh")))</f>
+        <v>1</v>
+      </c>
+      <c r="S13" s="41" t="str">
+        <f>IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R13=TRUE), "", LEN(韻母表_4[[#This Row],[台羅拼音]]))</f>
+        <v/>
+      </c>
+      <c r="T13" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", $R13=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48?])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v/>
+      </c>
+      <c r="U13" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R13=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v/>
+      </c>
+      <c r="W13" s="41" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" ht="44.25">
       <c r="A14" s="54">
         <v>13</v>
       </c>
@@ -23473,8 +24128,27 @@
       <c r="M14" s="57" t="s">
         <v>1090</v>
       </c>
-    </row>
-    <row r="15" spans="1:17" ht="44.25">
+      <c r="R14" t="b">
+        <f>IF(韻母表_4[[#This Row],[台羅拼音]]="", FALSE, ISNUMBER(FIND(RIGHT(韻母表_4[[#This Row],[台羅拼音]],1), "ptkh")))</f>
+        <v>0</v>
+      </c>
+      <c r="S14" s="41">
+        <f>IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R14=TRUE), "", LEN(韻母表_4[[#This Row],[台羅拼音]]))</f>
+        <v>3</v>
+      </c>
+      <c r="T14" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", $R14=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48?])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v xml:space="preserve">    - xform/ong([48?])/ok$1/    # 公</v>
+      </c>
+      <c r="U14" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R14=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v xml:space="preserve">    - xform/ong([48])/ok$1/    # 公</v>
+      </c>
+      <c r="W14" s="41" t="s">
+        <v>1410</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" ht="44.25">
       <c r="A15" s="54">
         <v>14</v>
       </c>
@@ -23513,8 +24187,27 @@
       <c r="M15" s="57" t="s">
         <v>1092</v>
       </c>
-    </row>
-    <row r="16" spans="1:17" ht="44.25">
+      <c r="R15" t="b">
+        <f>IF(韻母表_4[[#This Row],[台羅拼音]]="", FALSE, ISNUMBER(FIND(RIGHT(韻母表_4[[#This Row],[台羅拼音]],1), "ptkh")))</f>
+        <v>1</v>
+      </c>
+      <c r="S15" s="41" t="str">
+        <f>IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R15=TRUE), "", LEN(韻母表_4[[#This Row],[台羅拼音]]))</f>
+        <v/>
+      </c>
+      <c r="T15" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", $R15=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48?])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v/>
+      </c>
+      <c r="U15" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R15=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v/>
+      </c>
+      <c r="W15" s="41" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" ht="44.25">
       <c r="A16" s="54">
         <v>15</v>
       </c>
@@ -23553,8 +24246,27 @@
       <c r="M16" s="57" t="s">
         <v>1094</v>
       </c>
-    </row>
-    <row r="17" spans="1:13" ht="44.25">
+      <c r="R16" t="b">
+        <f>IF(韻母表_4[[#This Row],[台羅拼音]]="", FALSE, ISNUMBER(FIND(RIGHT(韻母表_4[[#This Row],[台羅拼音]],1), "ptkh")))</f>
+        <v>0</v>
+      </c>
+      <c r="S16" s="41">
+        <f>IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R16=TRUE), "", LEN(韻母表_4[[#This Row],[台羅拼音]]))</f>
+        <v>3</v>
+      </c>
+      <c r="T16" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", $R16=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48?])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v xml:space="preserve">    - xform/uai([48?])/uaih$1/    # 乖</v>
+      </c>
+      <c r="U16" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R16=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v xml:space="preserve">    - xform/uai([48])/uaih$1/    # 乖</v>
+      </c>
+      <c r="W16" s="41" t="s">
+        <v>1411</v>
+      </c>
+    </row>
+    <row r="17" spans="1:23" ht="44.25">
       <c r="A17" s="54">
         <v>16</v>
       </c>
@@ -23593,8 +24305,27 @@
       <c r="M17" s="57" t="s">
         <v>1098</v>
       </c>
-    </row>
-    <row r="18" spans="1:13" ht="44.25">
+      <c r="R17" t="b">
+        <f>IF(韻母表_4[[#This Row],[台羅拼音]]="", FALSE, ISNUMBER(FIND(RIGHT(韻母表_4[[#This Row],[台羅拼音]],1), "ptkh")))</f>
+        <v>1</v>
+      </c>
+      <c r="S17" s="41" t="str">
+        <f>IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R17=TRUE), "", LEN(韻母表_4[[#This Row],[台羅拼音]]))</f>
+        <v/>
+      </c>
+      <c r="T17" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", $R17=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48?])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v/>
+      </c>
+      <c r="U17" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R17=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v/>
+      </c>
+      <c r="W17" s="41" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="18" spans="1:23" ht="44.25">
       <c r="A18" s="54">
         <v>17</v>
       </c>
@@ -23635,8 +24366,27 @@
       <c r="M18" s="57" t="s">
         <v>1375</v>
       </c>
-    </row>
-    <row r="19" spans="1:13" ht="44.25">
+      <c r="R18" t="b">
+        <f>IF(韻母表_4[[#This Row],[台羅拼音]]="", FALSE, ISNUMBER(FIND(RIGHT(韻母表_4[[#This Row],[台羅拼音]],1), "ptkh")))</f>
+        <v>0</v>
+      </c>
+      <c r="S18" s="41">
+        <f>IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R18=TRUE), "", LEN(韻母表_4[[#This Row],[台羅拼音]]))</f>
+        <v>3</v>
+      </c>
+      <c r="T18" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", $R18=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48?])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v xml:space="preserve">    - xform/ing([48?])/ik$1/    # 經</v>
+      </c>
+      <c r="U18" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R18=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v xml:space="preserve">    - xform/ing([48])/ik$1/    # 經</v>
+      </c>
+      <c r="W18" s="41" t="s">
+        <v>1412</v>
+      </c>
+    </row>
+    <row r="19" spans="1:23" ht="44.25">
       <c r="A19" s="54">
         <v>18</v>
       </c>
@@ -23677,8 +24427,27 @@
       <c r="M19" s="57" t="s">
         <v>1377</v>
       </c>
-    </row>
-    <row r="20" spans="1:13" ht="44.25">
+      <c r="R19" t="b">
+        <f>IF(韻母表_4[[#This Row],[台羅拼音]]="", FALSE, ISNUMBER(FIND(RIGHT(韻母表_4[[#This Row],[台羅拼音]],1), "ptkh")))</f>
+        <v>1</v>
+      </c>
+      <c r="S19" s="41" t="str">
+        <f>IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R19=TRUE), "", LEN(韻母表_4[[#This Row],[台羅拼音]]))</f>
+        <v/>
+      </c>
+      <c r="T19" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", $R19=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48?])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v/>
+      </c>
+      <c r="U19" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R19=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v/>
+      </c>
+      <c r="W19" s="41" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="20" spans="1:23" ht="44.25">
       <c r="A20" s="54">
         <v>19</v>
       </c>
@@ -23717,8 +24486,27 @@
       <c r="M20" s="57" t="s">
         <v>1102</v>
       </c>
-    </row>
-    <row r="21" spans="1:13" ht="44.25">
+      <c r="R20" t="b">
+        <f>IF(韻母表_4[[#This Row],[台羅拼音]]="", FALSE, ISNUMBER(FIND(RIGHT(韻母表_4[[#This Row],[台羅拼音]],1), "ptkh")))</f>
+        <v>0</v>
+      </c>
+      <c r="S20" s="41">
+        <f>IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R20=TRUE), "", LEN(韻母表_4[[#This Row],[台羅拼音]]))</f>
+        <v>3</v>
+      </c>
+      <c r="T20" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", $R20=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48?])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v xml:space="preserve">    - xform/uan([48?])/uat$1/    # 觀</v>
+      </c>
+      <c r="U20" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R20=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v xml:space="preserve">    - xform/uan([48])/uat$1/    # 觀</v>
+      </c>
+      <c r="W20" s="41" t="s">
+        <v>1413</v>
+      </c>
+    </row>
+    <row r="21" spans="1:23" ht="44.25">
       <c r="A21" s="54">
         <v>20</v>
       </c>
@@ -23757,8 +24545,27 @@
       <c r="M21" s="57" t="s">
         <v>1106</v>
       </c>
-    </row>
-    <row r="22" spans="1:13" ht="44.25">
+      <c r="R21" t="b">
+        <f>IF(韻母表_4[[#This Row],[台羅拼音]]="", FALSE, ISNUMBER(FIND(RIGHT(韻母表_4[[#This Row],[台羅拼音]],1), "ptkh")))</f>
+        <v>1</v>
+      </c>
+      <c r="S21" s="41" t="str">
+        <f>IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R21=TRUE), "", LEN(韻母表_4[[#This Row],[台羅拼音]]))</f>
+        <v/>
+      </c>
+      <c r="T21" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", $R21=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48?])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v/>
+      </c>
+      <c r="U21" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R21=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v/>
+      </c>
+      <c r="W21" s="41" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="22" spans="1:23" ht="44.25">
       <c r="A22" s="54">
         <v>21</v>
       </c>
@@ -23799,8 +24606,27 @@
       <c r="M22" s="57" t="s">
         <v>1110</v>
       </c>
-    </row>
-    <row r="23" spans="1:13" ht="44.25">
+      <c r="R22" t="b">
+        <f>IF(韻母表_4[[#This Row],[台羅拼音]]="", FALSE, ISNUMBER(FIND(RIGHT(韻母表_4[[#This Row],[台羅拼音]],1), "ptkh")))</f>
+        <v>0</v>
+      </c>
+      <c r="S22" s="41">
+        <f>IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R22=TRUE), "", LEN(韻母表_4[[#This Row],[台羅拼音]]))</f>
+        <v>2</v>
+      </c>
+      <c r="T22" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", $R22=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48?])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v xml:space="preserve">    - xform/oo([48?])/ooh$1/    # 沽</v>
+      </c>
+      <c r="U22" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R22=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v xml:space="preserve">    - xform/oo([48])/ooh$1/    # 沽</v>
+      </c>
+      <c r="W22" s="41" t="s">
+        <v>1414</v>
+      </c>
+    </row>
+    <row r="23" spans="1:23" ht="44.25">
       <c r="A23" s="54">
         <v>22</v>
       </c>
@@ -23845,8 +24671,27 @@
         <f xml:space="preserve"> _xlfn.CONCAT(M22, "ㄏ")</f>
         <v>ㄛㄏ</v>
       </c>
-    </row>
-    <row r="24" spans="1:13" ht="44.25">
+      <c r="R23" t="b">
+        <f>IF(韻母表_4[[#This Row],[台羅拼音]]="", FALSE, ISNUMBER(FIND(RIGHT(韻母表_4[[#This Row],[台羅拼音]],1), "ptkh")))</f>
+        <v>1</v>
+      </c>
+      <c r="S23" s="41" t="str">
+        <f>IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R23=TRUE), "", LEN(韻母表_4[[#This Row],[台羅拼音]]))</f>
+        <v/>
+      </c>
+      <c r="T23" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", $R23=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48?])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v/>
+      </c>
+      <c r="U23" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R23=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v/>
+      </c>
+      <c r="W23" s="41" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="24" spans="1:23" ht="44.25">
       <c r="A24" s="54">
         <v>23</v>
       </c>
@@ -23885,8 +24730,27 @@
       <c r="M24" s="57" t="s">
         <v>1112</v>
       </c>
-    </row>
-    <row r="25" spans="1:13" ht="44.25">
+      <c r="R24" t="b">
+        <f>IF(韻母表_4[[#This Row],[台羅拼音]]="", FALSE, ISNUMBER(FIND(RIGHT(韻母表_4[[#This Row],[台羅拼音]],1), "ptkh")))</f>
+        <v>0</v>
+      </c>
+      <c r="S24" s="41">
+        <f>IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R24=TRUE), "", LEN(韻母表_4[[#This Row],[台羅拼音]]))</f>
+        <v>3</v>
+      </c>
+      <c r="T24" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", $R24=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48?])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v xml:space="preserve">    - xform/iau([48?])/iauh$1/    # 嬌</v>
+      </c>
+      <c r="U24" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R24=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v xml:space="preserve">    - xform/iau([48])/iauh$1/    # 嬌</v>
+      </c>
+      <c r="W24" s="41" t="s">
+        <v>1415</v>
+      </c>
+    </row>
+    <row r="25" spans="1:23" ht="44.25">
       <c r="A25" s="54">
         <v>24</v>
       </c>
@@ -23925,8 +24789,27 @@
       <c r="M25" s="57" t="s">
         <v>1115</v>
       </c>
-    </row>
-    <row r="26" spans="1:13" ht="44.25">
+      <c r="R25" t="b">
+        <f>IF(韻母表_4[[#This Row],[台羅拼音]]="", FALSE, ISNUMBER(FIND(RIGHT(韻母表_4[[#This Row],[台羅拼音]],1), "ptkh")))</f>
+        <v>1</v>
+      </c>
+      <c r="S25" s="41" t="str">
+        <f>IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R25=TRUE), "", LEN(韻母表_4[[#This Row],[台羅拼音]]))</f>
+        <v/>
+      </c>
+      <c r="T25" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", $R25=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48?])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v/>
+      </c>
+      <c r="U25" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R25=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v/>
+      </c>
+      <c r="W25" s="41" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="26" spans="1:23" ht="44.25">
       <c r="A26" s="54">
         <v>25</v>
       </c>
@@ -23967,8 +24850,27 @@
       <c r="M26" s="57" t="s">
         <v>1081</v>
       </c>
-    </row>
-    <row r="27" spans="1:13" ht="44.25">
+      <c r="R26" t="b">
+        <f>IF(韻母表_4[[#This Row],[台羅拼音]]="", FALSE, ISNUMBER(FIND(RIGHT(韻母表_4[[#This Row],[台羅拼音]],1), "ptkh")))</f>
+        <v>0</v>
+      </c>
+      <c r="S26" s="41">
+        <f>IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R26=TRUE), "", LEN(韻母表_4[[#This Row],[台羅拼音]]))</f>
+        <v>1</v>
+      </c>
+      <c r="T26" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", $R26=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48?])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v xml:space="preserve">    - xform/e([48?])/$1/    # 稽</v>
+      </c>
+      <c r="U26" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R26=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v xml:space="preserve">    - xform/e([48])/$1/    # 稽</v>
+      </c>
+      <c r="W26" s="41" t="s">
+        <v>1416</v>
+      </c>
+    </row>
+    <row r="27" spans="1:23" ht="44.25">
       <c r="A27" s="54">
         <v>26</v>
       </c>
@@ -24003,8 +24905,27 @@
       <c r="M27" s="57" t="s">
         <v>1079</v>
       </c>
-    </row>
-    <row r="28" spans="1:13" ht="44.25">
+      <c r="R27" t="b">
+        <f>IF(韻母表_4[[#This Row],[台羅拼音]]="", FALSE, ISNUMBER(FIND(RIGHT(韻母表_4[[#This Row],[台羅拼音]],1), "ptkh")))</f>
+        <v>0</v>
+      </c>
+      <c r="S27" s="41" t="str">
+        <f>IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R27=TRUE), "", LEN(韻母表_4[[#This Row],[台羅拼音]]))</f>
+        <v/>
+      </c>
+      <c r="T27" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", $R27=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48?])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v/>
+      </c>
+      <c r="U27" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R27=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v/>
+      </c>
+      <c r="W27" s="41" t="s">
+        <v>1417</v>
+      </c>
+    </row>
+    <row r="28" spans="1:23" ht="44.25">
       <c r="A28" s="54">
         <v>27</v>
       </c>
@@ -24043,8 +24964,27 @@
       <c r="M28" s="57" t="s">
         <v>1119</v>
       </c>
-    </row>
-    <row r="29" spans="1:13" ht="44.25">
+      <c r="R28" t="b">
+        <f>IF(韻母表_4[[#This Row],[台羅拼音]]="", FALSE, ISNUMBER(FIND(RIGHT(韻母表_4[[#This Row],[台羅拼音]],1), "ptkh")))</f>
+        <v>0</v>
+      </c>
+      <c r="S28" s="41">
+        <f>IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R28=TRUE), "", LEN(韻母表_4[[#This Row],[台羅拼音]]))</f>
+        <v>4</v>
+      </c>
+      <c r="T28" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", $R28=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48?])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v xml:space="preserve">    - xform/iong([48?])/iok$1/    # 恭</v>
+      </c>
+      <c r="U28" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R28=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v xml:space="preserve">    - xform/iong([48])/iok$1/    # 恭</v>
+      </c>
+      <c r="W28" s="41" t="s">
+        <v>1418</v>
+      </c>
+    </row>
+    <row r="29" spans="1:23" ht="44.25">
       <c r="A29" s="54">
         <v>28</v>
       </c>
@@ -24083,8 +25023,27 @@
       <c r="M29" s="57" t="s">
         <v>1122</v>
       </c>
-    </row>
-    <row r="30" spans="1:13" ht="44.25">
+      <c r="R29" t="b">
+        <f>IF(韻母表_4[[#This Row],[台羅拼音]]="", FALSE, ISNUMBER(FIND(RIGHT(韻母表_4[[#This Row],[台羅拼音]],1), "ptkh")))</f>
+        <v>1</v>
+      </c>
+      <c r="S29" s="41" t="str">
+        <f>IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R29=TRUE), "", LEN(韻母表_4[[#This Row],[台羅拼音]]))</f>
+        <v/>
+      </c>
+      <c r="T29" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", $R29=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48?])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v/>
+      </c>
+      <c r="U29" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R29=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v/>
+      </c>
+      <c r="W29" s="41" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="30" spans="1:23" ht="44.25">
       <c r="A30" s="54">
         <v>29</v>
       </c>
@@ -24123,8 +25082,27 @@
       <c r="M30" s="57" t="s">
         <v>1125</v>
       </c>
-    </row>
-    <row r="31" spans="1:13" ht="44.25">
+      <c r="R30" t="b">
+        <f>IF(韻母表_4[[#This Row],[台羅拼音]]="", FALSE, ISNUMBER(FIND(RIGHT(韻母表_4[[#This Row],[台羅拼音]],1), "ptkh")))</f>
+        <v>0</v>
+      </c>
+      <c r="S30" s="41">
+        <f>IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R30=TRUE), "", LEN(韻母表_4[[#This Row],[台羅拼音]]))</f>
+        <v>1</v>
+      </c>
+      <c r="T30" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", $R30=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48?])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v xml:space="preserve">    - xform/o([48?])/oh$1/    # 高</v>
+      </c>
+      <c r="U30" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R30=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v xml:space="preserve">    - xform/o([48])/oh$1/    # 高</v>
+      </c>
+      <c r="W30" s="41" t="s">
+        <v>1419</v>
+      </c>
+    </row>
+    <row r="31" spans="1:23" ht="44.25">
       <c r="A31" s="54">
         <v>30</v>
       </c>
@@ -24163,8 +25141,27 @@
       <c r="M31" s="57" t="s">
         <v>1129</v>
       </c>
-    </row>
-    <row r="32" spans="1:13" ht="44.25">
+      <c r="R31" t="b">
+        <f>IF(韻母表_4[[#This Row],[台羅拼音]]="", FALSE, ISNUMBER(FIND(RIGHT(韻母表_4[[#This Row],[台羅拼音]],1), "ptkh")))</f>
+        <v>1</v>
+      </c>
+      <c r="S31" s="41" t="str">
+        <f>IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R31=TRUE), "", LEN(韻母表_4[[#This Row],[台羅拼音]]))</f>
+        <v/>
+      </c>
+      <c r="T31" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", $R31=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48?])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v/>
+      </c>
+      <c r="U31" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R31=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v/>
+      </c>
+      <c r="W31" s="41" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="32" spans="1:23" ht="44.25">
       <c r="A32" s="54">
         <v>31</v>
       </c>
@@ -24203,8 +25200,27 @@
       <c r="M32" s="57" t="s">
         <v>1130</v>
       </c>
-    </row>
-    <row r="33" spans="1:13" ht="44.25">
+      <c r="R32" t="b">
+        <f>IF(韻母表_4[[#This Row],[台羅拼音]]="", FALSE, ISNUMBER(FIND(RIGHT(韻母表_4[[#This Row],[台羅拼音]],1), "ptkh")))</f>
+        <v>0</v>
+      </c>
+      <c r="S32" s="41">
+        <f>IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R32=TRUE), "", LEN(韻母表_4[[#This Row],[台羅拼音]]))</f>
+        <v>2</v>
+      </c>
+      <c r="T32" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", $R32=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48?])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v xml:space="preserve">    - xform/ai([48?])/$1/    # 皆</v>
+      </c>
+      <c r="U32" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R32=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v xml:space="preserve">    - xform/ai([48])/$1/    # 皆</v>
+      </c>
+      <c r="W32" s="41" t="s">
+        <v>1420</v>
+      </c>
+    </row>
+    <row r="33" spans="1:23" ht="44.25">
       <c r="A33" s="54">
         <v>32</v>
       </c>
@@ -24223,8 +25239,27 @@
       <c r="K33" s="57"/>
       <c r="L33" s="57"/>
       <c r="M33" s="57"/>
-    </row>
-    <row r="34" spans="1:13" ht="44.25">
+      <c r="R33" t="b">
+        <f>IF(韻母表_4[[#This Row],[台羅拼音]]="", FALSE, ISNUMBER(FIND(RIGHT(韻母表_4[[#This Row],[台羅拼音]],1), "ptkh")))</f>
+        <v>0</v>
+      </c>
+      <c r="S33" s="41" t="str">
+        <f>IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R33=TRUE), "", LEN(韻母表_4[[#This Row],[台羅拼音]]))</f>
+        <v/>
+      </c>
+      <c r="T33" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", $R33=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48?])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v/>
+      </c>
+      <c r="U33" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R33=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v/>
+      </c>
+      <c r="W33" s="41" t="s">
+        <v>1421</v>
+      </c>
+    </row>
+    <row r="34" spans="1:23" ht="44.25">
       <c r="A34" s="54">
         <v>33</v>
       </c>
@@ -24263,8 +25298,27 @@
       <c r="M34" s="57" t="s">
         <v>1131</v>
       </c>
-    </row>
-    <row r="35" spans="1:13" ht="44.25">
+      <c r="R34" t="b">
+        <f>IF(韻母表_4[[#This Row],[台羅拼音]]="", FALSE, ISNUMBER(FIND(RIGHT(韻母表_4[[#This Row],[台羅拼音]],1), "ptkh")))</f>
+        <v>0</v>
+      </c>
+      <c r="S34" s="41">
+        <f>IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R34=TRUE), "", LEN(韻母表_4[[#This Row],[台羅拼音]]))</f>
+        <v>2</v>
+      </c>
+      <c r="T34" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", $R34=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48?])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v xml:space="preserve">    - xform/in([48?])/it$1/    # 巾</v>
+      </c>
+      <c r="U34" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R34=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v xml:space="preserve">    - xform/in([48])/it$1/    # 巾</v>
+      </c>
+      <c r="W34" s="41" t="s">
+        <v>1422</v>
+      </c>
+    </row>
+    <row r="35" spans="1:23" ht="44.25">
       <c r="A35" s="54">
         <v>34</v>
       </c>
@@ -24303,8 +25357,27 @@
       <c r="M35" s="57" t="s">
         <v>1134</v>
       </c>
-    </row>
-    <row r="36" spans="1:13" ht="44.25">
+      <c r="R35" t="b">
+        <f>IF(韻母表_4[[#This Row],[台羅拼音]]="", FALSE, ISNUMBER(FIND(RIGHT(韻母表_4[[#This Row],[台羅拼音]],1), "ptkh")))</f>
+        <v>1</v>
+      </c>
+      <c r="S35" s="41" t="str">
+        <f>IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R35=TRUE), "", LEN(韻母表_4[[#This Row],[台羅拼音]]))</f>
+        <v/>
+      </c>
+      <c r="T35" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", $R35=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48?])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v/>
+      </c>
+      <c r="U35" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R35=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v/>
+      </c>
+      <c r="W35" s="41" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="36" spans="1:23" ht="44.25">
       <c r="A36" s="54">
         <v>35</v>
       </c>
@@ -24343,8 +25416,27 @@
       <c r="M36" s="57" t="s">
         <v>1135</v>
       </c>
-    </row>
-    <row r="37" spans="1:13" ht="44.25">
+      <c r="R36" t="b">
+        <f>IF(韻母表_4[[#This Row],[台羅拼音]]="", FALSE, ISNUMBER(FIND(RIGHT(韻母表_4[[#This Row],[台羅拼音]],1), "ptkh")))</f>
+        <v>0</v>
+      </c>
+      <c r="S36" s="41">
+        <f>IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R36=TRUE), "", LEN(韻母表_4[[#This Row],[台羅拼音]]))</f>
+        <v>4</v>
+      </c>
+      <c r="T36" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", $R36=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48?])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v xml:space="preserve">    - xform/iang([48?])/iak$1/    # 姜</v>
+      </c>
+      <c r="U36" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R36=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v xml:space="preserve">    - xform/iang([48])/iak$1/    # 姜</v>
+      </c>
+      <c r="W36" s="41" t="s">
+        <v>1423</v>
+      </c>
+    </row>
+    <row r="37" spans="1:23" ht="44.25">
       <c r="A37" s="54">
         <v>36</v>
       </c>
@@ -24383,8 +25475,27 @@
       <c r="M37" s="57" t="s">
         <v>1137</v>
       </c>
-    </row>
-    <row r="38" spans="1:13" ht="44.25">
+      <c r="R37" t="b">
+        <f>IF(韻母表_4[[#This Row],[台羅拼音]]="", FALSE, ISNUMBER(FIND(RIGHT(韻母表_4[[#This Row],[台羅拼音]],1), "ptkh")))</f>
+        <v>1</v>
+      </c>
+      <c r="S37" s="41" t="str">
+        <f>IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R37=TRUE), "", LEN(韻母表_4[[#This Row],[台羅拼音]]))</f>
+        <v/>
+      </c>
+      <c r="T37" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", $R37=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48?])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v/>
+      </c>
+      <c r="U37" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R37=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v/>
+      </c>
+      <c r="W37" s="41" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="38" spans="1:23" ht="44.25">
       <c r="A38" s="54">
         <v>37</v>
       </c>
@@ -24423,8 +25534,27 @@
       <c r="M38" s="57" t="s">
         <v>1139</v>
       </c>
-    </row>
-    <row r="39" spans="1:13" ht="44.25">
+      <c r="R38" t="b">
+        <f>IF(韻母表_4[[#This Row],[台羅拼音]]="", FALSE, ISNUMBER(FIND(RIGHT(韻母表_4[[#This Row],[台羅拼音]],1), "ptkh")))</f>
+        <v>0</v>
+      </c>
+      <c r="S38" s="41">
+        <f>IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R38=TRUE), "", LEN(韻母表_4[[#This Row],[台羅拼音]]))</f>
+        <v>2</v>
+      </c>
+      <c r="T38" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", $R38=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48?])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v xml:space="preserve">    - xform/am([48?])/ap$1/    # 甘</v>
+      </c>
+      <c r="U38" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R38=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v xml:space="preserve">    - xform/am([48])/ap$1/    # 甘</v>
+      </c>
+      <c r="W38" s="41" t="s">
+        <v>1424</v>
+      </c>
+    </row>
+    <row r="39" spans="1:23" ht="44.25">
       <c r="A39" s="54">
         <v>38</v>
       </c>
@@ -24463,8 +25593,27 @@
       <c r="M39" s="57" t="s">
         <v>1142</v>
       </c>
-    </row>
-    <row r="40" spans="1:13" ht="44.25">
+      <c r="R39" t="b">
+        <f>IF(韻母表_4[[#This Row],[台羅拼音]]="", FALSE, ISNUMBER(FIND(RIGHT(韻母表_4[[#This Row],[台羅拼音]],1), "ptkh")))</f>
+        <v>1</v>
+      </c>
+      <c r="S39" s="41" t="str">
+        <f>IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R39=TRUE), "", LEN(韻母表_4[[#This Row],[台羅拼音]]))</f>
+        <v/>
+      </c>
+      <c r="T39" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", $R39=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48?])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v/>
+      </c>
+      <c r="U39" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R39=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v/>
+      </c>
+      <c r="W39" s="41" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="40" spans="1:23" ht="44.25">
       <c r="A40" s="54">
         <v>39</v>
       </c>
@@ -24503,8 +25652,27 @@
       <c r="M40" s="57" t="s">
         <v>1144</v>
       </c>
-    </row>
-    <row r="41" spans="1:13" ht="44.25">
+      <c r="R40" t="b">
+        <f>IF(韻母表_4[[#This Row],[台羅拼音]]="", FALSE, ISNUMBER(FIND(RIGHT(韻母表_4[[#This Row],[台羅拼音]],1), "ptkh")))</f>
+        <v>0</v>
+      </c>
+      <c r="S40" s="41">
+        <f>IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R40=TRUE), "", LEN(韻母表_4[[#This Row],[台羅拼音]]))</f>
+        <v>2</v>
+      </c>
+      <c r="T40" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", $R40=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48?])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v xml:space="preserve">    - xform/ua([48?])/uah$1/    # 瓜</v>
+      </c>
+      <c r="U40" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R40=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v xml:space="preserve">    - xform/ua([48])/uah$1/    # 瓜</v>
+      </c>
+      <c r="W40" s="41" t="s">
+        <v>1425</v>
+      </c>
+    </row>
+    <row r="41" spans="1:23" ht="44.25">
       <c r="A41" s="54">
         <v>40</v>
       </c>
@@ -24543,8 +25711,27 @@
       <c r="M41" s="57" t="s">
         <v>1148</v>
       </c>
-    </row>
-    <row r="42" spans="1:13" ht="44.25">
+      <c r="R41" t="b">
+        <f>IF(韻母表_4[[#This Row],[台羅拼音]]="", FALSE, ISNUMBER(FIND(RIGHT(韻母表_4[[#This Row],[台羅拼音]],1), "ptkh")))</f>
+        <v>1</v>
+      </c>
+      <c r="S41" s="41" t="str">
+        <f>IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R41=TRUE), "", LEN(韻母表_4[[#This Row],[台羅拼音]]))</f>
+        <v/>
+      </c>
+      <c r="T41" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", $R41=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48?])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v/>
+      </c>
+      <c r="U41" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R41=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v/>
+      </c>
+      <c r="W41" s="41" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="42" spans="1:23" ht="44.25">
       <c r="A42" s="54">
         <v>41</v>
       </c>
@@ -24583,8 +25770,27 @@
       <c r="M42" s="57" t="s">
         <v>1149</v>
       </c>
-    </row>
-    <row r="43" spans="1:13" ht="44.25">
+      <c r="R42" t="b">
+        <f>IF(韻母表_4[[#This Row],[台羅拼音]]="", FALSE, ISNUMBER(FIND(RIGHT(韻母表_4[[#This Row],[台羅拼音]],1), "ptkh")))</f>
+        <v>0</v>
+      </c>
+      <c r="S42" s="41">
+        <f>IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R42=TRUE), "", LEN(韻母表_4[[#This Row],[台羅拼音]]))</f>
+        <v>3</v>
+      </c>
+      <c r="T42" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", $R42=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48?])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v xml:space="preserve">    - xform/ang([48?])/ak$1/    # 江</v>
+      </c>
+      <c r="U42" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R42=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v xml:space="preserve">    - xform/ang([48])/ak$1/    # 江</v>
+      </c>
+      <c r="W42" s="41" t="s">
+        <v>1426</v>
+      </c>
+    </row>
+    <row r="43" spans="1:23" ht="44.25">
       <c r="A43" s="54">
         <v>42</v>
       </c>
@@ -24623,8 +25829,27 @@
       <c r="M43" s="57" t="s">
         <v>1152</v>
       </c>
-    </row>
-    <row r="44" spans="1:13" ht="44.25">
+      <c r="R43" t="b">
+        <f>IF(韻母表_4[[#This Row],[台羅拼音]]="", FALSE, ISNUMBER(FIND(RIGHT(韻母表_4[[#This Row],[台羅拼音]],1), "ptkh")))</f>
+        <v>1</v>
+      </c>
+      <c r="S43" s="41" t="str">
+        <f>IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R43=TRUE), "", LEN(韻母表_4[[#This Row],[台羅拼音]]))</f>
+        <v/>
+      </c>
+      <c r="T43" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", $R43=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48?])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v/>
+      </c>
+      <c r="U43" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R43=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v/>
+      </c>
+      <c r="W43" s="41" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="44" spans="1:23" ht="44.25">
       <c r="A44" s="54">
         <v>43</v>
       </c>
@@ -24663,8 +25888,27 @@
       <c r="M44" s="57" t="s">
         <v>1154</v>
       </c>
-    </row>
-    <row r="45" spans="1:13" ht="44.25">
+      <c r="R44" t="b">
+        <f>IF(韻母表_4[[#This Row],[台羅拼音]]="", FALSE, ISNUMBER(FIND(RIGHT(韻母表_4[[#This Row],[台羅拼音]],1), "ptkh")))</f>
+        <v>0</v>
+      </c>
+      <c r="S44" s="41">
+        <f>IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R44=TRUE), "", LEN(韻母表_4[[#This Row],[台羅拼音]]))</f>
+        <v>3</v>
+      </c>
+      <c r="T44" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", $R44=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48?])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v xml:space="preserve">    - xform/iam([48?])/iap$1/    # 兼</v>
+      </c>
+      <c r="U44" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R44=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v xml:space="preserve">    - xform/iam([48])/iap$1/    # 兼</v>
+      </c>
+      <c r="W44" s="41" t="s">
+        <v>1427</v>
+      </c>
+    </row>
+    <row r="45" spans="1:23" ht="44.25">
       <c r="A45" s="54">
         <v>44</v>
       </c>
@@ -24703,8 +25947,27 @@
       <c r="M45" s="57" t="s">
         <v>1156</v>
       </c>
-    </row>
-    <row r="46" spans="1:13" ht="44.25">
+      <c r="R45" t="b">
+        <f>IF(韻母表_4[[#This Row],[台羅拼音]]="", FALSE, ISNUMBER(FIND(RIGHT(韻母表_4[[#This Row],[台羅拼音]],1), "ptkh")))</f>
+        <v>1</v>
+      </c>
+      <c r="S45" s="41" t="str">
+        <f>IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R45=TRUE), "", LEN(韻母表_4[[#This Row],[台羅拼音]]))</f>
+        <v/>
+      </c>
+      <c r="T45" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", $R45=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48?])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v/>
+      </c>
+      <c r="U45" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R45=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v/>
+      </c>
+      <c r="W45" s="41" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="46" spans="1:23" ht="44.25">
       <c r="A46" s="54">
         <v>45</v>
       </c>
@@ -24743,8 +26006,27 @@
       <c r="M46" s="57" t="s">
         <v>1158</v>
       </c>
-    </row>
-    <row r="47" spans="1:13" ht="44.25">
+      <c r="R46" t="b">
+        <f>IF(韻母表_4[[#This Row],[台羅拼音]]="", FALSE, ISNUMBER(FIND(RIGHT(韻母表_4[[#This Row],[台羅拼音]],1), "ptkh")))</f>
+        <v>0</v>
+      </c>
+      <c r="S46" s="41">
+        <f>IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R46=TRUE), "", LEN(韻母表_4[[#This Row],[台羅拼音]]))</f>
+        <v>2</v>
+      </c>
+      <c r="T46" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", $R46=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48?])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v xml:space="preserve">    - xform/au([48?])/auh$1/    # 交</v>
+      </c>
+      <c r="U46" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R46=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v xml:space="preserve">    - xform/au([48])/auh$1/    # 交</v>
+      </c>
+      <c r="W46" s="41" t="s">
+        <v>1428</v>
+      </c>
+    </row>
+    <row r="47" spans="1:23" ht="44.25">
       <c r="A47" s="54">
         <v>46</v>
       </c>
@@ -24783,8 +26065,27 @@
       <c r="M47" s="57" t="s">
         <v>1162</v>
       </c>
-    </row>
-    <row r="48" spans="1:13" ht="44.25">
+      <c r="R47" t="b">
+        <f>IF(韻母表_4[[#This Row],[台羅拼音]]="", FALSE, ISNUMBER(FIND(RIGHT(韻母表_4[[#This Row],[台羅拼音]],1), "ptkh")))</f>
+        <v>1</v>
+      </c>
+      <c r="S47" s="41" t="str">
+        <f>IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R47=TRUE), "", LEN(韻母表_4[[#This Row],[台羅拼音]]))</f>
+        <v/>
+      </c>
+      <c r="T47" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", $R47=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48?])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v/>
+      </c>
+      <c r="U47" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R47=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v/>
+      </c>
+      <c r="W47" s="41" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="48" spans="1:23" ht="44.25">
       <c r="A48" s="54">
         <v>47</v>
       </c>
@@ -24823,8 +26124,27 @@
       <c r="M48" s="57" t="s">
         <v>1163</v>
       </c>
-    </row>
-    <row r="49" spans="1:13" ht="44.25">
+      <c r="R48" t="b">
+        <f>IF(韻母表_4[[#This Row],[台羅拼音]]="", FALSE, ISNUMBER(FIND(RIGHT(韻母表_4[[#This Row],[台羅拼音]],1), "ptkh")))</f>
+        <v>0</v>
+      </c>
+      <c r="S48" s="41">
+        <f>IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R48=TRUE), "", LEN(韻母表_4[[#This Row],[台羅拼音]]))</f>
+        <v>2</v>
+      </c>
+      <c r="T48" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", $R48=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48?])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v xml:space="preserve">    - xform/ia([48?])/iah$1/    # 迦</v>
+      </c>
+      <c r="U48" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R48=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v xml:space="preserve">    - xform/ia([48])/iah$1/    # 迦</v>
+      </c>
+      <c r="W48" s="41" t="s">
+        <v>1429</v>
+      </c>
+    </row>
+    <row r="49" spans="1:23" ht="44.25">
       <c r="A49" s="54">
         <v>48</v>
       </c>
@@ -24863,8 +26183,27 @@
       <c r="M49" s="57" t="s">
         <v>1165</v>
       </c>
-    </row>
-    <row r="50" spans="1:13" ht="44.25">
+      <c r="R49" t="b">
+        <f>IF(韻母表_4[[#This Row],[台羅拼音]]="", FALSE, ISNUMBER(FIND(RIGHT(韻母表_4[[#This Row],[台羅拼音]],1), "ptkh")))</f>
+        <v>1</v>
+      </c>
+      <c r="S49" s="41" t="str">
+        <f>IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R49=TRUE), "", LEN(韻母表_4[[#This Row],[台羅拼音]]))</f>
+        <v/>
+      </c>
+      <c r="T49" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", $R49=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48?])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v/>
+      </c>
+      <c r="U49" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R49=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v/>
+      </c>
+      <c r="W49" s="41" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="50" spans="1:23" ht="44.25">
       <c r="A50" s="54">
         <v>49</v>
       </c>
@@ -24905,8 +26244,27 @@
       <c r="M50" s="57" t="s">
         <v>1168</v>
       </c>
-    </row>
-    <row r="51" spans="1:13" ht="44.25">
+      <c r="R50" t="b">
+        <f>IF(韻母表_4[[#This Row],[台羅拼音]]="", FALSE, ISNUMBER(FIND(RIGHT(韻母表_4[[#This Row],[台羅拼音]],1), "ptkh")))</f>
+        <v>0</v>
+      </c>
+      <c r="S50" s="41">
+        <f>IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R50=TRUE), "", LEN(韻母表_4[[#This Row],[台羅拼音]]))</f>
+        <v>2</v>
+      </c>
+      <c r="T50" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", $R50=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48?])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v xml:space="preserve">    - xform/ue([48?])/ueh$1/    # 檜</v>
+      </c>
+      <c r="U50" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R50=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v xml:space="preserve">    - xform/ue([48])/ueh$1/    # 檜</v>
+      </c>
+      <c r="W50" s="41" t="s">
+        <v>1430</v>
+      </c>
+    </row>
+    <row r="51" spans="1:23" ht="44.25">
       <c r="A51" s="54">
         <v>50</v>
       </c>
@@ -24947,8 +26305,27 @@
       <c r="M51" s="57" t="s">
         <v>1171</v>
       </c>
-    </row>
-    <row r="52" spans="1:13" ht="44.25">
+      <c r="R51" t="b">
+        <f>IF(韻母表_4[[#This Row],[台羅拼音]]="", FALSE, ISNUMBER(FIND(RIGHT(韻母表_4[[#This Row],[台羅拼音]],1), "ptkh")))</f>
+        <v>1</v>
+      </c>
+      <c r="S51" s="41" t="str">
+        <f>IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R51=TRUE), "", LEN(韻母表_4[[#This Row],[台羅拼音]]))</f>
+        <v/>
+      </c>
+      <c r="T51" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", $R51=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48?])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v/>
+      </c>
+      <c r="U51" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R51=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v/>
+      </c>
+      <c r="W51" s="41" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="52" spans="1:23" ht="44.25">
       <c r="A52" s="54">
         <v>51</v>
       </c>
@@ -24987,8 +26364,27 @@
       <c r="M52" s="57" t="s">
         <v>1175</v>
       </c>
-    </row>
-    <row r="53" spans="1:13" ht="44.25">
+      <c r="R52" t="b">
+        <f>IF(韻母表_4[[#This Row],[台羅拼音]]="", FALSE, ISNUMBER(FIND(RIGHT(韻母表_4[[#This Row],[台羅拼音]],1), "ptkh")))</f>
+        <v>0</v>
+      </c>
+      <c r="S52" s="41">
+        <f>IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R52=TRUE), "", LEN(韻母表_4[[#This Row],[台羅拼音]]))</f>
+        <v>3</v>
+      </c>
+      <c r="T52" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", $R52=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48?])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v xml:space="preserve">    - xform/ann([48?])/annh$1/    # 監</v>
+      </c>
+      <c r="U52" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R52=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v xml:space="preserve">    - xform/ann([48])/annh$1/    # 監</v>
+      </c>
+      <c r="W52" s="41" t="s">
+        <v>1431</v>
+      </c>
+    </row>
+    <row r="53" spans="1:23" ht="44.25">
       <c r="A53" s="54">
         <v>52</v>
       </c>
@@ -25027,8 +26423,27 @@
       <c r="M53" s="57" t="s">
         <v>1179</v>
       </c>
-    </row>
-    <row r="54" spans="1:13" ht="44.25">
+      <c r="R53" t="b">
+        <f>IF(韻母表_4[[#This Row],[台羅拼音]]="", FALSE, ISNUMBER(FIND(RIGHT(韻母表_4[[#This Row],[台羅拼音]],1), "ptkh")))</f>
+        <v>1</v>
+      </c>
+      <c r="S53" s="41" t="str">
+        <f>IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R53=TRUE), "", LEN(韻母表_4[[#This Row],[台羅拼音]]))</f>
+        <v/>
+      </c>
+      <c r="T53" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", $R53=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48?])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v/>
+      </c>
+      <c r="U53" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R53=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v/>
+      </c>
+      <c r="W53" s="41" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="54" spans="1:23" ht="44.25">
       <c r="A54" s="54">
         <v>53</v>
       </c>
@@ -25067,8 +26482,27 @@
       <c r="M54" s="57" t="s">
         <v>1180</v>
       </c>
-    </row>
-    <row r="55" spans="1:13" ht="44.25">
+      <c r="R54" t="b">
+        <f>IF(韻母表_4[[#This Row],[台羅拼音]]="", FALSE, ISNUMBER(FIND(RIGHT(韻母表_4[[#This Row],[台羅拼音]],1), "ptkh")))</f>
+        <v>0</v>
+      </c>
+      <c r="S54" s="41">
+        <f>IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R54=TRUE), "", LEN(韻母表_4[[#This Row],[台羅拼音]]))</f>
+        <v>1</v>
+      </c>
+      <c r="T54" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", $R54=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48?])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v xml:space="preserve">    - xform/u([48?])/uh$1/    # 艍</v>
+      </c>
+      <c r="U54" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R54=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v xml:space="preserve">    - xform/u([48])/uh$1/    # 艍</v>
+      </c>
+      <c r="W54" s="41" t="s">
+        <v>1432</v>
+      </c>
+    </row>
+    <row r="55" spans="1:23" ht="44.25">
       <c r="A55" s="54">
         <v>54</v>
       </c>
@@ -25107,8 +26541,27 @@
       <c r="M55" s="57" t="s">
         <v>1183</v>
       </c>
-    </row>
-    <row r="56" spans="1:13" ht="44.25">
+      <c r="R55" t="b">
+        <f>IF(韻母表_4[[#This Row],[台羅拼音]]="", FALSE, ISNUMBER(FIND(RIGHT(韻母表_4[[#This Row],[台羅拼音]],1), "ptkh")))</f>
+        <v>1</v>
+      </c>
+      <c r="S55" s="41" t="str">
+        <f>IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R55=TRUE), "", LEN(韻母表_4[[#This Row],[台羅拼音]]))</f>
+        <v/>
+      </c>
+      <c r="T55" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", $R55=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48?])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v/>
+      </c>
+      <c r="U55" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R55=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v/>
+      </c>
+      <c r="W55" s="41" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="56" spans="1:23" ht="44.25">
       <c r="A56" s="54">
         <v>55</v>
       </c>
@@ -25147,8 +26600,27 @@
       <c r="M56" s="57" t="s">
         <v>1184</v>
       </c>
-    </row>
-    <row r="57" spans="1:13" ht="44.25">
+      <c r="R56" t="b">
+        <f>IF(韻母表_4[[#This Row],[台羅拼音]]="", FALSE, ISNUMBER(FIND(RIGHT(韻母表_4[[#This Row],[台羅拼音]],1), "ptkh")))</f>
+        <v>0</v>
+      </c>
+      <c r="S56" s="41">
+        <f>IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R56=TRUE), "", LEN(韻母表_4[[#This Row],[台羅拼音]]))</f>
+        <v>1</v>
+      </c>
+      <c r="T56" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", $R56=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48?])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v xml:space="preserve">    - xform/a([48?])/ah$1/    # 膠</v>
+      </c>
+      <c r="U56" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R56=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v xml:space="preserve">    - xform/a([48])/ah$1/    # 膠</v>
+      </c>
+      <c r="W56" s="41" t="s">
+        <v>1433</v>
+      </c>
+    </row>
+    <row r="57" spans="1:23" ht="44.25">
       <c r="A57" s="54">
         <v>56</v>
       </c>
@@ -25187,8 +26659,27 @@
       <c r="M57" s="57" t="s">
         <v>1187</v>
       </c>
-    </row>
-    <row r="58" spans="1:13" ht="44.25">
+      <c r="R57" t="b">
+        <f>IF(韻母表_4[[#This Row],[台羅拼音]]="", FALSE, ISNUMBER(FIND(RIGHT(韻母表_4[[#This Row],[台羅拼音]],1), "ptkh")))</f>
+        <v>1</v>
+      </c>
+      <c r="S57" s="41" t="str">
+        <f>IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R57=TRUE), "", LEN(韻母表_4[[#This Row],[台羅拼音]]))</f>
+        <v/>
+      </c>
+      <c r="T57" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", $R57=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48?])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v/>
+      </c>
+      <c r="U57" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R57=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v/>
+      </c>
+      <c r="W57" s="41" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="58" spans="1:23" ht="44.25">
       <c r="A58" s="54">
         <v>57</v>
       </c>
@@ -25227,8 +26718,27 @@
       <c r="M58" s="57" t="s">
         <v>1188</v>
       </c>
-    </row>
-    <row r="59" spans="1:13" ht="44.25">
+      <c r="R58" t="b">
+        <f>IF(韻母表_4[[#This Row],[台羅拼音]]="", FALSE, ISNUMBER(FIND(RIGHT(韻母表_4[[#This Row],[台羅拼音]],1), "ptkh")))</f>
+        <v>0</v>
+      </c>
+      <c r="S58" s="41">
+        <f>IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R58=TRUE), "", LEN(韻母表_4[[#This Row],[台羅拼音]]))</f>
+        <v>1</v>
+      </c>
+      <c r="T58" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", $R58=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48?])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v xml:space="preserve">    - xform/i([48?])/ih$1/    # 居</v>
+      </c>
+      <c r="U58" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R58=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v xml:space="preserve">    - xform/i([48])/ih$1/    # 居</v>
+      </c>
+      <c r="W58" s="41" t="s">
+        <v>1434</v>
+      </c>
+    </row>
+    <row r="59" spans="1:23" ht="44.25">
       <c r="A59" s="54">
         <v>58</v>
       </c>
@@ -25267,8 +26777,27 @@
       <c r="M59" s="57" t="s">
         <v>1191</v>
       </c>
-    </row>
-    <row r="60" spans="1:13" ht="44.25">
+      <c r="R59" t="b">
+        <f>IF(韻母表_4[[#This Row],[台羅拼音]]="", FALSE, ISNUMBER(FIND(RIGHT(韻母表_4[[#This Row],[台羅拼音]],1), "ptkh")))</f>
+        <v>1</v>
+      </c>
+      <c r="S59" s="41" t="str">
+        <f>IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R59=TRUE), "", LEN(韻母表_4[[#This Row],[台羅拼音]]))</f>
+        <v/>
+      </c>
+      <c r="T59" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", $R59=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48?])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v/>
+      </c>
+      <c r="U59" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R59=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v/>
+      </c>
+      <c r="W59" s="41" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="60" spans="1:23" ht="44.25">
       <c r="A60" s="54">
         <v>59</v>
       </c>
@@ -25307,8 +26836,27 @@
       <c r="M60" s="57" t="s">
         <v>1192</v>
       </c>
-    </row>
-    <row r="61" spans="1:13" ht="44.25">
+      <c r="R60" t="b">
+        <f>IF(韻母表_4[[#This Row],[台羅拼音]]="", FALSE, ISNUMBER(FIND(RIGHT(韻母表_4[[#This Row],[台羅拼音]],1), "ptkh")))</f>
+        <v>0</v>
+      </c>
+      <c r="S60" s="41">
+        <f>IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R60=TRUE), "", LEN(韻母表_4[[#This Row],[台羅拼音]]))</f>
+        <v>2</v>
+      </c>
+      <c r="T60" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", $R60=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48?])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v xml:space="preserve">    - xform/iu([48?])/$1/    # 丩</v>
+      </c>
+      <c r="U60" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R60=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v xml:space="preserve">    - xform/iu([48])/$1/    # 丩</v>
+      </c>
+      <c r="W60" s="41" t="s">
+        <v>1435</v>
+      </c>
+    </row>
+    <row r="61" spans="1:23" ht="44.25">
       <c r="A61" s="54">
         <v>60</v>
       </c>
@@ -25343,8 +26891,27 @@
       <c r="M61" s="57" t="s">
         <v>1079</v>
       </c>
-    </row>
-    <row r="62" spans="1:13" ht="44.25">
+      <c r="R61" t="b">
+        <f>IF(韻母表_4[[#This Row],[台羅拼音]]="", FALSE, ISNUMBER(FIND(RIGHT(韻母表_4[[#This Row],[台羅拼音]],1), "ptkh")))</f>
+        <v>0</v>
+      </c>
+      <c r="S61" s="41" t="str">
+        <f>IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R61=TRUE), "", LEN(韻母表_4[[#This Row],[台羅拼音]]))</f>
+        <v/>
+      </c>
+      <c r="T61" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", $R61=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48?])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v/>
+      </c>
+      <c r="U61" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R61=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v/>
+      </c>
+      <c r="W61" s="41" t="s">
+        <v>1436</v>
+      </c>
+    </row>
+    <row r="62" spans="1:23" ht="44.25">
       <c r="A62" s="54">
         <v>61</v>
       </c>
@@ -25387,8 +26954,27 @@
       <c r="M62" s="57" t="s">
         <v>1195</v>
       </c>
-    </row>
-    <row r="63" spans="1:13" ht="44.25">
+      <c r="R62" t="b">
+        <f>IF(韻母表_4[[#This Row],[台羅拼音]]="", FALSE, ISNUMBER(FIND(RIGHT(韻母表_4[[#This Row],[台羅拼音]],1), "ptkh")))</f>
+        <v>0</v>
+      </c>
+      <c r="S62" s="41">
+        <f>IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R62=TRUE), "", LEN(韻母表_4[[#This Row],[台羅拼音]]))</f>
+        <v>3</v>
+      </c>
+      <c r="T62" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", $R62=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48?])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v xml:space="preserve">    - xform/enn([48?])/ennh$1/    # 更</v>
+      </c>
+      <c r="U62" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R62=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v xml:space="preserve">    - xform/enn([48])/ennh$1/    # 更</v>
+      </c>
+      <c r="W62" s="41" t="s">
+        <v>1437</v>
+      </c>
+    </row>
+    <row r="63" spans="1:23" ht="44.25">
       <c r="A63" s="54">
         <v>62</v>
       </c>
@@ -25431,8 +27017,27 @@
       <c r="M63" s="57" t="s">
         <v>1198</v>
       </c>
-    </row>
-    <row r="64" spans="1:13" ht="44.25">
+      <c r="R63" t="b">
+        <f>IF(韻母表_4[[#This Row],[台羅拼音]]="", FALSE, ISNUMBER(FIND(RIGHT(韻母表_4[[#This Row],[台羅拼音]],1), "ptkh")))</f>
+        <v>1</v>
+      </c>
+      <c r="S63" s="41" t="str">
+        <f>IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R63=TRUE), "", LEN(韻母表_4[[#This Row],[台羅拼音]]))</f>
+        <v/>
+      </c>
+      <c r="T63" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", $R63=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48?])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v/>
+      </c>
+      <c r="U63" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R63=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v/>
+      </c>
+      <c r="W63" s="41" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="64" spans="1:23" ht="44.25">
       <c r="A64" s="54">
         <v>63</v>
       </c>
@@ -25471,8 +27076,27 @@
       <c r="M64" s="57" t="s">
         <v>1203</v>
       </c>
-    </row>
-    <row r="65" spans="1:13" ht="44.25">
+      <c r="R64" t="b">
+        <f>IF(韻母表_4[[#This Row],[台羅拼音]]="", FALSE, ISNUMBER(FIND(RIGHT(韻母表_4[[#This Row],[台羅拼音]],1), "ptkh")))</f>
+        <v>0</v>
+      </c>
+      <c r="S64" s="41">
+        <f>IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R64=TRUE), "", LEN(韻母表_4[[#This Row],[台羅拼音]]))</f>
+        <v>4</v>
+      </c>
+      <c r="T64" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", $R64=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48?])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v xml:space="preserve">    - xform/uinn([48?])/$1/    # 褌</v>
+      </c>
+      <c r="U64" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R64=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v xml:space="preserve">    - xform/uinn([48])/$1/    # 褌</v>
+      </c>
+      <c r="W64" s="41" t="s">
+        <v>1438</v>
+      </c>
+    </row>
+    <row r="65" spans="1:23" ht="44.25">
       <c r="A65" s="54">
         <v>64</v>
       </c>
@@ -25491,8 +27115,27 @@
       <c r="K65" s="57"/>
       <c r="L65" s="57"/>
       <c r="M65" s="57"/>
-    </row>
-    <row r="66" spans="1:13" ht="44.25">
+      <c r="R65" t="b">
+        <f>IF(韻母表_4[[#This Row],[台羅拼音]]="", FALSE, ISNUMBER(FIND(RIGHT(韻母表_4[[#This Row],[台羅拼音]],1), "ptkh")))</f>
+        <v>0</v>
+      </c>
+      <c r="S65" s="41" t="str">
+        <f>IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R65=TRUE), "", LEN(韻母表_4[[#This Row],[台羅拼音]]))</f>
+        <v/>
+      </c>
+      <c r="T65" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", $R65=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48?])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v/>
+      </c>
+      <c r="U65" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R65=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v/>
+      </c>
+      <c r="W65" s="41" t="s">
+        <v>1439</v>
+      </c>
+    </row>
+    <row r="66" spans="1:23" ht="44.25">
       <c r="A66" s="54">
         <v>65</v>
       </c>
@@ -25531,8 +27174,27 @@
       <c r="M66" s="57" t="s">
         <v>1205</v>
       </c>
-    </row>
-    <row r="67" spans="1:13" ht="44.25">
+      <c r="R66" t="b">
+        <f>IF(韻母表_4[[#This Row],[台羅拼音]]="", FALSE, ISNUMBER(FIND(RIGHT(韻母表_4[[#This Row],[台羅拼音]],1), "ptkh")))</f>
+        <v>0</v>
+      </c>
+      <c r="S66" s="41">
+        <f>IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R66=TRUE), "", LEN(韻母表_4[[#This Row],[台羅拼音]]))</f>
+        <v>2</v>
+      </c>
+      <c r="T66" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", $R66=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48?])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v xml:space="preserve">    - xform/io([48?])/ioh$1/    # 茄</v>
+      </c>
+      <c r="U66" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R66=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v xml:space="preserve">    - xform/io([48])/ioh$1/    # 茄</v>
+      </c>
+      <c r="W66" s="41" t="s">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="67" spans="1:23" ht="44.25">
       <c r="A67" s="54">
         <v>66</v>
       </c>
@@ -25571,8 +27233,27 @@
       <c r="M67" s="57" t="s">
         <v>1208</v>
       </c>
-    </row>
-    <row r="68" spans="1:13" ht="44.25">
+      <c r="R67" t="b">
+        <f>IF(韻母表_4[[#This Row],[台羅拼音]]="", FALSE, ISNUMBER(FIND(RIGHT(韻母表_4[[#This Row],[台羅拼音]],1), "ptkh")))</f>
+        <v>1</v>
+      </c>
+      <c r="S67" s="41" t="str">
+        <f>IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R67=TRUE), "", LEN(韻母表_4[[#This Row],[台羅拼音]]))</f>
+        <v/>
+      </c>
+      <c r="T67" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", $R67=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48?])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v/>
+      </c>
+      <c r="U67" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R67=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v/>
+      </c>
+      <c r="W67" s="41" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="68" spans="1:23" ht="44.25">
       <c r="A68" s="54">
         <v>67</v>
       </c>
@@ -25611,8 +27292,27 @@
       <c r="M68" s="57" t="s">
         <v>1212</v>
       </c>
-    </row>
-    <row r="69" spans="1:13" ht="44.25">
+      <c r="R68" t="b">
+        <f>IF(韻母表_4[[#This Row],[台羅拼音]]="", FALSE, ISNUMBER(FIND(RIGHT(韻母表_4[[#This Row],[台羅拼音]],1), "ptkh")))</f>
+        <v>0</v>
+      </c>
+      <c r="S68" s="41">
+        <f>IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R68=TRUE), "", LEN(韻母表_4[[#This Row],[台羅拼音]]))</f>
+        <v>3</v>
+      </c>
+      <c r="T68" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", $R68=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48?])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v xml:space="preserve">    - xform/inn([48?])/$1/    # 梔</v>
+      </c>
+      <c r="U68" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R68=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v xml:space="preserve">    - xform/inn([48])/$1/    # 梔</v>
+      </c>
+      <c r="W68" s="41" t="s">
+        <v>1441</v>
+      </c>
+    </row>
+    <row r="69" spans="1:23" ht="44.25">
       <c r="A69" s="54">
         <v>68</v>
       </c>
@@ -25649,8 +27349,27 @@
       <c r="M69" s="57" t="s">
         <v>1079</v>
       </c>
-    </row>
-    <row r="70" spans="1:13" ht="44.25">
+      <c r="R69" t="b">
+        <f>IF(韻母表_4[[#This Row],[台羅拼音]]="", FALSE, ISNUMBER(FIND(RIGHT(韻母表_4[[#This Row],[台羅拼音]],1), "ptkh")))</f>
+        <v>0</v>
+      </c>
+      <c r="S69" s="41" t="str">
+        <f>IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R69=TRUE), "", LEN(韻母表_4[[#This Row],[台羅拼音]]))</f>
+        <v/>
+      </c>
+      <c r="T69" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", $R69=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48?])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v/>
+      </c>
+      <c r="U69" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R69=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v/>
+      </c>
+      <c r="W69" s="41" t="s">
+        <v>1442</v>
+      </c>
+    </row>
+    <row r="70" spans="1:23" ht="44.25">
       <c r="A70" s="54">
         <v>69</v>
       </c>
@@ -25689,8 +27408,27 @@
       <c r="M70" s="57" t="s">
         <v>1217</v>
       </c>
-    </row>
-    <row r="71" spans="1:13" ht="44.25">
+      <c r="R70" t="b">
+        <f>IF(韻母表_4[[#This Row],[台羅拼音]]="", FALSE, ISNUMBER(FIND(RIGHT(韻母表_4[[#This Row],[台羅拼音]],1), "ptkh")))</f>
+        <v>0</v>
+      </c>
+      <c r="S70" s="41">
+        <f>IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R70=TRUE), "", LEN(韻母表_4[[#This Row],[台羅拼音]]))</f>
+        <v>4</v>
+      </c>
+      <c r="T70" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", $R70=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48?])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v xml:space="preserve">    - xform/ionn([48?])/$1/    # 薑</v>
+      </c>
+      <c r="U70" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R70=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v xml:space="preserve">    - xform/ionn([48])/$1/    # 薑</v>
+      </c>
+      <c r="W70" s="41" t="s">
+        <v>1443</v>
+      </c>
+    </row>
+    <row r="71" spans="1:23" ht="44.25">
       <c r="A71" s="54">
         <v>70</v>
       </c>
@@ -25725,8 +27463,27 @@
       <c r="M71" s="57" t="s">
         <v>1079</v>
       </c>
-    </row>
-    <row r="72" spans="1:13" ht="44.25">
+      <c r="R71" t="b">
+        <f>IF(韻母表_4[[#This Row],[台羅拼音]]="", FALSE, ISNUMBER(FIND(RIGHT(韻母表_4[[#This Row],[台羅拼音]],1), "ptkh")))</f>
+        <v>0</v>
+      </c>
+      <c r="S71" s="41" t="str">
+        <f>IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R71=TRUE), "", LEN(韻母表_4[[#This Row],[台羅拼音]]))</f>
+        <v/>
+      </c>
+      <c r="T71" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", $R71=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48?])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v/>
+      </c>
+      <c r="U71" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R71=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v/>
+      </c>
+      <c r="W71" s="41" t="s">
+        <v>1444</v>
+      </c>
+    </row>
+    <row r="72" spans="1:23" ht="44.25">
       <c r="A72" s="54">
         <v>71</v>
       </c>
@@ -25765,8 +27522,27 @@
       <c r="M72" s="57" t="s">
         <v>1220</v>
       </c>
-    </row>
-    <row r="73" spans="1:13" ht="44.25">
+      <c r="R72" t="b">
+        <f>IF(韻母表_4[[#This Row],[台羅拼音]]="", FALSE, ISNUMBER(FIND(RIGHT(韻母表_4[[#This Row],[台羅拼音]],1), "ptkh")))</f>
+        <v>0</v>
+      </c>
+      <c r="S72" s="41">
+        <f>IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R72=TRUE), "", LEN(韻母表_4[[#This Row],[台羅拼音]]))</f>
+        <v>4</v>
+      </c>
+      <c r="T72" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", $R72=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48?])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v xml:space="preserve">    - xform/iann([48?])/iannh$1/    # 驚</v>
+      </c>
+      <c r="U72" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R72=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v xml:space="preserve">    - xform/iann([48])/iannh$1/    # 驚</v>
+      </c>
+      <c r="W72" s="41" t="s">
+        <v>1445</v>
+      </c>
+    </row>
+    <row r="73" spans="1:23" ht="44.25">
       <c r="A73" s="54">
         <v>72</v>
       </c>
@@ -25811,8 +27587,27 @@
         <f xml:space="preserve"> _xlfn.CONCAT(M72, "ㄏ")</f>
         <v>⁰ㄧㄚㄏ</v>
       </c>
-    </row>
-    <row r="74" spans="1:13" ht="44.25">
+      <c r="R73" t="b">
+        <f>IF(韻母表_4[[#This Row],[台羅拼音]]="", FALSE, ISNUMBER(FIND(RIGHT(韻母表_4[[#This Row],[台羅拼音]],1), "ptkh")))</f>
+        <v>1</v>
+      </c>
+      <c r="S73" s="41" t="str">
+        <f>IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R73=TRUE), "", LEN(韻母表_4[[#This Row],[台羅拼音]]))</f>
+        <v/>
+      </c>
+      <c r="T73" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", $R73=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48?])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v/>
+      </c>
+      <c r="U73" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R73=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v/>
+      </c>
+      <c r="W73" s="41" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="74" spans="1:23" ht="44.25">
       <c r="A74" s="54">
         <v>73</v>
       </c>
@@ -25851,8 +27646,27 @@
       <c r="M74" s="57" t="s">
         <v>1224</v>
       </c>
-    </row>
-    <row r="75" spans="1:13" ht="44.25">
+      <c r="R74" t="b">
+        <f>IF(韻母表_4[[#This Row],[台羅拼音]]="", FALSE, ISNUMBER(FIND(RIGHT(韻母表_4[[#This Row],[台羅拼音]],1), "ptkh")))</f>
+        <v>0</v>
+      </c>
+      <c r="S74" s="41">
+        <f>IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R74=TRUE), "", LEN(韻母表_4[[#This Row],[台羅拼音]]))</f>
+        <v>4</v>
+      </c>
+      <c r="T74" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", $R74=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48?])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v xml:space="preserve">    - xform/uann([48?])/$1/    # 官</v>
+      </c>
+      <c r="U74" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R74=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v xml:space="preserve">    - xform/uann([48])/$1/    # 官</v>
+      </c>
+      <c r="W74" s="41" t="s">
+        <v>1446</v>
+      </c>
+    </row>
+    <row r="75" spans="1:23" ht="44.25">
       <c r="A75" s="54">
         <v>74</v>
       </c>
@@ -25887,8 +27701,27 @@
       <c r="M75" s="57" t="s">
         <v>1079</v>
       </c>
-    </row>
-    <row r="76" spans="1:13" ht="44.25">
+      <c r="R75" t="b">
+        <f>IF(韻母表_4[[#This Row],[台羅拼音]]="", FALSE, ISNUMBER(FIND(RIGHT(韻母表_4[[#This Row],[台羅拼音]],1), "ptkh")))</f>
+        <v>0</v>
+      </c>
+      <c r="S75" s="41" t="str">
+        <f>IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R75=TRUE), "", LEN(韻母表_4[[#This Row],[台羅拼音]]))</f>
+        <v/>
+      </c>
+      <c r="T75" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", $R75=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48?])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v/>
+      </c>
+      <c r="U75" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R75=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v/>
+      </c>
+      <c r="W75" s="41" t="s">
+        <v>1447</v>
+      </c>
+    </row>
+    <row r="76" spans="1:23" ht="44.25">
       <c r="A76" s="54">
         <v>75</v>
       </c>
@@ -25927,8 +27760,27 @@
       <c r="M76" s="57" t="s">
         <v>1226</v>
       </c>
-    </row>
-    <row r="77" spans="1:13" ht="44.25">
+      <c r="R76" t="b">
+        <f>IF(韻母表_4[[#This Row],[台羅拼音]]="", FALSE, ISNUMBER(FIND(RIGHT(韻母表_4[[#This Row],[台羅拼音]],1), "ptkh")))</f>
+        <v>0</v>
+      </c>
+      <c r="S76" s="41">
+        <f>IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R76=TRUE), "", LEN(韻母表_4[[#This Row],[台羅拼音]]))</f>
+        <v>2</v>
+      </c>
+      <c r="T76" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", $R76=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48?])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v xml:space="preserve">    - xform/ng([48?])/ngh$1/    # 鋼</v>
+      </c>
+      <c r="U76" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R76=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v xml:space="preserve">    - xform/ng([48])/ngh$1/    # 鋼</v>
+      </c>
+      <c r="W76" s="41" t="s">
+        <v>1448</v>
+      </c>
+    </row>
+    <row r="77" spans="1:23" ht="44.25">
       <c r="A77" s="54">
         <v>76</v>
       </c>
@@ -25973,8 +27825,27 @@
         <f xml:space="preserve"> _xlfn.CONCAT(M76, "ㄏ")</f>
         <v>ㄥㄏ</v>
       </c>
-    </row>
-    <row r="78" spans="1:13" ht="44.25">
+      <c r="R77" t="b">
+        <f>IF(韻母表_4[[#This Row],[台羅拼音]]="", FALSE, ISNUMBER(FIND(RIGHT(韻母表_4[[#This Row],[台羅拼音]],1), "ptkh")))</f>
+        <v>1</v>
+      </c>
+      <c r="S77" s="41" t="str">
+        <f>IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R77=TRUE), "", LEN(韻母表_4[[#This Row],[台羅拼音]]))</f>
+        <v/>
+      </c>
+      <c r="T77" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", $R77=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48?])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v/>
+      </c>
+      <c r="U77" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R77=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v/>
+      </c>
+      <c r="W77" s="41" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="78" spans="1:23" ht="44.25">
       <c r="A78" s="54">
         <v>77</v>
       </c>
@@ -26013,8 +27884,27 @@
       <c r="M78" s="57" t="s">
         <v>1079</v>
       </c>
-    </row>
-    <row r="79" spans="1:13" ht="44.25">
+      <c r="R78" t="b">
+        <f>IF(韻母表_4[[#This Row],[台羅拼音]]="", FALSE, ISNUMBER(FIND(RIGHT(韻母表_4[[#This Row],[台羅拼音]],1), "ptkh")))</f>
+        <v>0</v>
+      </c>
+      <c r="S78" s="41" t="str">
+        <f>IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R78=TRUE), "", LEN(韻母表_4[[#This Row],[台羅拼音]]))</f>
+        <v/>
+      </c>
+      <c r="T78" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", $R78=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48?])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v/>
+      </c>
+      <c r="U78" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R78=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v/>
+      </c>
+      <c r="W78" s="41" t="s">
+        <v>1449</v>
+      </c>
+    </row>
+    <row r="79" spans="1:23" ht="44.25">
       <c r="A79" s="54">
         <v>78</v>
       </c>
@@ -26053,8 +27943,27 @@
       <c r="M79" s="57" t="s">
         <v>1084</v>
       </c>
-    </row>
-    <row r="80" spans="1:13" ht="44.25">
+      <c r="R79" t="b">
+        <f>IF(韻母表_4[[#This Row],[台羅拼音]]="", FALSE, ISNUMBER(FIND(RIGHT(韻母表_4[[#This Row],[台羅拼音]],1), "ptkh")))</f>
+        <v>1</v>
+      </c>
+      <c r="S79" s="41" t="str">
+        <f>IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R79=TRUE), "", LEN(韻母表_4[[#This Row],[台羅拼音]]))</f>
+        <v/>
+      </c>
+      <c r="T79" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", $R79=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48?])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v/>
+      </c>
+      <c r="U79" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R79=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v/>
+      </c>
+      <c r="W79" s="41" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="80" spans="1:23" ht="44.25">
       <c r="A80" s="54">
         <v>79</v>
       </c>
@@ -26093,8 +28002,27 @@
       <c r="M80" s="57" t="s">
         <v>1231</v>
       </c>
-    </row>
-    <row r="81" spans="1:13" ht="44.25">
+      <c r="R80" t="b">
+        <f>IF(韻母表_4[[#This Row],[台羅拼音]]="", FALSE, ISNUMBER(FIND(RIGHT(韻母表_4[[#This Row],[台羅拼音]],1), "ptkh")))</f>
+        <v>0</v>
+      </c>
+      <c r="S80" s="41">
+        <f>IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R80=TRUE), "", LEN(韻母表_4[[#This Row],[台羅拼音]]))</f>
+        <v>4</v>
+      </c>
+      <c r="T80" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", $R80=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48?])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v xml:space="preserve">    - xform/ainn([48?])/$1/    # 閒</v>
+      </c>
+      <c r="U80" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R80=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v xml:space="preserve">    - xform/ainn([48])/$1/    # 閒</v>
+      </c>
+      <c r="W80" s="41" t="s">
+        <v>1450</v>
+      </c>
+    </row>
+    <row r="81" spans="1:23" ht="44.25">
       <c r="A81" s="54">
         <v>80</v>
       </c>
@@ -26129,8 +28057,27 @@
       <c r="M81" s="57" t="s">
         <v>1079</v>
       </c>
-    </row>
-    <row r="82" spans="1:13" ht="44.25">
+      <c r="R81" t="b">
+        <f>IF(韻母表_4[[#This Row],[台羅拼音]]="", FALSE, ISNUMBER(FIND(RIGHT(韻母表_4[[#This Row],[台羅拼音]],1), "ptkh")))</f>
+        <v>0</v>
+      </c>
+      <c r="S81" s="41" t="str">
+        <f>IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R81=TRUE), "", LEN(韻母表_4[[#This Row],[台羅拼音]]))</f>
+        <v/>
+      </c>
+      <c r="T81" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", $R81=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48?])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v/>
+      </c>
+      <c r="U81" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R81=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v/>
+      </c>
+      <c r="W81" s="41" t="s">
+        <v>1451</v>
+      </c>
+    </row>
+    <row r="82" spans="1:23" ht="44.25">
       <c r="A82" s="54">
         <v>81</v>
       </c>
@@ -26173,8 +28120,27 @@
       <c r="M82" s="57" t="s">
         <v>1235</v>
       </c>
-    </row>
-    <row r="83" spans="1:13" ht="44.25">
+      <c r="R82" t="b">
+        <f>IF(韻母表_4[[#This Row],[台羅拼音]]="", FALSE, ISNUMBER(FIND(RIGHT(韻母表_4[[#This Row],[台羅拼音]],1), "ptkh")))</f>
+        <v>0</v>
+      </c>
+      <c r="S82" s="41">
+        <f>IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R82=TRUE), "", LEN(韻母表_4[[#This Row],[台羅拼音]]))</f>
+        <v>3</v>
+      </c>
+      <c r="T82" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", $R82=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48?])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v xml:space="preserve">    - xform/onn([48?])/$1/    # 姑</v>
+      </c>
+      <c r="U82" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R82=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v xml:space="preserve">    - xform/onn([48])/$1/    # 姑</v>
+      </c>
+      <c r="W82" s="41" t="s">
+        <v>1452</v>
+      </c>
+    </row>
+    <row r="83" spans="1:23" ht="44.25">
       <c r="A83" s="54">
         <v>82</v>
       </c>
@@ -26209,8 +28175,27 @@
       <c r="M83" s="57" t="s">
         <v>1079</v>
       </c>
-    </row>
-    <row r="84" spans="1:13" ht="44.25">
+      <c r="R83" t="b">
+        <f>IF(韻母表_4[[#This Row],[台羅拼音]]="", FALSE, ISNUMBER(FIND(RIGHT(韻母表_4[[#This Row],[台羅拼音]],1), "ptkh")))</f>
+        <v>0</v>
+      </c>
+      <c r="S83" s="41" t="str">
+        <f>IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R83=TRUE), "", LEN(韻母表_4[[#This Row],[台羅拼音]]))</f>
+        <v/>
+      </c>
+      <c r="T83" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", $R83=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48?])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v/>
+      </c>
+      <c r="U83" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R83=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v/>
+      </c>
+      <c r="W83" s="41" t="s">
+        <v>1453</v>
+      </c>
+    </row>
+    <row r="84" spans="1:23" ht="44.25">
       <c r="A84" s="54">
         <v>83</v>
       </c>
@@ -26249,8 +28234,27 @@
       <c r="M84" s="57" t="s">
         <v>1238</v>
       </c>
-    </row>
-    <row r="85" spans="1:13" ht="44.25">
+      <c r="R84" t="b">
+        <f>IF(韻母表_4[[#This Row],[台羅拼音]]="", FALSE, ISNUMBER(FIND(RIGHT(韻母表_4[[#This Row],[台羅拼音]],1), "ptkh")))</f>
+        <v>0</v>
+      </c>
+      <c r="S84" s="41">
+        <f>IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R84=TRUE), "", LEN(韻母表_4[[#This Row],[台羅拼音]]))</f>
+        <v>1</v>
+      </c>
+      <c r="T84" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", $R84=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48?])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v xml:space="preserve">    - xform/m([48?])/mh$1/    # 姆</v>
+      </c>
+      <c r="U84" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R84=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v xml:space="preserve">    - xform/m([48])/mh$1/    # 姆</v>
+      </c>
+      <c r="W84" s="41" t="s">
+        <v>1454</v>
+      </c>
+    </row>
+    <row r="85" spans="1:23" ht="44.25">
       <c r="A85" s="54">
         <v>84</v>
       </c>
@@ -26295,8 +28299,27 @@
         <f xml:space="preserve"> _xlfn.CONCAT(M84, "ㄏ")</f>
         <v>ㄇㄏ</v>
       </c>
-    </row>
-    <row r="86" spans="1:13" ht="44.25">
+      <c r="R85" t="b">
+        <f>IF(韻母表_4[[#This Row],[台羅拼音]]="", FALSE, ISNUMBER(FIND(RIGHT(韻母表_4[[#This Row],[台羅拼音]],1), "ptkh")))</f>
+        <v>1</v>
+      </c>
+      <c r="S85" s="41" t="str">
+        <f>IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R85=TRUE), "", LEN(韻母表_4[[#This Row],[台羅拼音]]))</f>
+        <v/>
+      </c>
+      <c r="T85" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", $R85=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48?])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v/>
+      </c>
+      <c r="U85" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R85=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v/>
+      </c>
+      <c r="W85" s="41" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="86" spans="1:23" ht="44.25">
       <c r="A86" s="54">
         <v>85</v>
       </c>
@@ -26335,8 +28358,27 @@
       <c r="M86" s="57" t="s">
         <v>1240</v>
       </c>
-    </row>
-    <row r="87" spans="1:13" ht="44.25">
+      <c r="R86" t="b">
+        <f>IF(韻母表_4[[#This Row],[台羅拼音]]="", FALSE, ISNUMBER(FIND(RIGHT(韻母表_4[[#This Row],[台羅拼音]],1), "ptkh")))</f>
+        <v>0</v>
+      </c>
+      <c r="S86" s="41">
+        <f>IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R86=TRUE), "", LEN(韻母表_4[[#This Row],[台羅拼音]]))</f>
+        <v>4</v>
+      </c>
+      <c r="T86" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", $R86=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48?])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v xml:space="preserve">    - xform/uang([48?])/$1/    # 光</v>
+      </c>
+      <c r="U86" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R86=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v xml:space="preserve">    - xform/uang([48])/$1/    # 光</v>
+      </c>
+      <c r="W86" s="41" t="s">
+        <v>1455</v>
+      </c>
+    </row>
+    <row r="87" spans="1:23" ht="44.25">
       <c r="A87" s="54">
         <v>86</v>
       </c>
@@ -26373,8 +28415,27 @@
       <c r="M87" s="57" t="s">
         <v>1079</v>
       </c>
-    </row>
-    <row r="88" spans="1:13" ht="44.25">
+      <c r="R87" t="b">
+        <f>IF(韻母表_4[[#This Row],[台羅拼音]]="", FALSE, ISNUMBER(FIND(RIGHT(韻母表_4[[#This Row],[台羅拼音]],1), "ptkh")))</f>
+        <v>0</v>
+      </c>
+      <c r="S87" s="41" t="str">
+        <f>IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R87=TRUE), "", LEN(韻母表_4[[#This Row],[台羅拼音]]))</f>
+        <v/>
+      </c>
+      <c r="T87" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", $R87=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48?])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v/>
+      </c>
+      <c r="U87" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R87=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v/>
+      </c>
+      <c r="W87" s="41" t="s">
+        <v>1456</v>
+      </c>
+    </row>
+    <row r="88" spans="1:23" ht="44.25">
       <c r="A88" s="54">
         <v>87</v>
       </c>
@@ -26411,8 +28472,27 @@
       <c r="M88" s="57" t="s">
         <v>1245</v>
       </c>
-    </row>
-    <row r="89" spans="1:13" ht="44.25">
+      <c r="R88" t="b">
+        <f>IF(韻母表_4[[#This Row],[台羅拼音]]="", FALSE, ISNUMBER(FIND(RIGHT(韻母表_4[[#This Row],[台羅拼音]],1), "ptkh")))</f>
+        <v>0</v>
+      </c>
+      <c r="S88" s="41">
+        <f>IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R88=TRUE), "", LEN(韻母表_4[[#This Row],[台羅拼音]]))</f>
+        <v>5</v>
+      </c>
+      <c r="T88" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", $R88=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48?])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v xml:space="preserve">    - xform/uainn([48?])/uainnh$1/    # 閂</v>
+      </c>
+      <c r="U88" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R88=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v xml:space="preserve">    - xform/uainn([48])/uainnh$1/    # 閂</v>
+      </c>
+      <c r="W88" s="41" t="s">
+        <v>1457</v>
+      </c>
+    </row>
+    <row r="89" spans="1:23" ht="44.25">
       <c r="A89" s="54">
         <v>88</v>
       </c>
@@ -26449,8 +28529,27 @@
       <c r="M89" s="57" t="s">
         <v>1250</v>
       </c>
-    </row>
-    <row r="90" spans="1:13" ht="44.25">
+      <c r="R89" t="b">
+        <f>IF(韻母表_4[[#This Row],[台羅拼音]]="", FALSE, ISNUMBER(FIND(RIGHT(韻母表_4[[#This Row],[台羅拼音]],1), "ptkh")))</f>
+        <v>1</v>
+      </c>
+      <c r="S89" s="41" t="str">
+        <f>IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R89=TRUE), "", LEN(韻母表_4[[#This Row],[台羅拼音]]))</f>
+        <v/>
+      </c>
+      <c r="T89" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", $R89=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48?])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v/>
+      </c>
+      <c r="U89" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R89=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v/>
+      </c>
+      <c r="W89" s="41" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="90" spans="1:23" ht="44.25">
       <c r="A90" s="54">
         <v>89</v>
       </c>
@@ -26489,8 +28588,27 @@
       <c r="M90" s="57" t="s">
         <v>1079</v>
       </c>
-    </row>
-    <row r="91" spans="1:13" ht="44.25">
+      <c r="R90" t="b">
+        <f>IF(韻母表_4[[#This Row],[台羅拼音]]="", FALSE, ISNUMBER(FIND(RIGHT(韻母表_4[[#This Row],[台羅拼音]],1), "ptkh")))</f>
+        <v>0</v>
+      </c>
+      <c r="S90" s="41" t="str">
+        <f>IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R90=TRUE), "", LEN(韻母表_4[[#This Row],[台羅拼音]]))</f>
+        <v/>
+      </c>
+      <c r="T90" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", $R90=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48?])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v/>
+      </c>
+      <c r="U90" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R90=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v/>
+      </c>
+      <c r="W90" s="41" t="s">
+        <v>1458</v>
+      </c>
+    </row>
+    <row r="91" spans="1:23" ht="44.25">
       <c r="A91" s="54">
         <v>90</v>
       </c>
@@ -26529,8 +28647,27 @@
       <c r="M91" s="57" t="s">
         <v>1079</v>
       </c>
-    </row>
-    <row r="92" spans="1:13" ht="44.25">
+      <c r="R91" t="b">
+        <f>IF(韻母表_4[[#This Row],[台羅拼音]]="", FALSE, ISNUMBER(FIND(RIGHT(韻母表_4[[#This Row],[台羅拼音]],1), "ptkh")))</f>
+        <v>0</v>
+      </c>
+      <c r="S91" s="41" t="str">
+        <f>IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R91=TRUE), "", LEN(韻母表_4[[#This Row],[台羅拼音]]))</f>
+        <v/>
+      </c>
+      <c r="T91" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", $R91=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48?])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v/>
+      </c>
+      <c r="U91" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R91=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v/>
+      </c>
+      <c r="W91" s="41" t="s">
+        <v>1459</v>
+      </c>
+    </row>
+    <row r="92" spans="1:23" ht="44.25">
       <c r="A92" s="54">
         <v>91</v>
       </c>
@@ -26569,8 +28706,27 @@
       <c r="M92" s="57" t="s">
         <v>1254</v>
       </c>
-    </row>
-    <row r="93" spans="1:13" ht="44.25">
+      <c r="R92" t="b">
+        <f>IF(韻母表_4[[#This Row],[台羅拼音]]="", FALSE, ISNUMBER(FIND(RIGHT(韻母表_4[[#This Row],[台羅拼音]],1), "ptkh")))</f>
+        <v>0</v>
+      </c>
+      <c r="S92" s="41">
+        <f>IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R92=TRUE), "", LEN(韻母表_4[[#This Row],[台羅拼音]]))</f>
+        <v>5</v>
+      </c>
+      <c r="T92" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", $R92=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48?])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v xml:space="preserve">    - xform/iaunn([48?])/$1/    # 嘄</v>
+      </c>
+      <c r="U92" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R92=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v xml:space="preserve">    - xform/iaunn([48])/$1/    # 嘄</v>
+      </c>
+      <c r="W92" s="41" t="s">
+        <v>1460</v>
+      </c>
+    </row>
+    <row r="93" spans="1:23" ht="44.25">
       <c r="A93" s="54">
         <v>92</v>
       </c>
@@ -26609,8 +28765,27 @@
       <c r="M93" s="57" t="s">
         <v>1079</v>
       </c>
-    </row>
-    <row r="94" spans="1:13" ht="44.25">
+      <c r="R93" t="b">
+        <f>IF(韻母表_4[[#This Row],[台羅拼音]]="", FALSE, ISNUMBER(FIND(RIGHT(韻母表_4[[#This Row],[台羅拼音]],1), "ptkh")))</f>
+        <v>0</v>
+      </c>
+      <c r="S93" s="41" t="str">
+        <f>IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R93=TRUE), "", LEN(韻母表_4[[#This Row],[台羅拼音]]))</f>
+        <v/>
+      </c>
+      <c r="T93" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", $R93=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48?])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v/>
+      </c>
+      <c r="U93" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R93=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v/>
+      </c>
+      <c r="W93" s="41" t="s">
+        <v>1461</v>
+      </c>
+    </row>
+    <row r="94" spans="1:23" ht="44.25">
       <c r="A94" s="54">
         <v>93</v>
       </c>
@@ -26649,8 +28824,27 @@
       <c r="M94" s="57" t="s">
         <v>1257</v>
       </c>
-    </row>
-    <row r="95" spans="1:13" ht="44.25">
+      <c r="R94" t="b">
+        <f>IF(韻母表_4[[#This Row],[台羅拼音]]="", FALSE, ISNUMBER(FIND(RIGHT(韻母表_4[[#This Row],[台羅拼音]],1), "ptkh")))</f>
+        <v>0</v>
+      </c>
+      <c r="S94" s="41">
+        <f>IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R94=TRUE), "", LEN(韻母表_4[[#This Row],[台羅拼音]]))</f>
+        <v>2</v>
+      </c>
+      <c r="T94" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", $R94=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48?])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v xml:space="preserve">    - xform/om([48?])/op$1/    # 箴</v>
+      </c>
+      <c r="U94" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R94=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v xml:space="preserve">    - xform/om([48])/op$1/    # 箴</v>
+      </c>
+      <c r="W94" s="41" t="s">
+        <v>1462</v>
+      </c>
+    </row>
+    <row r="95" spans="1:23" ht="44.25">
       <c r="A95" s="54">
         <v>94</v>
       </c>
@@ -26689,8 +28883,27 @@
       <c r="M95" s="57" t="s">
         <v>1261</v>
       </c>
-    </row>
-    <row r="96" spans="1:13" ht="32.25">
+      <c r="R95" t="b">
+        <f>IF(韻母表_4[[#This Row],[台羅拼音]]="", FALSE, ISNUMBER(FIND(RIGHT(韻母表_4[[#This Row],[台羅拼音]],1), "ptkh")))</f>
+        <v>1</v>
+      </c>
+      <c r="S95" s="41" t="str">
+        <f>IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R95=TRUE), "", LEN(韻母表_4[[#This Row],[台羅拼音]]))</f>
+        <v/>
+      </c>
+      <c r="T95" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", $R95=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48?])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v/>
+      </c>
+      <c r="U95" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R95=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v/>
+      </c>
+      <c r="W95" s="41" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="96" spans="1:23" ht="32.25">
       <c r="A96" s="54">
         <v>95</v>
       </c>
@@ -26729,8 +28942,27 @@
       <c r="M96" s="57" t="s">
         <v>1079</v>
       </c>
-    </row>
-    <row r="97" spans="1:13" ht="44.25">
+      <c r="R96" t="b">
+        <f>IF(韻母表_4[[#This Row],[台羅拼音]]="", FALSE, ISNUMBER(FIND(RIGHT(韻母表_4[[#This Row],[台羅拼音]],1), "ptkh")))</f>
+        <v>0</v>
+      </c>
+      <c r="S96" s="41" t="str">
+        <f>IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R96=TRUE), "", LEN(韻母表_4[[#This Row],[台羅拼音]]))</f>
+        <v/>
+      </c>
+      <c r="T96" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", $R96=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48?])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v/>
+      </c>
+      <c r="U96" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R96=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v/>
+      </c>
+      <c r="W96" s="41" t="s">
+        <v>1463</v>
+      </c>
+    </row>
+    <row r="97" spans="1:23" ht="44.25">
       <c r="A97" s="54">
         <v>96</v>
       </c>
@@ -26765,8 +28997,27 @@
       <c r="M97" s="57" t="s">
         <v>1079</v>
       </c>
-    </row>
-    <row r="98" spans="1:13" ht="44.25">
+      <c r="R97" t="b">
+        <f>IF(韻母表_4[[#This Row],[台羅拼音]]="", FALSE, ISNUMBER(FIND(RIGHT(韻母表_4[[#This Row],[台羅拼音]],1), "ptkh")))</f>
+        <v>0</v>
+      </c>
+      <c r="S97" s="41" t="str">
+        <f>IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R97=TRUE), "", LEN(韻母表_4[[#This Row],[台羅拼音]]))</f>
+        <v/>
+      </c>
+      <c r="T97" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", $R97=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48?])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v/>
+      </c>
+      <c r="U97" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R97=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v/>
+      </c>
+      <c r="W97" s="41" t="s">
+        <v>1464</v>
+      </c>
+    </row>
+    <row r="98" spans="1:23" ht="44.25">
       <c r="A98" s="54">
         <v>97</v>
       </c>
@@ -26803,8 +29054,27 @@
       <c r="M98" s="57" t="s">
         <v>1079</v>
       </c>
-    </row>
-    <row r="99" spans="1:13" ht="44.25">
+      <c r="R98" t="b">
+        <f>IF(韻母表_4[[#This Row],[台羅拼音]]="", FALSE, ISNUMBER(FIND(RIGHT(韻母表_4[[#This Row],[台羅拼音]],1), "ptkh")))</f>
+        <v>0</v>
+      </c>
+      <c r="S98" s="41" t="str">
+        <f>IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R98=TRUE), "", LEN(韻母表_4[[#This Row],[台羅拼音]]))</f>
+        <v/>
+      </c>
+      <c r="T98" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", $R98=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48?])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v/>
+      </c>
+      <c r="U98" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R98=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v/>
+      </c>
+      <c r="W98" s="41" t="s">
+        <v>1465</v>
+      </c>
+    </row>
+    <row r="99" spans="1:23" ht="44.25">
       <c r="A99" s="54">
         <v>98</v>
       </c>
@@ -26841,8 +29111,27 @@
       <c r="M99" s="57" t="s">
         <v>1266</v>
       </c>
-    </row>
-    <row r="100" spans="1:13" ht="44.25">
+      <c r="R99" t="b">
+        <f>IF(韻母表_4[[#This Row],[台羅拼音]]="", FALSE, ISNUMBER(FIND(RIGHT(韻母表_4[[#This Row],[台羅拼音]],1), "ptkh")))</f>
+        <v>1</v>
+      </c>
+      <c r="S99" s="41" t="str">
+        <f>IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R99=TRUE), "", LEN(韻母表_4[[#This Row],[台羅拼音]]))</f>
+        <v/>
+      </c>
+      <c r="T99" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", $R99=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48?])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v/>
+      </c>
+      <c r="U99" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R99=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v/>
+      </c>
+      <c r="W99" s="41" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="100" spans="1:23" ht="44.25">
       <c r="A100" s="54">
         <v>99</v>
       </c>
@@ -26881,8 +29170,27 @@
       <c r="M100" s="57" t="s">
         <v>1269</v>
       </c>
-    </row>
-    <row r="101" spans="1:13" ht="44.25">
+      <c r="R100" t="b">
+        <f>IF(韻母表_4[[#This Row],[台羅拼音]]="", FALSE, ISNUMBER(FIND(RIGHT(韻母表_4[[#This Row],[台羅拼音]],1), "ptkh")))</f>
+        <v>0</v>
+      </c>
+      <c r="S100" s="41">
+        <f>IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R100=TRUE), "", LEN(韻母表_4[[#This Row],[台羅拼音]]))</f>
+        <v>4</v>
+      </c>
+      <c r="T100" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", $R100=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48?])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v xml:space="preserve">    - xform/iunn([48?])/iunnh$1/    # 牛</v>
+      </c>
+      <c r="U100" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R100=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v xml:space="preserve">    - xform/iunn([48])/iunnh$1/    # 牛</v>
+      </c>
+      <c r="W100" s="41" t="s">
+        <v>1466</v>
+      </c>
+    </row>
+    <row r="101" spans="1:23" ht="44.25">
       <c r="A101" s="67">
         <v>100</v>
       </c>
@@ -26919,15 +29227,34 @@
       <c r="M101" s="92" t="s">
         <v>1272</v>
       </c>
-    </row>
-    <row r="102" spans="1:13" ht="44.25">
+      <c r="R101" t="b">
+        <f>IF(韻母表_4[[#This Row],[台羅拼音]]="", FALSE, ISNUMBER(FIND(RIGHT(韻母表_4[[#This Row],[台羅拼音]],1), "ptkh")))</f>
+        <v>1</v>
+      </c>
+      <c r="S101" s="41" t="str">
+        <f>IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R101=TRUE), "", LEN(韻母表_4[[#This Row],[台羅拼音]]))</f>
+        <v/>
+      </c>
+      <c r="T101" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", $R101=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48?])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v/>
+      </c>
+      <c r="U101" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R101=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v/>
+      </c>
+      <c r="W101" s="41" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="102" spans="1:23" ht="44.25">
       <c r="A102" s="54">
         <v>101</v>
       </c>
-      <c r="B102" s="98"/>
+      <c r="B102" s="54"/>
       <c r="C102" s="55"/>
       <c r="D102" s="63"/>
-      <c r="E102" s="101" t="s">
+      <c r="E102" s="98" t="s">
         <v>1396</v>
       </c>
       <c r="F102" s="86"/>
@@ -26948,112 +29275,165 @@
         <v>1125</v>
       </c>
       <c r="M102" s="57"/>
-    </row>
-    <row r="103" spans="1:13" ht="44.25">
+      <c r="R102" t="b">
+        <f>IF(韻母表_4[[#This Row],[台羅拼音]]="", FALSE, ISNUMBER(FIND(RIGHT(韻母表_4[[#This Row],[台羅拼音]],1), "ptkh")))</f>
+        <v>0</v>
+      </c>
+      <c r="S102" s="41">
+        <f>IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R102=TRUE), "", LEN(韻母表_4[[#This Row],[台羅拼音]]))</f>
+        <v>2</v>
+      </c>
+      <c r="T102" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", $R102=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48?])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v xml:space="preserve">    - xform/er([48?])/ir$1/    # </v>
+      </c>
+      <c r="U102" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R102=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v xml:space="preserve">    - xform/er([48])/ir$1/    # </v>
+      </c>
+      <c r="W102" s="41" t="s">
+        <v>1467</v>
+      </c>
+    </row>
+    <row r="103" spans="1:23" ht="44.25">
       <c r="A103" s="67">
         <v>102</v>
       </c>
-      <c r="B103" s="99"/>
+      <c r="B103" s="67"/>
       <c r="C103" s="68"/>
-      <c r="D103" s="100"/>
-      <c r="E103" s="104" t="s">
+      <c r="D103" s="97"/>
+      <c r="E103" s="100" t="s">
         <v>1395</v>
       </c>
-      <c r="F103" s="102"/>
-      <c r="G103" s="103" t="s">
+      <c r="F103" s="98"/>
+      <c r="G103" s="99" t="s">
         <v>1394</v>
       </c>
-      <c r="H103" s="103"/>
-      <c r="I103" s="103" t="s">
+      <c r="H103" s="99"/>
+      <c r="I103" s="99" t="s">
         <v>1400</v>
       </c>
-      <c r="J103" s="103"/>
-      <c r="K103" s="103"/>
-      <c r="L103" s="103" t="s">
+      <c r="J103" s="99"/>
+      <c r="K103" s="99"/>
+      <c r="L103" s="99" t="s">
         <v>1397</v>
       </c>
-      <c r="M103" s="103"/>
-    </row>
-    <row r="104" spans="1:13" ht="44.25">
+      <c r="M103" s="99"/>
+      <c r="R103" t="b">
+        <f>IF(韻母表_4[[#This Row],[台羅拼音]]="", FALSE, ISNUMBER(FIND(RIGHT(韻母表_4[[#This Row],[台羅拼音]],1), "ptkh")))</f>
+        <v>0</v>
+      </c>
+      <c r="S103" s="41">
+        <f>IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R103=TRUE), "", LEN(韻母表_4[[#This Row],[台羅拼音]]))</f>
+        <v>2</v>
+      </c>
+      <c r="T103" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", $R103=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48?])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v xml:space="preserve">    - xform/ir([48?])/$1/    # </v>
+      </c>
+      <c r="U103" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R103=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v xml:space="preserve">    - xform/ir([48])/$1/    # </v>
+      </c>
+      <c r="W103" s="41" t="s">
+        <v>1468</v>
+      </c>
+    </row>
+    <row r="104" spans="1:23" ht="44.25">
       <c r="A104" s="67"/>
-      <c r="B104" s="99"/>
+      <c r="B104" s="67"/>
       <c r="C104" s="68"/>
-      <c r="D104" s="105"/>
-      <c r="E104" s="101"/>
-      <c r="F104" s="102"/>
-      <c r="G104" s="103"/>
-      <c r="H104" s="106"/>
-      <c r="I104" s="103"/>
-      <c r="J104" s="106"/>
-      <c r="K104" s="106"/>
-      <c r="L104" s="106"/>
-      <c r="M104" s="106"/>
+      <c r="D104" s="101"/>
+      <c r="E104" s="98"/>
+      <c r="F104" s="98"/>
+      <c r="G104" s="99"/>
+      <c r="H104" s="102"/>
+      <c r="I104" s="99"/>
+      <c r="J104" s="102"/>
+      <c r="K104" s="102"/>
+      <c r="L104" s="102"/>
+      <c r="M104" s="102"/>
+      <c r="R104" t="b">
+        <f>IF(韻母表_4[[#This Row],[台羅拼音]]="", FALSE, ISNUMBER(FIND(RIGHT(韻母表_4[[#This Row],[台羅拼音]],1), "ptkh")))</f>
+        <v>0</v>
+      </c>
+      <c r="S104" s="41" t="str">
+        <f>IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R104=TRUE), "", LEN(韻母表_4[[#This Row],[台羅拼音]]))</f>
+        <v/>
+      </c>
+      <c r="T104" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", $R104=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48?])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v/>
+      </c>
+      <c r="U104" s="41" t="str">
+        <f ca="1" xml:space="preserve"> IF(OR(韻母表_4[[#This Row],[台羅拼音]]="", R104=TRUE), "", _xlfn.CONCAT("    ", "- xform/", 韻母表_4[[#This Row],[台羅拼音]], "([48])/", OFFSET(韻母表_4[[#This Row],[台羅拼音]],1,0), "$1", "/    # ", LEFT(韻母表_4[[#This Row],[十五音]],1)))</f>
+        <v/>
+      </c>
+      <c r="W104" s="41" t="s">
+        <v>1464</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="A2:M102 A103:D103 F103:M103">
-    <cfRule type="expression" dxfId="43" priority="22">
+    <cfRule type="expression" dxfId="18" priority="22">
       <formula>MOD($B2,2)&lt;&gt;0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="42" priority="23">
+    <cfRule type="expression" dxfId="17" priority="23">
       <formula>MOD($A2,2)&lt;&gt;0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="41" priority="24">
+    <cfRule type="expression" dxfId="16" priority="24">
       <formula>MOD($A2,2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A102:M102 A103:D103 F103:M103">
-    <cfRule type="expression" dxfId="23" priority="19">
+    <cfRule type="expression" dxfId="15" priority="19">
       <formula>MOD($B102,2)&lt;&gt;0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="22" priority="20">
+    <cfRule type="expression" dxfId="14" priority="20">
       <formula>MOD($A102,2)&lt;&gt;0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="21" priority="21">
+    <cfRule type="expression" dxfId="13" priority="21">
       <formula>MOD($A102,2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E103">
-    <cfRule type="expression" dxfId="11" priority="10">
+    <cfRule type="expression" dxfId="12" priority="7">
       <formula>MOD($B103,2)&lt;&gt;0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="10" priority="11">
+    <cfRule type="expression" dxfId="11" priority="8">
       <formula>MOD($A103,2)&lt;&gt;0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="9" priority="12">
+    <cfRule type="expression" dxfId="10" priority="9">
       <formula>MOD($A103,2)=0</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E103">
-    <cfRule type="expression" dxfId="8" priority="7">
+    <cfRule type="expression" dxfId="9" priority="10">
       <formula>MOD($B103,2)&lt;&gt;0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="7" priority="8">
+    <cfRule type="expression" dxfId="8" priority="11">
       <formula>MOD($A103,2)&lt;&gt;0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="6" priority="9">
+    <cfRule type="expression" dxfId="7" priority="12">
       <formula>MOD($A103,2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I104">
-    <cfRule type="expression" dxfId="5" priority="4">
+    <cfRule type="expression" dxfId="6" priority="1">
       <formula>MOD($B104,2)&lt;&gt;0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="4" priority="5">
+    <cfRule type="expression" dxfId="5" priority="2">
       <formula>MOD($A104,2)&lt;&gt;0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="3" priority="6">
+    <cfRule type="expression" dxfId="4" priority="3">
       <formula>MOD($A104,2)=0</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I104">
-    <cfRule type="expression" dxfId="2" priority="1">
+    <cfRule type="expression" dxfId="3" priority="4">
       <formula>MOD($B104,2)&lt;&gt;0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="1" priority="2">
+    <cfRule type="expression" dxfId="2" priority="5">
       <formula>MOD($A104,2)&lt;&gt;0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="0" priority="3">
+    <cfRule type="expression" dxfId="1" priority="6">
       <formula>MOD($A104,2)=0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -27065,6 +29445,1145 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{63FDC818-4576-4836-ADCE-5368C6C31AFB}">
+  <dimension ref="A1:E104"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
+  <cols>
+    <col min="2" max="2" width="42" customWidth="1"/>
+    <col min="5" max="5" width="39.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="22.5">
+      <c r="A1" t="s">
+        <v>1469</v>
+      </c>
+      <c r="B1" s="41" t="s">
+        <v>1472</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>2</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1473</v>
+      </c>
+      <c r="D2" cm="1">
+        <f t="array" ref="D2:E49">_xlfn._xlws.SORT(_xlfn._xlws.FILTER(A2:B104, (B2:B104&lt;&gt;"")*(A2:A104&lt;&gt;""), "無資料"), 1, -1)</f>
+        <v>5</v>
+      </c>
+      <c r="E2" t="str">
+        <v xml:space="preserve">    - xform/uainn([48?])/uainnh$1/    # 閂</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" t="s">
+        <v>1079</v>
+      </c>
+      <c r="B3" t="s">
+        <v>1474</v>
+      </c>
+      <c r="D3">
+        <v>5</v>
+      </c>
+      <c r="E3" t="str">
+        <v xml:space="preserve">    - xform/iaunn([48?])/$1/    # 嘄</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>1475</v>
+      </c>
+      <c r="D4">
+        <v>4</v>
+      </c>
+      <c r="E4" t="str">
+        <v xml:space="preserve">    - xform/iong([48?])/iok$1/    # 恭</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" t="s">
+        <v>1079</v>
+      </c>
+      <c r="B5" t="s">
+        <v>1476</v>
+      </c>
+      <c r="D5">
+        <v>4</v>
+      </c>
+      <c r="E5" t="str">
+        <v xml:space="preserve">    - xform/iang([48?])/iak$1/    # 姜</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6">
+        <v>2</v>
+      </c>
+      <c r="B6" t="s">
+        <v>1477</v>
+      </c>
+      <c r="D6">
+        <v>4</v>
+      </c>
+      <c r="E6" t="str">
+        <v xml:space="preserve">    - xform/uinn([48?])/$1/    # 褌</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" t="s">
+        <v>1079</v>
+      </c>
+      <c r="B7" t="s">
+        <v>1478</v>
+      </c>
+      <c r="D7">
+        <v>4</v>
+      </c>
+      <c r="E7" t="str">
+        <v xml:space="preserve">    - xform/ionn([48?])/$1/    # 薑</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8">
+        <v>2</v>
+      </c>
+      <c r="B8" t="s">
+        <v>1479</v>
+      </c>
+      <c r="D8">
+        <v>4</v>
+      </c>
+      <c r="E8" t="str">
+        <v xml:space="preserve">    - xform/iann([48?])/iannh$1/    # 驚</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" t="s">
+        <v>1079</v>
+      </c>
+      <c r="B9" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D9">
+        <v>4</v>
+      </c>
+      <c r="E9" t="str">
+        <v xml:space="preserve">    - xform/uann([48?])/$1/    # 官</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10">
+        <v>2</v>
+      </c>
+      <c r="B10" t="s">
+        <v>1480</v>
+      </c>
+      <c r="D10">
+        <v>4</v>
+      </c>
+      <c r="E10" t="str">
+        <v xml:space="preserve">    - xform/ainn([48?])/$1/    # 閒</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" t="s">
+        <v>1079</v>
+      </c>
+      <c r="B11" t="s">
+        <v>1481</v>
+      </c>
+      <c r="D11">
+        <v>4</v>
+      </c>
+      <c r="E11" t="str">
+        <v xml:space="preserve">    - xform/uang([48?])/$1/    # 光</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12">
+        <v>2</v>
+      </c>
+      <c r="B12" t="s">
+        <v>1482</v>
+      </c>
+      <c r="D12">
+        <v>4</v>
+      </c>
+      <c r="E12" t="str">
+        <v xml:space="preserve">    - xform/iunn([48?])/iunnh$1/    # 牛</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" t="s">
+        <v>1079</v>
+      </c>
+      <c r="B13" t="s">
+        <v>1483</v>
+      </c>
+      <c r="D13">
+        <v>3</v>
+      </c>
+      <c r="E13" t="str">
+        <v xml:space="preserve">    - xform/ian([48?])/iat$1/    # 堅</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14">
+        <v>3</v>
+      </c>
+      <c r="B14" t="s">
+        <v>1484</v>
+      </c>
+      <c r="D14">
+        <v>3</v>
+      </c>
+      <c r="E14" t="str">
+        <v xml:space="preserve">    - xform/ong([48?])/ok$1/    # 公</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" t="s">
+        <v>1079</v>
+      </c>
+      <c r="B15" t="s">
+        <v>1485</v>
+      </c>
+      <c r="D15">
+        <v>3</v>
+      </c>
+      <c r="E15" t="str">
+        <v xml:space="preserve">    - xform/uai([48?])/uaih$1/    # 乖</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16">
+        <v>3</v>
+      </c>
+      <c r="B16" t="s">
+        <v>1486</v>
+      </c>
+      <c r="D16">
+        <v>3</v>
+      </c>
+      <c r="E16" t="str">
+        <v xml:space="preserve">    - xform/ing([48?])/ik$1/    # 經</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" t="s">
+        <v>1079</v>
+      </c>
+      <c r="B17" t="s">
+        <v>1487</v>
+      </c>
+      <c r="D17">
+        <v>3</v>
+      </c>
+      <c r="E17" t="str">
+        <v xml:space="preserve">    - xform/uan([48?])/uat$1/    # 觀</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18">
+        <v>3</v>
+      </c>
+      <c r="B18" t="s">
+        <v>1488</v>
+      </c>
+      <c r="D18">
+        <v>3</v>
+      </c>
+      <c r="E18" t="str">
+        <v xml:space="preserve">    - xform/iau([48?])/iauh$1/    # 嬌</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" t="s">
+        <v>1079</v>
+      </c>
+      <c r="B19" t="s">
+        <v>1489</v>
+      </c>
+      <c r="D19">
+        <v>3</v>
+      </c>
+      <c r="E19" t="str">
+        <v xml:space="preserve">    - xform/ang([48?])/ak$1/    # 江</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20">
+        <v>3</v>
+      </c>
+      <c r="B20" t="s">
+        <v>1490</v>
+      </c>
+      <c r="D20">
+        <v>3</v>
+      </c>
+      <c r="E20" t="str">
+        <v xml:space="preserve">    - xform/iam([48?])/iap$1/    # 兼</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" t="s">
+        <v>1079</v>
+      </c>
+      <c r="B21" t="s">
+        <v>1491</v>
+      </c>
+      <c r="D21">
+        <v>3</v>
+      </c>
+      <c r="E21" t="str">
+        <v xml:space="preserve">    - xform/ann([48?])/annh$1/    # 監</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22">
+        <v>2</v>
+      </c>
+      <c r="B22" t="s">
+        <v>1492</v>
+      </c>
+      <c r="D22">
+        <v>3</v>
+      </c>
+      <c r="E22" t="str">
+        <v xml:space="preserve">    - xform/enn([48?])/ennh$1/    # 更</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" t="s">
+        <v>1079</v>
+      </c>
+      <c r="B23" t="s">
+        <v>1493</v>
+      </c>
+      <c r="D23">
+        <v>3</v>
+      </c>
+      <c r="E23" t="str">
+        <v xml:space="preserve">    - xform/inn([48?])/$1/    # 梔</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24">
+        <v>3</v>
+      </c>
+      <c r="B24" t="s">
+        <v>1494</v>
+      </c>
+      <c r="D24">
+        <v>3</v>
+      </c>
+      <c r="E24" t="str">
+        <v xml:space="preserve">    - xform/onn([48?])/$1/    # 姑</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" t="s">
+        <v>1079</v>
+      </c>
+      <c r="B25" t="s">
+        <v>1495</v>
+      </c>
+      <c r="D25">
+        <v>2</v>
+      </c>
+      <c r="E25" t="str">
+        <v xml:space="preserve">    - xform/un([48?])/ut$1/    # 君</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26">
+        <v>1</v>
+      </c>
+      <c r="B26" t="s">
+        <v>1496</v>
+      </c>
+      <c r="D26">
+        <v>2</v>
+      </c>
+      <c r="E26" t="str">
+        <v xml:space="preserve">    - xform/im([48?])/ip$1/    # 金</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" t="s">
+        <v>1079</v>
+      </c>
+      <c r="B27" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D27">
+        <v>2</v>
+      </c>
+      <c r="E27" t="str">
+        <v xml:space="preserve">    - xform/ui([48?])/$1/    # 規</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28">
+        <v>4</v>
+      </c>
+      <c r="B28" t="s">
+        <v>1497</v>
+      </c>
+      <c r="D28">
+        <v>2</v>
+      </c>
+      <c r="E28" t="str">
+        <v xml:space="preserve">    - xform/ee([48?])/eeh$1/    # 嘉</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" t="s">
+        <v>1079</v>
+      </c>
+      <c r="B29" t="s">
+        <v>1498</v>
+      </c>
+      <c r="D29">
+        <v>2</v>
+      </c>
+      <c r="E29" t="str">
+        <v xml:space="preserve">    - xform/an([48?])/at$1/    # 干</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30">
+        <v>1</v>
+      </c>
+      <c r="B30" t="s">
+        <v>1499</v>
+      </c>
+      <c r="D30">
+        <v>2</v>
+      </c>
+      <c r="E30" t="str">
+        <v xml:space="preserve">    - xform/oo([48?])/ooh$1/    # 沽</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" t="s">
+        <v>1079</v>
+      </c>
+      <c r="B31" t="s">
+        <v>1500</v>
+      </c>
+      <c r="D31">
+        <v>2</v>
+      </c>
+      <c r="E31" t="str">
+        <v xml:space="preserve">    - xform/ai([48?])/$1/    # 皆</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32">
+        <v>2</v>
+      </c>
+      <c r="B32" t="s">
+        <v>1501</v>
+      </c>
+      <c r="D32">
+        <v>2</v>
+      </c>
+      <c r="E32" t="str">
+        <v xml:space="preserve">    - xform/in([48?])/it$1/    # 巾</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" t="s">
+        <v>1079</v>
+      </c>
+      <c r="B33" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D33">
+        <v>2</v>
+      </c>
+      <c r="E33" t="str">
+        <v xml:space="preserve">    - xform/am([48?])/ap$1/    # 甘</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34">
+        <v>2</v>
+      </c>
+      <c r="B34" t="s">
+        <v>1502</v>
+      </c>
+      <c r="D34">
+        <v>2</v>
+      </c>
+      <c r="E34" t="str">
+        <v xml:space="preserve">    - xform/ua([48?])/uah$1/    # 瓜</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" t="s">
+        <v>1079</v>
+      </c>
+      <c r="B35" t="s">
+        <v>1503</v>
+      </c>
+      <c r="D35">
+        <v>2</v>
+      </c>
+      <c r="E35" t="str">
+        <v xml:space="preserve">    - xform/au([48?])/auh$1/    # 交</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36">
+        <v>4</v>
+      </c>
+      <c r="B36" t="s">
+        <v>1504</v>
+      </c>
+      <c r="D36">
+        <v>2</v>
+      </c>
+      <c r="E36" t="str">
+        <v xml:space="preserve">    - xform/ia([48?])/iah$1/    # 迦</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" t="s">
+        <v>1079</v>
+      </c>
+      <c r="B37" t="s">
+        <v>1505</v>
+      </c>
+      <c r="D37">
+        <v>2</v>
+      </c>
+      <c r="E37" t="str">
+        <v xml:space="preserve">    - xform/ue([48?])/ueh$1/    # 檜</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38">
+        <v>2</v>
+      </c>
+      <c r="B38" t="s">
+        <v>1506</v>
+      </c>
+      <c r="D38">
+        <v>2</v>
+      </c>
+      <c r="E38" t="str">
+        <v xml:space="preserve">    - xform/iu([48?])/$1/    # 丩</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" t="s">
+        <v>1079</v>
+      </c>
+      <c r="B39" t="s">
+        <v>1507</v>
+      </c>
+      <c r="D39">
+        <v>2</v>
+      </c>
+      <c r="E39" t="str">
+        <v xml:space="preserve">    - xform/io([48?])/ioh$1/    # 茄</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40">
+        <v>2</v>
+      </c>
+      <c r="B40" t="s">
+        <v>1508</v>
+      </c>
+      <c r="D40">
+        <v>2</v>
+      </c>
+      <c r="E40" t="str">
+        <v xml:space="preserve">    - xform/ng([48?])/ngh$1/    # 鋼</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" t="s">
+        <v>1079</v>
+      </c>
+      <c r="B41" t="s">
+        <v>1509</v>
+      </c>
+      <c r="D41">
+        <v>2</v>
+      </c>
+      <c r="E41" t="str">
+        <v xml:space="preserve">    - xform/om([48?])/op$1/    # 箴</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42">
+        <v>3</v>
+      </c>
+      <c r="B42" t="s">
+        <v>1510</v>
+      </c>
+      <c r="D42">
+        <v>2</v>
+      </c>
+      <c r="E42" t="str">
+        <v xml:space="preserve">    - xform/er([48?])/ir$1/    # </v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" t="s">
+        <v>1079</v>
+      </c>
+      <c r="B43" t="s">
+        <v>1511</v>
+      </c>
+      <c r="D43">
+        <v>2</v>
+      </c>
+      <c r="E43" t="str">
+        <v xml:space="preserve">    - xform/ir([48?])/$1/    # </v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44">
+        <v>3</v>
+      </c>
+      <c r="B44" t="s">
+        <v>1512</v>
+      </c>
+      <c r="D44">
+        <v>1</v>
+      </c>
+      <c r="E44" t="str">
+        <v xml:space="preserve">    - xform/e([48?])/$1/    # 稽</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" t="s">
+        <v>1079</v>
+      </c>
+      <c r="B45" t="s">
+        <v>1513</v>
+      </c>
+      <c r="D45">
+        <v>1</v>
+      </c>
+      <c r="E45" t="str">
+        <v xml:space="preserve">    - xform/o([48?])/oh$1/    # 高</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46">
+        <v>2</v>
+      </c>
+      <c r="B46" t="s">
+        <v>1514</v>
+      </c>
+      <c r="D46">
+        <v>1</v>
+      </c>
+      <c r="E46" t="str">
+        <v xml:space="preserve">    - xform/u([48?])/uh$1/    # 艍</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" t="s">
+        <v>1079</v>
+      </c>
+      <c r="B47" t="s">
+        <v>1515</v>
+      </c>
+      <c r="D47">
+        <v>1</v>
+      </c>
+      <c r="E47" t="str">
+        <v xml:space="preserve">    - xform/a([48?])/ah$1/    # 膠</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48">
+        <v>2</v>
+      </c>
+      <c r="B48" t="s">
+        <v>1516</v>
+      </c>
+      <c r="D48">
+        <v>1</v>
+      </c>
+      <c r="E48" t="str">
+        <v xml:space="preserve">    - xform/i([48?])/ih$1/    # 居</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" t="s">
+        <v>1079</v>
+      </c>
+      <c r="B49" t="s">
+        <v>1517</v>
+      </c>
+      <c r="D49">
+        <v>1</v>
+      </c>
+      <c r="E49" t="str">
+        <v xml:space="preserve">    - xform/m([48?])/mh$1/    # 姆</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50">
+        <v>2</v>
+      </c>
+      <c r="B50" t="s">
+        <v>1518</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" t="s">
+        <v>1079</v>
+      </c>
+      <c r="B51" t="s">
+        <v>1519</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52">
+        <v>3</v>
+      </c>
+      <c r="B52" t="s">
+        <v>1520</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" t="s">
+        <v>1079</v>
+      </c>
+      <c r="B53" t="s">
+        <v>1521</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54">
+        <v>1</v>
+      </c>
+      <c r="B54" t="s">
+        <v>1522</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" t="s">
+        <v>1079</v>
+      </c>
+      <c r="B55" t="s">
+        <v>1523</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56">
+        <v>1</v>
+      </c>
+      <c r="B56" t="s">
+        <v>1524</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" t="s">
+        <v>1079</v>
+      </c>
+      <c r="B57" t="s">
+        <v>1525</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58">
+        <v>1</v>
+      </c>
+      <c r="B58" t="s">
+        <v>1526</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" t="s">
+        <v>1079</v>
+      </c>
+      <c r="B59" t="s">
+        <v>1527</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60">
+        <v>2</v>
+      </c>
+      <c r="B60" t="s">
+        <v>1528</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" t="s">
+        <v>1079</v>
+      </c>
+      <c r="B61" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62">
+        <v>3</v>
+      </c>
+      <c r="B62" t="s">
+        <v>1529</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" t="s">
+        <v>1079</v>
+      </c>
+      <c r="B63" t="s">
+        <v>1530</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64">
+        <v>4</v>
+      </c>
+      <c r="B64" t="s">
+        <v>1531</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2">
+      <c r="A65" t="s">
+        <v>1079</v>
+      </c>
+      <c r="B65" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2">
+      <c r="A66">
+        <v>2</v>
+      </c>
+      <c r="B66" t="s">
+        <v>1532</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2">
+      <c r="A67" t="s">
+        <v>1079</v>
+      </c>
+      <c r="B67" t="s">
+        <v>1533</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2">
+      <c r="A68">
+        <v>3</v>
+      </c>
+      <c r="B68" t="s">
+        <v>1534</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2">
+      <c r="A69" t="s">
+        <v>1079</v>
+      </c>
+      <c r="B69" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2">
+      <c r="A70">
+        <v>4</v>
+      </c>
+      <c r="B70" t="s">
+        <v>1535</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2">
+      <c r="A71" t="s">
+        <v>1079</v>
+      </c>
+      <c r="B71" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2">
+      <c r="A72">
+        <v>4</v>
+      </c>
+      <c r="B72" t="s">
+        <v>1536</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2">
+      <c r="A73" t="s">
+        <v>1079</v>
+      </c>
+      <c r="B73" t="s">
+        <v>1537</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2">
+      <c r="A74">
+        <v>4</v>
+      </c>
+      <c r="B74" t="s">
+        <v>1538</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2">
+      <c r="A75" t="s">
+        <v>1079</v>
+      </c>
+      <c r="B75" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2">
+      <c r="A76">
+        <v>2</v>
+      </c>
+      <c r="B76" t="s">
+        <v>1539</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2">
+      <c r="A77" t="s">
+        <v>1079</v>
+      </c>
+      <c r="B77" t="s">
+        <v>1540</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2">
+      <c r="A78" t="s">
+        <v>1079</v>
+      </c>
+      <c r="B78" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2">
+      <c r="A79" t="s">
+        <v>1079</v>
+      </c>
+      <c r="B79" t="s">
+        <v>1541</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2">
+      <c r="A80">
+        <v>4</v>
+      </c>
+      <c r="B80" t="s">
+        <v>1542</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2">
+      <c r="A81" t="s">
+        <v>1079</v>
+      </c>
+      <c r="B81" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2">
+      <c r="A82">
+        <v>3</v>
+      </c>
+      <c r="B82" t="s">
+        <v>1543</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2">
+      <c r="A83" t="s">
+        <v>1079</v>
+      </c>
+      <c r="B83" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2">
+      <c r="A84">
+        <v>1</v>
+      </c>
+      <c r="B84" t="s">
+        <v>1544</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2">
+      <c r="A85" t="s">
+        <v>1079</v>
+      </c>
+      <c r="B85" t="s">
+        <v>1545</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2">
+      <c r="A86">
+        <v>4</v>
+      </c>
+      <c r="B86" t="s">
+        <v>1546</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2">
+      <c r="A87" t="s">
+        <v>1079</v>
+      </c>
+      <c r="B87" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2">
+      <c r="A88">
+        <v>5</v>
+      </c>
+      <c r="B88" t="s">
+        <v>1547</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2">
+      <c r="A89" t="s">
+        <v>1079</v>
+      </c>
+      <c r="B89" t="s">
+        <v>1548</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2">
+      <c r="A90" t="s">
+        <v>1079</v>
+      </c>
+      <c r="B90" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2">
+      <c r="A91" t="s">
+        <v>1079</v>
+      </c>
+      <c r="B91" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2">
+      <c r="A92">
+        <v>5</v>
+      </c>
+      <c r="B92" t="s">
+        <v>1549</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2">
+      <c r="A93" t="s">
+        <v>1079</v>
+      </c>
+      <c r="B93" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2">
+      <c r="A94">
+        <v>2</v>
+      </c>
+      <c r="B94" t="s">
+        <v>1550</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2">
+      <c r="A95" t="s">
+        <v>1079</v>
+      </c>
+      <c r="B95" t="s">
+        <v>1551</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2">
+      <c r="A96" t="s">
+        <v>1079</v>
+      </c>
+      <c r="B96" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2">
+      <c r="A97" t="s">
+        <v>1079</v>
+      </c>
+      <c r="B97" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2">
+      <c r="A98" t="s">
+        <v>1079</v>
+      </c>
+      <c r="B98" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2">
+      <c r="A99" t="s">
+        <v>1079</v>
+      </c>
+      <c r="B99" t="s">
+        <v>1552</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2">
+      <c r="A100">
+        <v>4</v>
+      </c>
+      <c r="B100" t="s">
+        <v>1553</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2">
+      <c r="A101" t="s">
+        <v>1079</v>
+      </c>
+      <c r="B101" t="s">
+        <v>1554</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2">
+      <c r="A102">
+        <v>2</v>
+      </c>
+      <c r="B102" t="s">
+        <v>1555</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2">
+      <c r="A103">
+        <v>2</v>
+      </c>
+      <c r="B103" t="s">
+        <v>1556</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2">
+      <c r="A104" t="s">
+        <v>1079</v>
+      </c>
+      <c r="B104" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+  </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:B104">
+    <sortCondition descending="1" ref="B2:B104"/>
+  </sortState>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08C13F26-C902-4A86-A09F-2B9413421306}">
   <dimension ref="A1:Y83"/>
   <sheetFormatPr defaultRowHeight="22.5"/>
@@ -27224,17 +30743,17 @@
       <c r="Y3" s="50"/>
     </row>
     <row r="4" spans="1:25">
-      <c r="A4" s="96"/>
-      <c r="B4" s="107" t="s">
+      <c r="A4" s="95"/>
+      <c r="B4" s="103" t="s">
         <v>1056</v>
       </c>
-      <c r="C4" s="107" t="s">
+      <c r="C4" s="103" t="s">
         <v>1391</v>
       </c>
-      <c r="D4" s="107" t="s">
+      <c r="D4" s="103" t="s">
         <v>1057</v>
       </c>
-      <c r="E4" s="107" t="s">
+      <c r="E4" s="103" t="s">
         <v>40</v>
       </c>
       <c r="F4" s="49" t="s">
@@ -28126,7 +31645,7 @@
       <c r="C18" s="50" t="s">
         <v>78</v>
       </c>
-      <c r="D18" s="97" t="str" cm="1">
+      <c r="D18" s="96" t="str" cm="1">
         <f t="array" ref="D18" xml:space="preserve"> IF( INDEX(韻母表[國際音標2], MATCH(TRUE, EXACT($C18, 韻母表[十五音]), 0))&lt;&gt;"",  INDEX(韻母表[國際音標2], MATCH(TRUE, EXACT($C18, 韻母表[十五音]), 0)),  INDEX(韻母表[國際音標], MATCH(TRUE, EXACT($C18, 韻母表[十五音]), 0)))</f>
         <v>ɛŋ</v>
       </c>
@@ -28195,7 +31714,7 @@
       <c r="C19" s="50" t="s">
         <v>79</v>
       </c>
-      <c r="D19" s="97" t="str" cm="1">
+      <c r="D19" s="96" t="str" cm="1">
         <f t="array" ref="D19" xml:space="preserve"> IF( INDEX(韻母表[國際音標2], MATCH(TRUE, EXACT($C19, 韻母表[十五音]), 0))&lt;&gt;"",  INDEX(韻母表[國際音標2], MATCH(TRUE, EXACT($C19, 韻母表[十五音]), 0)),  INDEX(韻母表[國際音標], MATCH(TRUE, EXACT($C19, 韻母表[十五音]), 0)))</f>
         <v>ɛk</v>
       </c>
@@ -28398,7 +31917,7 @@
       <c r="C22" s="50" t="s">
         <v>82</v>
       </c>
-      <c r="D22" s="97" t="str" cm="1">
+      <c r="D22" s="96" t="str" cm="1">
         <f t="array" ref="D22" xml:space="preserve"> IF( INDEX(韻母表[國際音標2], MATCH(TRUE, EXACT($C22, 韻母表[十五音]), 0))&lt;&gt;"",  INDEX(韻母表[國際音標2], MATCH(TRUE, EXACT($C22, 韻母表[十五音]), 0)),  INDEX(韻母表[國際音標], MATCH(TRUE, EXACT($C22, 韻母表[十五音]), 0)))</f>
         <v>ou</v>
       </c>
@@ -28640,7 +32159,7 @@
       <c r="C26" s="50" t="s">
         <v>86</v>
       </c>
-      <c r="D26" s="97" t="str" cm="1">
+      <c r="D26" s="96" t="str" cm="1">
         <f t="array" ref="D26" xml:space="preserve"> IF( INDEX(韻母表[國際音標2], MATCH(TRUE, EXACT($C26, 韻母表[十五音]), 0))&lt;&gt;"",  INDEX(韻母表[國際音標2], MATCH(TRUE, EXACT($C26, 韻母表[十五音]), 0)),  INDEX(韻母表[國際音標], MATCH(TRUE, EXACT($C26, 韻母表[十五音]), 0)))</f>
         <v>ei</v>
       </c>
@@ -30100,7 +33619,7 @@
       <c r="C48" s="50" t="s">
         <v>110</v>
       </c>
-      <c r="D48" s="97" t="str" cm="1">
+      <c r="D48" s="96" t="str" cm="1">
         <f t="array" ref="D48" xml:space="preserve"> IF( INDEX(韻母表[國際音標2], MATCH(TRUE, EXACT($C48, 韻母表[十五音]), 0))&lt;&gt;"",  INDEX(韻母表[國際音標2], MATCH(TRUE, EXACT($C48, 韻母表[十五音]), 0)),  INDEX(韻母表[國際音標], MATCH(TRUE, EXACT($C48, 韻母表[十五音]), 0)))</f>
         <v>uei</v>
       </c>
@@ -30169,7 +33688,7 @@
       <c r="C49" s="50" t="s">
         <v>111</v>
       </c>
-      <c r="D49" s="97" t="str" cm="1">
+      <c r="D49" s="96" t="str" cm="1">
         <f t="array" ref="D49" xml:space="preserve"> IF( INDEX(韻母表[國際音標2], MATCH(TRUE, EXACT($C49, 韻母表[十五音]), 0))&lt;&gt;"",  INDEX(韻母表[國際音標2], MATCH(TRUE, EXACT($C49, 韻母表[十五音]), 0)),  INDEX(韻母表[國際音標], MATCH(TRUE, EXACT($C49, 韻母表[十五音]), 0)))</f>
         <v>ueiʔ</v>
       </c>
@@ -30815,7 +34334,7 @@
       <c r="C59" s="50" t="s">
         <v>122</v>
       </c>
-      <c r="D59" s="97" t="str" cm="1">
+      <c r="D59" s="96" t="str" cm="1">
         <f t="array" ref="D59" xml:space="preserve"> IF( INDEX(韻母表[國際音標2], MATCH(TRUE, EXACT($C59, 韻母表[十五音]), 0))&lt;&gt;"",  INDEX(韻母表[國際音標2], MATCH(TRUE, EXACT($C59, 韻母表[十五音]), 0)),  INDEX(韻母表[國際音標], MATCH(TRUE, EXACT($C59, 韻母表[十五音]), 0)))</f>
         <v>ɛ̃</v>
       </c>
@@ -30878,7 +34397,7 @@
       <c r="C60" s="50" t="s">
         <v>123</v>
       </c>
-      <c r="D60" s="97" t="str" cm="1">
+      <c r="D60" s="96" t="str" cm="1">
         <f t="array" ref="D60" xml:space="preserve"> IF( INDEX(韻母表[國際音標2], MATCH(TRUE, EXACT($C60, 韻母表[十五音]), 0))&lt;&gt;"",  INDEX(韻母表[國際音標2], MATCH(TRUE, EXACT($C60, 韻母表[十五音]), 0)),  INDEX(韻母表[國際音標], MATCH(TRUE, EXACT($C60, 韻母表[十五音]), 0)))</f>
         <v>ɛ̃ʔ</v>
       </c>
@@ -31517,7 +35036,7 @@
       <c r="C71" s="50" t="s">
         <v>142</v>
       </c>
-      <c r="D71" s="97" t="str" cm="1">
+      <c r="D71" s="96" t="str" cm="1">
         <f t="array" ref="D71" xml:space="preserve"> IF( INDEX(韻母表[國際音標2], MATCH(TRUE, EXACT($C71, 韻母表[十五音]), 0))&lt;&gt;"",  INDEX(韻母表[國際音標2], MATCH(TRUE, EXACT($C71, 韻母表[十五音]), 0)),  INDEX(韻母表[國際音標], MATCH(TRUE, EXACT($C71, 韻母表[十五音]), 0)))</f>
         <v>õu</v>
       </c>
@@ -31838,7 +35357,7 @@
       <c r="C78" s="50" t="s">
         <v>159</v>
       </c>
-      <c r="D78" s="97" t="str" cm="1">
+      <c r="D78" s="96" t="str" cm="1">
         <f t="array" ref="D78" xml:space="preserve"> IF( INDEX(韻母表[國際音標2], MATCH(TRUE, EXACT($C78, 韻母表[十五音]), 0))&lt;&gt;"",  INDEX(韻母表[國際音標2], MATCH(TRUE, EXACT($C78, 韻母表[十五音]), 0)),  INDEX(韻母表[國際音標], MATCH(TRUE, EXACT($C78, 韻母表[十五音]), 0)))</f>
         <v>ɔ̃ʔ</v>
       </c>
@@ -32136,7 +35655,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{835735A7-A696-418F-922F-4B8C378CF4A0}">
   <dimension ref="A1:Z83"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
@@ -40459,7 +43978,7 @@
   </sortState>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="E5:Z83">
-    <cfRule type="expression" dxfId="47" priority="2">
+    <cfRule type="expression" dxfId="0" priority="2">
       <formula>E5=""</formula>
     </cfRule>
   </conditionalFormatting>
@@ -40467,7 +43986,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CBA6DC20-E2C0-4283-A3A5-F96BEC7340DC}">
   <dimension ref="B1:Y79"/>
   <sheetFormatPr defaultRowHeight="22.5"/>

--- a/docs/105_十五音音節表.xlsx
+++ b/docs/105_十五音音節表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AlanJui\work\rime-tlpa\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A156D487-C636-445D-BAFB-AD72F3EF71A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD9F2F09-0444-4F7C-99F9-4BFE24C6161A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="15720" activeTab="3" xr2:uid="{5BF56E62-E34C-4B16-A26D-70A9456E8A67}"/>
   </bookViews>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -68,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5169" uniqueCount="1557">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5189" uniqueCount="1540">
   <si>
     <t>十五音</t>
   </si>
@@ -5280,186 +5280,102 @@
     <t xml:space="preserve">    - xform/un([48?])/ut$1/    # 君</t>
   </si>
   <si>
-    <t xml:space="preserve">    - xform/ut([48?])/ian$1/    # 君</t>
-  </si>
-  <si>
     <t xml:space="preserve">    - xform/ian([48?])/iat$1/    # 堅</t>
   </si>
   <si>
-    <t xml:space="preserve">    - xform/iat([48?])/im$1/    # 堅</t>
-  </si>
-  <si>
     <t xml:space="preserve">    - xform/im([48?])/ip$1/    # 金</t>
   </si>
   <si>
-    <t xml:space="preserve">    - xform/ip([48?])/ui$1/    # 金</t>
-  </si>
-  <si>
     <t xml:space="preserve">    - xform/ui([48?])/$1/    # 規</t>
   </si>
   <si>
     <t xml:space="preserve">    - xform/ee([48?])/eeh$1/    # 嘉</t>
   </si>
   <si>
-    <t xml:space="preserve">    - xform/eeh([48?])/an$1/    # 嘉</t>
-  </si>
-  <si>
     <t xml:space="preserve">    - xform/an([48?])/at$1/    # 干</t>
   </si>
   <si>
-    <t xml:space="preserve">    - xform/at([48?])/ong$1/    # 干</t>
-  </si>
-  <si>
     <t xml:space="preserve">    - xform/ong([48?])/ok$1/    # 公</t>
   </si>
   <si>
-    <t xml:space="preserve">    - xform/ok([48?])/uai$1/    # 公</t>
-  </si>
-  <si>
     <t xml:space="preserve">    - xform/uai([48?])/uaih$1/    # 乖</t>
   </si>
   <si>
-    <t xml:space="preserve">    - xform/uaih([48?])/ing$1/    # 乖</t>
-  </si>
-  <si>
     <t xml:space="preserve">    - xform/ing([48?])/ik$1/    # 經</t>
   </si>
   <si>
-    <t xml:space="preserve">    - xform/ik([48?])/uan$1/    # 經</t>
-  </si>
-  <si>
     <t xml:space="preserve">    - xform/uan([48?])/uat$1/    # 觀</t>
   </si>
   <si>
-    <t xml:space="preserve">    - xform/uat([48?])/oo$1/    # 觀</t>
-  </si>
-  <si>
     <t xml:space="preserve">    - xform/oo([48?])/ooh$1/    # 沽</t>
   </si>
   <si>
-    <t xml:space="preserve">    - xform/ooh([48?])/iau$1/    # 沽</t>
-  </si>
-  <si>
     <t xml:space="preserve">    - xform/iau([48?])/iauh$1/    # 嬌</t>
   </si>
   <si>
-    <t xml:space="preserve">    - xform/iauh([48?])/e$1/    # 嬌</t>
-  </si>
-  <si>
     <t xml:space="preserve">    - xform/e([48?])/$1/    # 稽</t>
   </si>
   <si>
     <t xml:space="preserve">    - xform/iong([48?])/iok$1/    # 恭</t>
   </si>
   <si>
-    <t xml:space="preserve">    - xform/iok([48?])/o$1/    # 恭</t>
-  </si>
-  <si>
     <t xml:space="preserve">    - xform/o([48?])/oh$1/    # 高</t>
   </si>
   <si>
-    <t xml:space="preserve">    - xform/oh([48?])/ai$1/    # 高</t>
-  </si>
-  <si>
     <t xml:space="preserve">    - xform/ai([48?])/$1/    # 皆</t>
   </si>
   <si>
     <t xml:space="preserve">    - xform/in([48?])/it$1/    # 巾</t>
   </si>
   <si>
-    <t xml:space="preserve">    - xform/it([48?])/iang$1/    # 巾</t>
-  </si>
-  <si>
     <t xml:space="preserve">    - xform/iang([48?])/iak$1/    # 姜</t>
   </si>
   <si>
-    <t xml:space="preserve">    - xform/iak([48?])/am$1/    # 姜</t>
-  </si>
-  <si>
     <t xml:space="preserve">    - xform/am([48?])/ap$1/    # 甘</t>
   </si>
   <si>
-    <t xml:space="preserve">    - xform/ap([48?])/ua$1/    # 甘</t>
-  </si>
-  <si>
     <t xml:space="preserve">    - xform/ua([48?])/uah$1/    # 瓜</t>
   </si>
   <si>
-    <t xml:space="preserve">    - xform/uah([48?])/ang$1/    # 瓜</t>
-  </si>
-  <si>
     <t xml:space="preserve">    - xform/ang([48?])/ak$1/    # 江</t>
   </si>
   <si>
-    <t xml:space="preserve">    - xform/ak([48?])/iam$1/    # 江</t>
-  </si>
-  <si>
     <t xml:space="preserve">    - xform/iam([48?])/iap$1/    # 兼</t>
   </si>
   <si>
-    <t xml:space="preserve">    - xform/iap([48?])/au$1/    # 兼</t>
-  </si>
-  <si>
     <t xml:space="preserve">    - xform/au([48?])/auh$1/    # 交</t>
   </si>
   <si>
-    <t xml:space="preserve">    - xform/auh([48?])/ia$1/    # 交</t>
-  </si>
-  <si>
     <t xml:space="preserve">    - xform/ia([48?])/iah$1/    # 迦</t>
   </si>
   <si>
-    <t xml:space="preserve">    - xform/iah([48?])/ue$1/    # 迦</t>
-  </si>
-  <si>
     <t xml:space="preserve">    - xform/ue([48?])/ueh$1/    # 檜</t>
   </si>
   <si>
-    <t xml:space="preserve">    - xform/ueh([48?])/ann$1/    # 檜</t>
-  </si>
-  <si>
     <t xml:space="preserve">    - xform/ann([48?])/annh$1/    # 監</t>
   </si>
   <si>
-    <t xml:space="preserve">    - xform/annh([48?])/u$1/    # 監</t>
-  </si>
-  <si>
     <t xml:space="preserve">    - xform/u([48?])/uh$1/    # 艍</t>
   </si>
   <si>
-    <t xml:space="preserve">    - xform/uh([48?])/a$1/    # 艍</t>
-  </si>
-  <si>
     <t xml:space="preserve">    - xform/a([48?])/ah$1/    # 膠</t>
   </si>
   <si>
-    <t xml:space="preserve">    - xform/ah([48?])/i$1/    # 膠</t>
-  </si>
-  <si>
     <t xml:space="preserve">    - xform/i([48?])/ih$1/    # 居</t>
   </si>
   <si>
-    <t xml:space="preserve">    - xform/ih([48?])/iu$1/    # 居</t>
-  </si>
-  <si>
     <t xml:space="preserve">    - xform/iu([48?])/$1/    # 丩</t>
   </si>
   <si>
     <t xml:space="preserve">    - xform/enn([48?])/ennh$1/    # 更</t>
   </si>
   <si>
-    <t xml:space="preserve">    - xform/ennh([48?])/uinn$1/    # 更</t>
-  </si>
-  <si>
     <t xml:space="preserve">    - xform/uinn([48?])/$1/    # 褌</t>
   </si>
   <si>
     <t xml:space="preserve">    - xform/io([48?])/ioh$1/    # 茄</t>
   </si>
   <si>
-    <t xml:space="preserve">    - xform/ioh([48?])/inn$1/    # 茄</t>
-  </si>
-  <si>
     <t xml:space="preserve">    - xform/inn([48?])/$1/    # 梔</t>
   </si>
   <si>
@@ -5469,21 +5385,12 @@
     <t xml:space="preserve">    - xform/iann([48?])/iannh$1/    # 驚</t>
   </si>
   <si>
-    <t xml:space="preserve">    - xform/iannh([48?])/uann$1/    # 驚</t>
-  </si>
-  <si>
     <t xml:space="preserve">    - xform/uann([48?])/$1/    # 官</t>
   </si>
   <si>
     <t xml:space="preserve">    - xform/ng([48?])/ngh$1/    # 鋼</t>
   </si>
   <si>
-    <t xml:space="preserve">    - xform/ngh([48?])/$1/    # 鋼</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    - xform/eh([48?])/ainn$1/    # 伽</t>
-  </si>
-  <si>
     <t xml:space="preserve">    - xform/ainn([48?])/$1/    # 閒</t>
   </si>
   <si>
@@ -5493,40 +5400,101 @@
     <t xml:space="preserve">    - xform/m([48?])/mh$1/    # 姆</t>
   </si>
   <si>
-    <t xml:space="preserve">    - xform/mh([48?])/uang$1/    # 姆</t>
-  </si>
-  <si>
     <t xml:space="preserve">    - xform/uang([48?])/$1/    # 光</t>
   </si>
   <si>
     <t xml:space="preserve">    - xform/uainn([48?])/uainnh$1/    # 閂</t>
   </si>
   <si>
-    <t xml:space="preserve">    - xform/uainnh([48?])/$1/    # 閂</t>
-  </si>
-  <si>
     <t xml:space="preserve">    - xform/iaunn([48?])/$1/    # 嘄</t>
   </si>
   <si>
     <t xml:space="preserve">    - xform/om([48?])/op$1/    # 箴</t>
   </si>
   <si>
-    <t xml:space="preserve">    - xform/op([48?])/$1/    # 箴</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    - xform/onnh([48?])/iunn$1/    # 扛</t>
-  </si>
-  <si>
     <t xml:space="preserve">    - xform/iunn([48?])/iunnh$1/    # 牛</t>
   </si>
   <si>
-    <t xml:space="preserve">    - xform/iunnh([48?])/er$1/    # 牛</t>
-  </si>
-  <si>
     <t xml:space="preserve">    - xform/er([48?])/ir$1/    # </t>
   </si>
   <si>
     <t xml:space="preserve">    - xform/ir([48?])/$1/    # </t>
+  </si>
+  <si>
+    <t>TL</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>BPM2</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>iok</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>iook</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>oh</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>orh</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>o</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>or</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ioh</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>iorh</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>io</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ior</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ionn</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ioonn</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>onn</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>oonn</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>om</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>oom</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>oop</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -6316,24 +6284,31 @@
     <xf numFmtId="0" fontId="39" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
     <cellStyle name="一般 2" xfId="1" xr:uid="{E57FFF29-A59B-46E2-A496-66E529F383CC}"/>
   </cellStyles>
-  <dxfs count="71">
+  <dxfs count="72">
     <dxf>
       <fill>
         <patternFill>
           <bgColor theme="2"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFFF0000"/>
+      </font>
     </dxf>
     <dxf>
       <font>
@@ -6857,22 +6832,22 @@
     <dxf>
       <border outline="0">
         <bottom style="thin">
-          <color rgb="FFBFBFBF"/>
+          <color theme="0" tint="-0.24994659260841701"/>
         </bottom>
       </border>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FF000000"/>
-          <bgColor rgb="FFFFFFFF"/>
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <border>
         <bottom style="thin">
-          <color rgb="FF000000"/>
+          <color indexed="64"/>
         </bottom>
       </border>
     </dxf>
@@ -7404,22 +7379,22 @@
     <dxf>
       <border outline="0">
         <bottom style="thin">
-          <color theme="0" tint="-0.24994659260841701"/>
+          <color rgb="FFBFBFBF"/>
         </bottom>
       </border>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
+          <fgColor rgb="FF000000"/>
+          <bgColor rgb="FFFFFFFF"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <border>
         <bottom style="thin">
-          <color indexed="64"/>
+          <color rgb="FF000000"/>
         </bottom>
       </border>
     </dxf>
@@ -7484,73 +7459,73 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D4D53CAA-1AC5-435B-8EFA-F8A8BD117A7E}" name="聲母表" displayName="聲母表" ref="A1:M23" totalsRowShown="0" headerRowDxfId="53" headerRowBorderDxfId="52" tableBorderDxfId="51" totalsRowBorderDxfId="50">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D4D53CAA-1AC5-435B-8EFA-F8A8BD117A7E}" name="聲母表" displayName="聲母表" ref="A1:M23" totalsRowShown="0" headerRowDxfId="54" headerRowBorderDxfId="53" tableBorderDxfId="52" totalsRowBorderDxfId="51">
   <autoFilter ref="A1:M23" xr:uid="{D4D53CAA-1AC5-435B-8EFA-F8A8BD117A7E}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:M23">
     <sortCondition ref="B2:B23"/>
   </sortState>
   <tableColumns count="13">
-    <tableColumn id="1" xr3:uid="{C83BAA32-BD80-4A6A-B041-EFB4E5BF0EAD}" name="序號" dataDxfId="49"/>
-    <tableColumn id="13" xr3:uid="{F49FED34-8A68-43B1-A51D-B6550AE47953}" name="音序" dataDxfId="48"/>
-    <tableColumn id="2" xr3:uid="{A6E193EA-549C-4029-8823-9DFE17442FF1}" name="漢字例" dataDxfId="47"/>
+    <tableColumn id="1" xr3:uid="{C83BAA32-BD80-4A6A-B041-EFB4E5BF0EAD}" name="序號" dataDxfId="50"/>
+    <tableColumn id="13" xr3:uid="{F49FED34-8A68-43B1-A51D-B6550AE47953}" name="音序" dataDxfId="49"/>
+    <tableColumn id="2" xr3:uid="{A6E193EA-549C-4029-8823-9DFE17442FF1}" name="漢字例" dataDxfId="48"/>
     <tableColumn id="3" xr3:uid="{6A134241-ADBE-4BD1-A5C6-D00613EF82BB}" name="十五音"/>
     <tableColumn id="14" xr3:uid="{E372684C-80C8-4FBB-8980-C9CF51A93857}" name="新十五音"/>
-    <tableColumn id="5" xr3:uid="{D62696E3-AB0E-4D6E-B91E-A6119DD3697B}" name="國際音標" dataDxfId="46"/>
+    <tableColumn id="5" xr3:uid="{D62696E3-AB0E-4D6E-B91E-A6119DD3697B}" name="國際音標" dataDxfId="47"/>
     <tableColumn id="4" xr3:uid="{9014A3FB-03BF-4D2A-833F-6D18B2FC48DE}" name="台羅拼音"/>
-    <tableColumn id="7" xr3:uid="{DE46D56A-2F6F-460E-97EB-6221DBF36190}" name="台語音標" dataDxfId="45"/>
-    <tableColumn id="8" xr3:uid="{6416C7B5-02F3-4A4B-A59B-F5CCC29DA4BC}" name="白話字" dataDxfId="44"/>
-    <tableColumn id="9" xr3:uid="{499810EC-AD1D-46F1-B997-07B17DA95245}" name="閩拼方案" dataDxfId="43"/>
-    <tableColumn id="10" xr3:uid="{5D3D9CE2-D240-4ADB-A8EC-5DF1AD126A55}" name="注音二式" dataDxfId="42"/>
-    <tableColumn id="11" xr3:uid="{E1D819DB-0A80-42E2-A97A-E02BCFDCB063}" name="方音符號" dataDxfId="41"/>
-    <tableColumn id="12" xr3:uid="{F009D45F-2383-4AB9-BA72-A06F1F14EE9E}" name="台語注音" dataDxfId="40"/>
+    <tableColumn id="7" xr3:uid="{DE46D56A-2F6F-460E-97EB-6221DBF36190}" name="台語音標" dataDxfId="46"/>
+    <tableColumn id="8" xr3:uid="{6416C7B5-02F3-4A4B-A59B-F5CCC29DA4BC}" name="白話字" dataDxfId="45"/>
+    <tableColumn id="9" xr3:uid="{499810EC-AD1D-46F1-B997-07B17DA95245}" name="閩拼方案" dataDxfId="44"/>
+    <tableColumn id="10" xr3:uid="{5D3D9CE2-D240-4ADB-A8EC-5DF1AD126A55}" name="注音二式" dataDxfId="43"/>
+    <tableColumn id="11" xr3:uid="{E1D819DB-0A80-42E2-A97A-E02BCFDCB063}" name="方音符號" dataDxfId="42"/>
+    <tableColumn id="12" xr3:uid="{F009D45F-2383-4AB9-BA72-A06F1F14EE9E}" name="台語注音" dataDxfId="41"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{23E007DD-5182-4B78-80DA-A6AB6CA14806}" name="韻母表" displayName="韻母表" ref="A1:M101" totalsRowShown="0" headerRowDxfId="70" dataDxfId="68" headerRowBorderDxfId="69" tableBorderDxfId="67">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{23E007DD-5182-4B78-80DA-A6AB6CA14806}" name="韻母表" displayName="韻母表" ref="A1:M101" totalsRowShown="0" headerRowDxfId="40" dataDxfId="38" headerRowBorderDxfId="39" tableBorderDxfId="37">
   <autoFilter ref="A1:M101" xr:uid="{23E007DD-5182-4B78-80DA-A6AB6CA14806}"/>
   <tableColumns count="13">
-    <tableColumn id="1" xr3:uid="{89688CC6-39FE-4435-8344-AAA347FCBED4}" name="序號" dataDxfId="66"/>
-    <tableColumn id="5" xr3:uid="{8A21DB38-57E0-482B-95FC-B597347A8BDE}" name="韻序" dataDxfId="65">
+    <tableColumn id="1" xr3:uid="{89688CC6-39FE-4435-8344-AAA347FCBED4}" name="序號" dataDxfId="36"/>
+    <tableColumn id="5" xr3:uid="{8A21DB38-57E0-482B-95FC-B597347A8BDE}" name="韻序" dataDxfId="35">
       <calculatedColumnFormula xml:space="preserve"> IF(MOD(韻母表[[#This Row],[序號]],2)=0, 韻母表[[#This Row],[序號]]/2, ROUNDUP(韻母表[[#This Row],[序號]]/2,0))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{C94EAE18-8E51-4E6B-AD98-90C9372F5188}" name="漢字例" dataDxfId="64"/>
-    <tableColumn id="3" xr3:uid="{2C1D54ED-CBE3-4710-8C55-0AC6BB332524}" name="十五音" dataDxfId="63"/>
-    <tableColumn id="6" xr3:uid="{9CAF41C9-1F52-4C5E-8A5F-0F0DECF6DB84}" name="國際音標" dataDxfId="62"/>
-    <tableColumn id="7" xr3:uid="{6F37C033-2A03-4BC2-AB1F-B6A6D6E849EF}" name="國際音標2" dataDxfId="61"/>
-    <tableColumn id="4" xr3:uid="{F38AD89D-9FC9-4519-A8D2-EEB6952EEAC1}" name="台羅拼音" dataDxfId="60"/>
-    <tableColumn id="8" xr3:uid="{E2316195-DFB7-4D73-80AE-5AF5CB638098}" name="台語音標" dataDxfId="59"/>
-    <tableColumn id="9" xr3:uid="{0A03E710-B799-4430-BEA2-5ABB2CD0E1A1}" name="白話字" dataDxfId="58"/>
-    <tableColumn id="10" xr3:uid="{CA8E7716-EF33-499C-AAB0-A73DA24D6D6C}" name="閩拼方案" dataDxfId="57"/>
-    <tableColumn id="11" xr3:uid="{44C917DF-FD45-429A-B606-AA4AA4A2D8B8}" name="注音二式" dataDxfId="56"/>
-    <tableColumn id="12" xr3:uid="{A817EC74-78DE-4E34-8B25-4BAD35257767}" name="方音符號" dataDxfId="55"/>
-    <tableColumn id="13" xr3:uid="{156C12E1-9EC9-4906-AFF2-E587C73D5F0D}" name="台語注音" dataDxfId="54"/>
+    <tableColumn id="2" xr3:uid="{C94EAE18-8E51-4E6B-AD98-90C9372F5188}" name="漢字例" dataDxfId="34"/>
+    <tableColumn id="3" xr3:uid="{2C1D54ED-CBE3-4710-8C55-0AC6BB332524}" name="十五音" dataDxfId="33"/>
+    <tableColumn id="6" xr3:uid="{9CAF41C9-1F52-4C5E-8A5F-0F0DECF6DB84}" name="國際音標" dataDxfId="32"/>
+    <tableColumn id="7" xr3:uid="{6F37C033-2A03-4BC2-AB1F-B6A6D6E849EF}" name="國際音標2" dataDxfId="31"/>
+    <tableColumn id="4" xr3:uid="{F38AD89D-9FC9-4519-A8D2-EEB6952EEAC1}" name="台羅拼音" dataDxfId="30"/>
+    <tableColumn id="8" xr3:uid="{E2316195-DFB7-4D73-80AE-5AF5CB638098}" name="台語音標" dataDxfId="29"/>
+    <tableColumn id="9" xr3:uid="{0A03E710-B799-4430-BEA2-5ABB2CD0E1A1}" name="白話字" dataDxfId="28"/>
+    <tableColumn id="10" xr3:uid="{CA8E7716-EF33-499C-AAB0-A73DA24D6D6C}" name="閩拼方案" dataDxfId="27"/>
+    <tableColumn id="11" xr3:uid="{44C917DF-FD45-429A-B606-AA4AA4A2D8B8}" name="注音二式" dataDxfId="26"/>
+    <tableColumn id="12" xr3:uid="{A817EC74-78DE-4E34-8B25-4BAD35257767}" name="方音符號" dataDxfId="25"/>
+    <tableColumn id="13" xr3:uid="{156C12E1-9EC9-4906-AFF2-E587C73D5F0D}" name="台語注音" dataDxfId="24"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{445995B0-5C2F-4E9A-9739-9EF19DAF1BE1}" name="韻母表_4" displayName="韻母表_4" ref="A1:M104" totalsRowShown="0" headerRowDxfId="39" dataDxfId="37" headerRowBorderDxfId="38" tableBorderDxfId="36">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{445995B0-5C2F-4E9A-9739-9EF19DAF1BE1}" name="韻母表_4" displayName="韻母表_4" ref="A1:M104" totalsRowShown="0" headerRowDxfId="71" dataDxfId="69" headerRowBorderDxfId="70" tableBorderDxfId="68">
   <autoFilter ref="A1:M104" xr:uid="{23E007DD-5182-4B78-80DA-A6AB6CA14806}"/>
   <tableColumns count="13">
-    <tableColumn id="1" xr3:uid="{F8E86299-D90F-4592-ABDC-A0D652A239EA}" name="序號" dataDxfId="35"/>
-    <tableColumn id="5" xr3:uid="{24C83CBE-F51A-4055-8C74-B669A9FEC2BB}" name="韻序" dataDxfId="34">
+    <tableColumn id="1" xr3:uid="{F8E86299-D90F-4592-ABDC-A0D652A239EA}" name="序號" dataDxfId="67"/>
+    <tableColumn id="5" xr3:uid="{24C83CBE-F51A-4055-8C74-B669A9FEC2BB}" name="韻序" dataDxfId="66">
       <calculatedColumnFormula xml:space="preserve"> IF(MOD(韻母表_4[[#This Row],[序號]],2)=0, 韻母表_4[[#This Row],[序號]]/2, ROUNDUP(韻母表_4[[#This Row],[序號]]/2,0))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{0C6809DB-3017-45B3-875B-B288340415E9}" name="漢字例" dataDxfId="33"/>
-    <tableColumn id="3" xr3:uid="{EC7EADF7-9219-4A1D-BADE-5B70D687F5BE}" name="十五音" dataDxfId="32"/>
-    <tableColumn id="6" xr3:uid="{D42B0375-1395-4AA5-9592-400D314FF4A6}" name="國際音標" dataDxfId="31"/>
-    <tableColumn id="7" xr3:uid="{4FF66326-E3D3-4547-AACD-6FB02A224286}" name="國際音標2" dataDxfId="30"/>
-    <tableColumn id="4" xr3:uid="{14118607-EB7E-45B6-BA80-82DA602FEA15}" name="台羅拼音" dataDxfId="29"/>
-    <tableColumn id="8" xr3:uid="{B9308C5F-5158-4627-97E6-3777D062785C}" name="台語音標" dataDxfId="28"/>
-    <tableColumn id="9" xr3:uid="{4D40D46C-12FE-42D7-893F-D328F6CC3B39}" name="白話字" dataDxfId="27"/>
-    <tableColumn id="10" xr3:uid="{E55C9A5F-E95C-4F9C-95C2-8A79906E6908}" name="閩拼方案" dataDxfId="26"/>
-    <tableColumn id="11" xr3:uid="{2FF03B77-E51C-4F7F-AC68-ACCC6F92D98A}" name="注音二式" dataDxfId="25"/>
-    <tableColumn id="12" xr3:uid="{E71F16DA-D83F-43D8-B782-448D0B3850FD}" name="方音符號" dataDxfId="24"/>
-    <tableColumn id="13" xr3:uid="{AF2B7E9E-8412-4DD8-AF9D-37FEF1CA2005}" name="台語注音" dataDxfId="23"/>
+    <tableColumn id="2" xr3:uid="{0C6809DB-3017-45B3-875B-B288340415E9}" name="漢字例" dataDxfId="65"/>
+    <tableColumn id="3" xr3:uid="{EC7EADF7-9219-4A1D-BADE-5B70D687F5BE}" name="十五音" dataDxfId="64"/>
+    <tableColumn id="6" xr3:uid="{D42B0375-1395-4AA5-9592-400D314FF4A6}" name="國際音標" dataDxfId="63"/>
+    <tableColumn id="7" xr3:uid="{4FF66326-E3D3-4547-AACD-6FB02A224286}" name="國際音標2" dataDxfId="62"/>
+    <tableColumn id="4" xr3:uid="{14118607-EB7E-45B6-BA80-82DA602FEA15}" name="台羅拼音" dataDxfId="61"/>
+    <tableColumn id="8" xr3:uid="{B9308C5F-5158-4627-97E6-3777D062785C}" name="台語音標" dataDxfId="60"/>
+    <tableColumn id="9" xr3:uid="{4D40D46C-12FE-42D7-893F-D328F6CC3B39}" name="白話字" dataDxfId="59"/>
+    <tableColumn id="10" xr3:uid="{E55C9A5F-E95C-4F9C-95C2-8A79906E6908}" name="閩拼方案" dataDxfId="58"/>
+    <tableColumn id="11" xr3:uid="{2FF03B77-E51C-4F7F-AC68-ACCC6F92D98A}" name="注音二式" dataDxfId="57"/>
+    <tableColumn id="12" xr3:uid="{E71F16DA-D83F-43D8-B782-448D0B3850FD}" name="方音符號" dataDxfId="56"/>
+    <tableColumn id="13" xr3:uid="{AF2B7E9E-8412-4DD8-AF9D-37FEF1CA2005}" name="台語注音" dataDxfId="55"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -7920,12 +7895,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="44.25">
-      <c r="A1" s="104" t="s">
+      <c r="A1" s="105" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="104"/>
-      <c r="C1" s="104"/>
-      <c r="D1" s="104"/>
+      <c r="B1" s="105"/>
+      <c r="C1" s="105"/>
+      <c r="D1" s="105"/>
       <c r="E1" s="4" t="s">
         <v>18</v>
       </c>
@@ -7994,12 +7969,12 @@
       </c>
     </row>
     <row r="2" spans="1:26" ht="29.25">
-      <c r="A2" s="104" t="s">
+      <c r="A2" s="105" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="104"/>
-      <c r="C2" s="104"/>
-      <c r="D2" s="104"/>
+      <c r="B2" s="105"/>
+      <c r="C2" s="105"/>
+      <c r="D2" s="105"/>
       <c r="E2" s="8" t="s">
         <v>1</v>
       </c>
@@ -8068,12 +8043,12 @@
       </c>
     </row>
     <row r="3" spans="1:26" ht="29.25">
-      <c r="A3" s="104" t="s">
+      <c r="A3" s="105" t="s">
         <v>40</v>
       </c>
-      <c r="B3" s="104"/>
-      <c r="C3" s="104"/>
-      <c r="D3" s="104"/>
+      <c r="B3" s="105"/>
+      <c r="C3" s="105"/>
+      <c r="D3" s="105"/>
       <c r="E3" s="12"/>
       <c r="F3" s="12" t="s">
         <v>41</v>
@@ -18277,7 +18252,7 @@
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="E4:Z103">
-    <cfRule type="expression" dxfId="22" priority="1">
+    <cfRule type="expression" dxfId="23" priority="1">
       <formula>E4=""</formula>
     </cfRule>
   </conditionalFormatting>
@@ -23281,13 +23256,13 @@
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="A2:M101">
-    <cfRule type="expression" dxfId="21" priority="1">
+    <cfRule type="expression" dxfId="22" priority="1">
       <formula>MOD($B2,2)&lt;&gt;0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="20" priority="2">
+    <cfRule type="expression" dxfId="21" priority="2">
       <formula>MOD($A2,2)&lt;&gt;0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="19" priority="3">
+    <cfRule type="expression" dxfId="20" priority="3">
       <formula>MOD($A2,2)=0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -23300,7 +23275,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59C75227-57C4-4844-A39D-F2B25DB9903D}">
-  <dimension ref="A1:AD104"/>
+  <dimension ref="A1:AD115"/>
   <sheetFormatPr defaultRowHeight="22.5"/>
   <cols>
     <col min="1" max="2" width="8.125" customWidth="1"/>
@@ -23369,7 +23344,7 @@
       <c r="R1" t="s">
         <v>1402</v>
       </c>
-      <c r="S1" s="105" t="s">
+      <c r="S1" s="104" t="s">
         <v>1470</v>
       </c>
       <c r="T1" s="41" t="s">
@@ -29373,68 +29348,153 @@
         <v>1464</v>
       </c>
     </row>
+    <row r="106" spans="1:23">
+      <c r="P106" t="s">
+        <v>1521</v>
+      </c>
+      <c r="Q106" t="s">
+        <v>1522</v>
+      </c>
+    </row>
+    <row r="107" spans="1:23">
+      <c r="P107" t="s">
+        <v>1523</v>
+      </c>
+      <c r="Q107" t="s">
+        <v>1524</v>
+      </c>
+    </row>
+    <row r="108" spans="1:23">
+      <c r="P108" t="s">
+        <v>1525</v>
+      </c>
+      <c r="Q108" t="s">
+        <v>1526</v>
+      </c>
+    </row>
+    <row r="109" spans="1:23">
+      <c r="P109" t="s">
+        <v>1527</v>
+      </c>
+      <c r="Q109" t="s">
+        <v>1528</v>
+      </c>
+    </row>
+    <row r="110" spans="1:23">
+      <c r="P110" t="s">
+        <v>1529</v>
+      </c>
+      <c r="Q110" t="s">
+        <v>1530</v>
+      </c>
+    </row>
+    <row r="111" spans="1:23">
+      <c r="P111" t="s">
+        <v>1531</v>
+      </c>
+      <c r="Q111" t="s">
+        <v>1532</v>
+      </c>
+    </row>
+    <row r="112" spans="1:23">
+      <c r="P112" t="s">
+        <v>1533</v>
+      </c>
+      <c r="Q112" t="s">
+        <v>1534</v>
+      </c>
+    </row>
+    <row r="113" spans="16:17">
+      <c r="P113" t="s">
+        <v>1535</v>
+      </c>
+      <c r="Q113" t="s">
+        <v>1536</v>
+      </c>
+    </row>
+    <row r="114" spans="16:17">
+      <c r="P114" t="s">
+        <v>1537</v>
+      </c>
+      <c r="Q114" t="s">
+        <v>1538</v>
+      </c>
+    </row>
+    <row r="115" spans="16:17">
+      <c r="P115" t="s">
+        <v>321</v>
+      </c>
+      <c r="Q115" t="s">
+        <v>1539</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="A2:M102 A103:D103 F103:M103">
-    <cfRule type="expression" dxfId="18" priority="22">
+    <cfRule type="expression" dxfId="19" priority="24">
       <formula>MOD($B2,2)&lt;&gt;0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="17" priority="23">
+    <cfRule type="expression" dxfId="18" priority="25">
       <formula>MOD($A2,2)&lt;&gt;0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="16" priority="24">
+    <cfRule type="expression" dxfId="17" priority="26">
       <formula>MOD($A2,2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A102:M102 A103:D103 F103:M103">
-    <cfRule type="expression" dxfId="15" priority="19">
+    <cfRule type="expression" dxfId="16" priority="21">
       <formula>MOD($B102,2)&lt;&gt;0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="14" priority="20">
+    <cfRule type="expression" dxfId="15" priority="22">
       <formula>MOD($A102,2)&lt;&gt;0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="13" priority="21">
+    <cfRule type="expression" dxfId="14" priority="23">
       <formula>MOD($A102,2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E103">
-    <cfRule type="expression" dxfId="12" priority="7">
+    <cfRule type="expression" dxfId="13" priority="9">
       <formula>MOD($B103,2)&lt;&gt;0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="11" priority="8">
+    <cfRule type="expression" dxfId="12" priority="10">
       <formula>MOD($A103,2)&lt;&gt;0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="10" priority="9">
+    <cfRule type="expression" dxfId="11" priority="11">
       <formula>MOD($A103,2)=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="9" priority="10">
+    <cfRule type="expression" dxfId="10" priority="12">
       <formula>MOD($B103,2)&lt;&gt;0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="8" priority="11">
+    <cfRule type="expression" dxfId="9" priority="13">
       <formula>MOD($A103,2)&lt;&gt;0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="7" priority="12">
+    <cfRule type="expression" dxfId="8" priority="14">
       <formula>MOD($A103,2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I104">
-    <cfRule type="expression" dxfId="6" priority="1">
+    <cfRule type="expression" dxfId="7" priority="3">
       <formula>MOD($B104,2)&lt;&gt;0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="5" priority="2">
+    <cfRule type="expression" dxfId="6" priority="4">
       <formula>MOD($A104,2)&lt;&gt;0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="4" priority="3">
+    <cfRule type="expression" dxfId="5" priority="5">
       <formula>MOD($A104,2)=0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="3" priority="4">
+    <cfRule type="expression" dxfId="4" priority="6">
       <formula>MOD($B104,2)&lt;&gt;0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="2" priority="5">
+    <cfRule type="expression" dxfId="3" priority="7">
       <formula>MOD($A104,2)&lt;&gt;0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="1" priority="6">
+    <cfRule type="expression" dxfId="2" priority="8">
       <formula>MOD($A104,2)=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K2:K103">
+    <cfRule type="expression" dxfId="1" priority="1">
+      <formula>$K2&lt;&gt;$G2</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -29481,7 +29541,7 @@
         <v>1079</v>
       </c>
       <c r="B3" t="s">
-        <v>1474</v>
+        <v>1079</v>
       </c>
       <c r="D3">
         <v>5</v>
@@ -29495,7 +29555,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>1475</v>
+        <v>1474</v>
       </c>
       <c r="D4">
         <v>4</v>
@@ -29509,7 +29569,7 @@
         <v>1079</v>
       </c>
       <c r="B5" t="s">
-        <v>1476</v>
+        <v>1079</v>
       </c>
       <c r="D5">
         <v>4</v>
@@ -29523,7 +29583,7 @@
         <v>2</v>
       </c>
       <c r="B6" t="s">
-        <v>1477</v>
+        <v>1475</v>
       </c>
       <c r="D6">
         <v>4</v>
@@ -29537,7 +29597,7 @@
         <v>1079</v>
       </c>
       <c r="B7" t="s">
-        <v>1478</v>
+        <v>1079</v>
       </c>
       <c r="D7">
         <v>4</v>
@@ -29551,7 +29611,7 @@
         <v>2</v>
       </c>
       <c r="B8" t="s">
-        <v>1479</v>
+        <v>1476</v>
       </c>
       <c r="D8">
         <v>4</v>
@@ -29579,7 +29639,7 @@
         <v>2</v>
       </c>
       <c r="B10" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
       <c r="D10">
         <v>4</v>
@@ -29593,7 +29653,7 @@
         <v>1079</v>
       </c>
       <c r="B11" t="s">
-        <v>1481</v>
+        <v>1079</v>
       </c>
       <c r="D11">
         <v>4</v>
@@ -29607,7 +29667,7 @@
         <v>2</v>
       </c>
       <c r="B12" t="s">
-        <v>1482</v>
+        <v>1478</v>
       </c>
       <c r="D12">
         <v>4</v>
@@ -29621,7 +29681,7 @@
         <v>1079</v>
       </c>
       <c r="B13" t="s">
-        <v>1483</v>
+        <v>1079</v>
       </c>
       <c r="D13">
         <v>3</v>
@@ -29635,7 +29695,7 @@
         <v>3</v>
       </c>
       <c r="B14" t="s">
-        <v>1484</v>
+        <v>1479</v>
       </c>
       <c r="D14">
         <v>3</v>
@@ -29649,7 +29709,7 @@
         <v>1079</v>
       </c>
       <c r="B15" t="s">
-        <v>1485</v>
+        <v>1079</v>
       </c>
       <c r="D15">
         <v>3</v>
@@ -29663,7 +29723,7 @@
         <v>3</v>
       </c>
       <c r="B16" t="s">
-        <v>1486</v>
+        <v>1480</v>
       </c>
       <c r="D16">
         <v>3</v>
@@ -29677,7 +29737,7 @@
         <v>1079</v>
       </c>
       <c r="B17" t="s">
-        <v>1487</v>
+        <v>1079</v>
       </c>
       <c r="D17">
         <v>3</v>
@@ -29691,7 +29751,7 @@
         <v>3</v>
       </c>
       <c r="B18" t="s">
-        <v>1488</v>
+        <v>1481</v>
       </c>
       <c r="D18">
         <v>3</v>
@@ -29705,7 +29765,7 @@
         <v>1079</v>
       </c>
       <c r="B19" t="s">
-        <v>1489</v>
+        <v>1079</v>
       </c>
       <c r="D19">
         <v>3</v>
@@ -29719,7 +29779,7 @@
         <v>3</v>
       </c>
       <c r="B20" t="s">
-        <v>1490</v>
+        <v>1482</v>
       </c>
       <c r="D20">
         <v>3</v>
@@ -29733,7 +29793,7 @@
         <v>1079</v>
       </c>
       <c r="B21" t="s">
-        <v>1491</v>
+        <v>1079</v>
       </c>
       <c r="D21">
         <v>3</v>
@@ -29747,7 +29807,7 @@
         <v>2</v>
       </c>
       <c r="B22" t="s">
-        <v>1492</v>
+        <v>1483</v>
       </c>
       <c r="D22">
         <v>3</v>
@@ -29761,7 +29821,7 @@
         <v>1079</v>
       </c>
       <c r="B23" t="s">
-        <v>1493</v>
+        <v>1079</v>
       </c>
       <c r="D23">
         <v>3</v>
@@ -29775,7 +29835,7 @@
         <v>3</v>
       </c>
       <c r="B24" t="s">
-        <v>1494</v>
+        <v>1484</v>
       </c>
       <c r="D24">
         <v>3</v>
@@ -29789,7 +29849,7 @@
         <v>1079</v>
       </c>
       <c r="B25" t="s">
-        <v>1495</v>
+        <v>1079</v>
       </c>
       <c r="D25">
         <v>2</v>
@@ -29803,7 +29863,7 @@
         <v>1</v>
       </c>
       <c r="B26" t="s">
-        <v>1496</v>
+        <v>1485</v>
       </c>
       <c r="D26">
         <v>2</v>
@@ -29831,7 +29891,7 @@
         <v>4</v>
       </c>
       <c r="B28" t="s">
-        <v>1497</v>
+        <v>1486</v>
       </c>
       <c r="D28">
         <v>2</v>
@@ -29845,7 +29905,7 @@
         <v>1079</v>
       </c>
       <c r="B29" t="s">
-        <v>1498</v>
+        <v>1079</v>
       </c>
       <c r="D29">
         <v>2</v>
@@ -29859,7 +29919,7 @@
         <v>1</v>
       </c>
       <c r="B30" t="s">
-        <v>1499</v>
+        <v>1487</v>
       </c>
       <c r="D30">
         <v>2</v>
@@ -29873,7 +29933,7 @@
         <v>1079</v>
       </c>
       <c r="B31" t="s">
-        <v>1500</v>
+        <v>1079</v>
       </c>
       <c r="D31">
         <v>2</v>
@@ -29887,7 +29947,7 @@
         <v>2</v>
       </c>
       <c r="B32" t="s">
-        <v>1501</v>
+        <v>1488</v>
       </c>
       <c r="D32">
         <v>2</v>
@@ -29915,7 +29975,7 @@
         <v>2</v>
       </c>
       <c r="B34" t="s">
-        <v>1502</v>
+        <v>1489</v>
       </c>
       <c r="D34">
         <v>2</v>
@@ -29929,7 +29989,7 @@
         <v>1079</v>
       </c>
       <c r="B35" t="s">
-        <v>1503</v>
+        <v>1079</v>
       </c>
       <c r="D35">
         <v>2</v>
@@ -29943,7 +30003,7 @@
         <v>4</v>
       </c>
       <c r="B36" t="s">
-        <v>1504</v>
+        <v>1490</v>
       </c>
       <c r="D36">
         <v>2</v>
@@ -29957,7 +30017,7 @@
         <v>1079</v>
       </c>
       <c r="B37" t="s">
-        <v>1505</v>
+        <v>1079</v>
       </c>
       <c r="D37">
         <v>2</v>
@@ -29971,7 +30031,7 @@
         <v>2</v>
       </c>
       <c r="B38" t="s">
-        <v>1506</v>
+        <v>1491</v>
       </c>
       <c r="D38">
         <v>2</v>
@@ -29985,7 +30045,7 @@
         <v>1079</v>
       </c>
       <c r="B39" t="s">
-        <v>1507</v>
+        <v>1079</v>
       </c>
       <c r="D39">
         <v>2</v>
@@ -29999,7 +30059,7 @@
         <v>2</v>
       </c>
       <c r="B40" t="s">
-        <v>1508</v>
+        <v>1492</v>
       </c>
       <c r="D40">
         <v>2</v>
@@ -30013,7 +30073,7 @@
         <v>1079</v>
       </c>
       <c r="B41" t="s">
-        <v>1509</v>
+        <v>1079</v>
       </c>
       <c r="D41">
         <v>2</v>
@@ -30027,7 +30087,7 @@
         <v>3</v>
       </c>
       <c r="B42" t="s">
-        <v>1510</v>
+        <v>1493</v>
       </c>
       <c r="D42">
         <v>2</v>
@@ -30041,7 +30101,7 @@
         <v>1079</v>
       </c>
       <c r="B43" t="s">
-        <v>1511</v>
+        <v>1079</v>
       </c>
       <c r="D43">
         <v>2</v>
@@ -30055,7 +30115,7 @@
         <v>3</v>
       </c>
       <c r="B44" t="s">
-        <v>1512</v>
+        <v>1494</v>
       </c>
       <c r="D44">
         <v>1</v>
@@ -30069,7 +30129,7 @@
         <v>1079</v>
       </c>
       <c r="B45" t="s">
-        <v>1513</v>
+        <v>1079</v>
       </c>
       <c r="D45">
         <v>1</v>
@@ -30083,7 +30143,7 @@
         <v>2</v>
       </c>
       <c r="B46" t="s">
-        <v>1514</v>
+        <v>1495</v>
       </c>
       <c r="D46">
         <v>1</v>
@@ -30097,7 +30157,7 @@
         <v>1079</v>
       </c>
       <c r="B47" t="s">
-        <v>1515</v>
+        <v>1079</v>
       </c>
       <c r="D47">
         <v>1</v>
@@ -30111,7 +30171,7 @@
         <v>2</v>
       </c>
       <c r="B48" t="s">
-        <v>1516</v>
+        <v>1496</v>
       </c>
       <c r="D48">
         <v>1</v>
@@ -30125,7 +30185,7 @@
         <v>1079</v>
       </c>
       <c r="B49" t="s">
-        <v>1517</v>
+        <v>1079</v>
       </c>
       <c r="D49">
         <v>1</v>
@@ -30139,7 +30199,7 @@
         <v>2</v>
       </c>
       <c r="B50" t="s">
-        <v>1518</v>
+        <v>1497</v>
       </c>
     </row>
     <row r="51" spans="1:5">
@@ -30147,7 +30207,7 @@
         <v>1079</v>
       </c>
       <c r="B51" t="s">
-        <v>1519</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="52" spans="1:5">
@@ -30155,7 +30215,7 @@
         <v>3</v>
       </c>
       <c r="B52" t="s">
-        <v>1520</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="53" spans="1:5">
@@ -30163,7 +30223,7 @@
         <v>1079</v>
       </c>
       <c r="B53" t="s">
-        <v>1521</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="54" spans="1:5">
@@ -30171,7 +30231,7 @@
         <v>1</v>
       </c>
       <c r="B54" t="s">
-        <v>1522</v>
+        <v>1499</v>
       </c>
     </row>
     <row r="55" spans="1:5">
@@ -30179,7 +30239,7 @@
         <v>1079</v>
       </c>
       <c r="B55" t="s">
-        <v>1523</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="56" spans="1:5">
@@ -30187,7 +30247,7 @@
         <v>1</v>
       </c>
       <c r="B56" t="s">
-        <v>1524</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="57" spans="1:5">
@@ -30195,7 +30255,7 @@
         <v>1079</v>
       </c>
       <c r="B57" t="s">
-        <v>1525</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="58" spans="1:5">
@@ -30203,7 +30263,7 @@
         <v>1</v>
       </c>
       <c r="B58" t="s">
-        <v>1526</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="59" spans="1:5">
@@ -30211,7 +30271,7 @@
         <v>1079</v>
       </c>
       <c r="B59" t="s">
-        <v>1527</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="60" spans="1:5">
@@ -30219,7 +30279,7 @@
         <v>2</v>
       </c>
       <c r="B60" t="s">
-        <v>1528</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="61" spans="1:5">
@@ -30235,7 +30295,7 @@
         <v>3</v>
       </c>
       <c r="B62" t="s">
-        <v>1529</v>
+        <v>1503</v>
       </c>
     </row>
     <row r="63" spans="1:5">
@@ -30243,7 +30303,7 @@
         <v>1079</v>
       </c>
       <c r="B63" t="s">
-        <v>1530</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="64" spans="1:5">
@@ -30251,7 +30311,7 @@
         <v>4</v>
       </c>
       <c r="B64" t="s">
-        <v>1531</v>
+        <v>1504</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -30267,7 +30327,7 @@
         <v>2</v>
       </c>
       <c r="B66" t="s">
-        <v>1532</v>
+        <v>1505</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -30275,7 +30335,7 @@
         <v>1079</v>
       </c>
       <c r="B67" t="s">
-        <v>1533</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -30283,7 +30343,7 @@
         <v>3</v>
       </c>
       <c r="B68" t="s">
-        <v>1534</v>
+        <v>1506</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -30299,7 +30359,7 @@
         <v>4</v>
       </c>
       <c r="B70" t="s">
-        <v>1535</v>
+        <v>1507</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -30315,7 +30375,7 @@
         <v>4</v>
       </c>
       <c r="B72" t="s">
-        <v>1536</v>
+        <v>1508</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -30323,7 +30383,7 @@
         <v>1079</v>
       </c>
       <c r="B73" t="s">
-        <v>1537</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -30331,7 +30391,7 @@
         <v>4</v>
       </c>
       <c r="B74" t="s">
-        <v>1538</v>
+        <v>1509</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -30347,7 +30407,7 @@
         <v>2</v>
       </c>
       <c r="B76" t="s">
-        <v>1539</v>
+        <v>1510</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -30355,7 +30415,7 @@
         <v>1079</v>
       </c>
       <c r="B77" t="s">
-        <v>1540</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -30371,7 +30431,7 @@
         <v>1079</v>
       </c>
       <c r="B79" t="s">
-        <v>1541</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -30379,7 +30439,7 @@
         <v>4</v>
       </c>
       <c r="B80" t="s">
-        <v>1542</v>
+        <v>1511</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -30395,7 +30455,7 @@
         <v>3</v>
       </c>
       <c r="B82" t="s">
-        <v>1543</v>
+        <v>1512</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -30411,7 +30471,7 @@
         <v>1</v>
       </c>
       <c r="B84" t="s">
-        <v>1544</v>
+        <v>1513</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -30419,7 +30479,7 @@
         <v>1079</v>
       </c>
       <c r="B85" t="s">
-        <v>1545</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -30427,7 +30487,7 @@
         <v>4</v>
       </c>
       <c r="B86" t="s">
-        <v>1546</v>
+        <v>1514</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -30443,7 +30503,7 @@
         <v>5</v>
       </c>
       <c r="B88" t="s">
-        <v>1547</v>
+        <v>1515</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -30451,7 +30511,7 @@
         <v>1079</v>
       </c>
       <c r="B89" t="s">
-        <v>1548</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -30475,7 +30535,7 @@
         <v>5</v>
       </c>
       <c r="B92" t="s">
-        <v>1549</v>
+        <v>1516</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -30491,7 +30551,7 @@
         <v>2</v>
       </c>
       <c r="B94" t="s">
-        <v>1550</v>
+        <v>1517</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -30499,7 +30559,7 @@
         <v>1079</v>
       </c>
       <c r="B95" t="s">
-        <v>1551</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -30531,7 +30591,7 @@
         <v>1079</v>
       </c>
       <c r="B99" t="s">
-        <v>1552</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -30539,7 +30599,7 @@
         <v>4</v>
       </c>
       <c r="B100" t="s">
-        <v>1553</v>
+        <v>1518</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -30547,7 +30607,7 @@
         <v>1079</v>
       </c>
       <c r="B101" t="s">
-        <v>1554</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -30555,7 +30615,7 @@
         <v>2</v>
       </c>
       <c r="B102" t="s">
-        <v>1555</v>
+        <v>1519</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -30563,7 +30623,7 @@
         <v>2</v>
       </c>
       <c r="B103" t="s">
-        <v>1556</v>
+        <v>1520</v>
       </c>
     </row>
     <row r="104" spans="1:2">
